--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anakonrad/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E62AF80-5461-4F05-88C6-9AD4988BAB39}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424B36F4-CD4D-ED4C-B2CE-D33BD863D11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-17388" windowWidth="30936" windowHeight="16776" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="680" windowWidth="30240" windowHeight="17380" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -26,16 +26,17 @@
     <sheet name="PeriodOfTime" sheetId="9" r:id="rId11"/>
     <sheet name="Attribution" sheetId="16" r:id="rId12"/>
     <sheet name="Relationship" sheetId="17" r:id="rId13"/>
-    <sheet name="QualityCertificate" sheetId="19" r:id="rId14"/>
-    <sheet name="CatalogueRecord" sheetId="10" state="hidden" r:id="rId15"/>
-    <sheet name="Checksum" sheetId="11" r:id="rId16"/>
+    <sheet name="RightsStatement" sheetId="21" r:id="rId14"/>
+    <sheet name="QualityCertificate" sheetId="19" r:id="rId15"/>
+    <sheet name="CatalogueRecord" sheetId="10" state="hidden" r:id="rId16"/>
+    <sheet name="Checksum" sheetId="11" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Agent!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Catalogue!$A$1:$J$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">DataService!$A$1:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dataset!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">DatasetSeries!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">DatasetSeries!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Distribution!$A$1:$J$23</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="691">
   <si>
     <t>Property label</t>
   </si>
@@ -2618,12 +2619,158 @@
 The email address has to be provided starting with mailto: prefix.
 For example: mailto:info@example.com</t>
   </si>
+  <si>
+    <t>series member</t>
+  </si>
+  <si>
+    <t>dcat:seriesMember</t>
+  </si>
+  <si>
+    <t>A dataset that is part of the dataset series.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This is an inverse property of the Dataset's </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> dcat:inSeries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> property. It can be used to show which Datasets are part of a Dataset Series. Note that this inverse </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>may</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> be used in addition to the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>dcat:inSeries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (in Dataset class), but must not be used to replace it. So the connection between Datasets and Series still has to run primarily via the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>dcat:inSeries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Value access rights (Dataset A)</t>
+  </si>
+  <si>
+    <t>Value  rights (Distribution A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Add more columns if you need to describe additional instances of dct:RightsStatement for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">rights or access rights </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>of additional classes (additional instances of Dataset or Distribution)</t>
+    </r>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>is defined by</t>
+  </si>
+  <si>
+    <t>rdfs:label</t>
+  </si>
+  <si>
+    <t>rdfs:isDefinedBy</t>
+  </si>
+  <si>
+    <t>rdfs:label is an instance of rdf:Property that may be used to provide a human-readable version of a resource's name.</t>
+  </si>
+  <si>
+    <t>Used to link to another resource that holds the rights statement.
+These properties could be used when dct:RightsStatement is used for the dct:rights (in Distribution), but are not mandatory, so do not need to be used for the dct:accessRights (in Dataset).</t>
+  </si>
+  <si>
+    <t>rdfs:isDefinedBy is an instance of rdf:Property that is used to indicate a resource defining the subject resource. This property may be used to indicate an RDF vocabulary in which a resource is described.</t>
+  </si>
+  <si>
+    <t>Value access rights (Data Service A)</t>
+  </si>
+  <si>
+    <t>This property allows free text description of the rights.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="55">
+  <fonts count="56" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2974,6 +3121,13 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -3764,9 +3918,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3778,10 +3929,25 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3789,25 +3955,223 @@
     </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="191">
+  <dxfs count="212">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -7379,7 +7743,7 @@
     <tabColor theme="2"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7392,17 +7756,17 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="33.44140625" customWidth="1"/>
-    <col min="3" max="10" width="22.44140625" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" hidden="1" customWidth="1"/>
-    <col min="12" max="14" width="21.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="33.5" customWidth="1"/>
+    <col min="3" max="10" width="22.5" customWidth="1"/>
+    <col min="11" max="11" width="22.5" hidden="1" customWidth="1"/>
+    <col min="12" max="14" width="21.5" customWidth="1"/>
     <col min="15" max="15" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="203" customFormat="1" ht="86.4">
+    <row r="1" spans="1:15" s="203" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -7449,7 +7813,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="72">
+    <row r="2" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="196" t="s">
         <v>563</v>
       </c>
@@ -7485,7 +7849,7 @@
       <c r="M2" s="186"/>
       <c r="N2" s="186"/>
     </row>
-    <row r="3" spans="1:15" ht="28.8">
+    <row r="3" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
         <v>568</v>
       </c>
@@ -7521,35 +7885,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7578,26 +7942,26 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:R52"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="36.109375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="9" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="23.88671875" style="221" customWidth="1"/>
-    <col min="14" max="17" width="23.88671875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="32.109375" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="2"/>
+    <col min="11" max="11" width="18.5" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="23.83203125" style="221" customWidth="1"/>
+    <col min="14" max="17" width="23.83203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="32.1640625" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="100.8">
+    <row r="1" spans="1:18" ht="112" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -7653,7 +8017,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
         <v>578</v>
       </c>
@@ -7687,7 +8051,7 @@
       <c r="P2" s="221"/>
       <c r="Q2" s="221"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
         <v>581</v>
       </c>
@@ -7724,7 +8088,7 @@
       <c r="P3" s="222"/>
       <c r="Q3" s="222"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
       <c r="B4" s="8"/>
       <c r="C4" s="13"/>
@@ -7734,7 +8098,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
       <c r="B5" s="8"/>
       <c r="C5" s="13"/>
@@ -7744,7 +8108,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
       <c r="B6" s="8"/>
       <c r="C6" s="13"/>
@@ -7754,7 +8118,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="B7" s="8"/>
       <c r="C7" s="21"/>
@@ -7764,7 +8128,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
       <c r="B8" s="8"/>
       <c r="C8" s="13"/>
@@ -7774,7 +8138,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13"/>
@@ -7783,7 +8147,7 @@
       <c r="F9" s="3"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="8"/>
       <c r="C10" s="21"/>
@@ -7793,7 +8157,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="8"/>
       <c r="C11" s="13"/>
@@ -7803,7 +8167,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="8"/>
       <c r="C12" s="13"/>
@@ -7813,7 +8177,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="8"/>
       <c r="C13" s="13"/>
@@ -7823,7 +8187,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="13"/>
       <c r="B14" s="8"/>
       <c r="C14" s="13"/>
@@ -7833,7 +8197,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
       <c r="B15" s="8"/>
       <c r="C15" s="13"/>
@@ -7842,7 +8206,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="11"/>
       <c r="D16" s="17"/>
@@ -7851,7 +8215,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="8"/>
       <c r="C17" s="13"/>
@@ -7861,7 +8225,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="20"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="8"/>
       <c r="C18" s="13"/>
@@ -7871,7 +8235,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
@@ -7881,7 +8245,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="8"/>
       <c r="C20" s="13"/>
@@ -7891,7 +8255,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="8"/>
       <c r="C21" s="13"/>
@@ -7901,7 +8265,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="8"/>
       <c r="C22" s="13"/>
@@ -7910,7 +8274,7 @@
       <c r="F22" s="6"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="8"/>
       <c r="C23" s="13"/>
@@ -7920,7 +8284,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="8"/>
       <c r="C24" s="13"/>
@@ -7930,7 +8294,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="8"/>
       <c r="C25" s="13"/>
@@ -7940,7 +8304,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="8"/>
       <c r="D26" s="13"/>
@@ -7949,7 +8313,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="8"/>
       <c r="C27" s="13"/>
@@ -7958,7 +8322,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="8"/>
       <c r="C28" s="13"/>
@@ -7967,7 +8331,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="8"/>
       <c r="C29" s="13"/>
@@ -7977,7 +8341,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="8"/>
       <c r="C30" s="13"/>
@@ -7987,7 +8351,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="8"/>
       <c r="C31" s="13"/>
@@ -7997,7 +8361,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="8"/>
       <c r="C32" s="13"/>
@@ -8007,7 +8371,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="8"/>
       <c r="C33" s="13"/>
@@ -8017,7 +8381,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="8"/>
       <c r="C34" s="13"/>
@@ -8027,7 +8391,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="8"/>
       <c r="C35" s="13"/>
@@ -8037,7 +8401,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="8"/>
       <c r="C36" s="13"/>
@@ -8047,7 +8411,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="8"/>
       <c r="C37" s="13"/>
@@ -8057,7 +8421,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="8"/>
       <c r="C38" s="13"/>
@@ -8067,7 +8431,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="8"/>
       <c r="C39" s="13"/>
@@ -8077,7 +8441,7 @@
       <c r="G39" s="12"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="8"/>
       <c r="C40" s="13"/>
@@ -8087,7 +8451,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="8"/>
       <c r="C41" s="13"/>
@@ -8097,7 +8461,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="13"/>
       <c r="B42" s="8"/>
       <c r="C42" s="13"/>
@@ -8107,7 +8471,7 @@
       <c r="G42" s="12"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="13"/>
       <c r="B43" s="8"/>
       <c r="C43" s="13"/>
@@ -8117,7 +8481,7 @@
       <c r="G43" s="12"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="8"/>
       <c r="C44" s="13"/>
@@ -8127,7 +8491,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="8"/>
       <c r="C45" s="13"/>
@@ -8137,7 +8501,7 @@
       <c r="G45" s="12"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="B46" s="8"/>
       <c r="C46" s="13"/>
@@ -8147,7 +8511,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
       <c r="B47" s="8"/>
       <c r="C47" s="13"/>
@@ -8156,7 +8520,7 @@
       <c r="F47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="11"/>
       <c r="C48" s="13"/>
@@ -8166,7 +8530,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="B49" s="11"/>
       <c r="C49" s="13"/>
@@ -8176,7 +8540,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="8"/>
       <c r="C50" s="13"/>
@@ -8186,7 +8550,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="13"/>
       <c r="B51" s="8"/>
       <c r="C51" s="13"/>
@@ -8196,7 +8560,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="13"/>
       <c r="B52" s="8"/>
       <c r="C52" s="13"/>
@@ -8211,71 +8575,71 @@
     <sortCondition ref="A2:A3"/>
   </sortState>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="95" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="91" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="87" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="86" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="82" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="19" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="20" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="80" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8307,22 +8671,22 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="84" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" style="84" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="84" customWidth="1"/>
-    <col min="4" max="4" width="62.44140625" style="84" customWidth="1"/>
-    <col min="5" max="5" width="43.44140625" style="84" customWidth="1"/>
-    <col min="6" max="9" width="20.109375" style="84" customWidth="1"/>
-    <col min="10" max="10" width="23.44140625" style="84" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" style="84" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="84" customWidth="1"/>
+    <col min="2" max="2" width="25.5" style="84" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="84" customWidth="1"/>
+    <col min="4" max="4" width="62.5" style="84" customWidth="1"/>
+    <col min="5" max="5" width="43.5" style="84" customWidth="1"/>
+    <col min="6" max="9" width="20.1640625" style="84" customWidth="1"/>
+    <col min="10" max="10" width="23.5" style="84" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="84" hidden="1" customWidth="1"/>
     <col min="12" max="14" width="23.6640625" style="84" customWidth="1"/>
-    <col min="15" max="15" width="28.88671875" style="84" customWidth="1"/>
-    <col min="16" max="16384" width="9.109375" style="84"/>
+    <col min="15" max="15" width="28.83203125" style="84" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="84"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="72">
+    <row r="1" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -8369,7 +8733,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="43.2">
+    <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
         <v>588</v>
       </c>
@@ -8411,7 +8775,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="129.6">
+    <row r="3" spans="1:15" ht="144" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
         <v>592</v>
       </c>
@@ -8449,35 +8813,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="76" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="75" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8506,17 +8870,17 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="39.44140625" customWidth="1"/>
-    <col min="6" max="10" width="21.5546875" customWidth="1"/>
-    <col min="11" max="11" width="21.5546875" hidden="1" customWidth="1"/>
+    <col min="1" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="39.5" customWidth="1"/>
+    <col min="6" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="11" width="21.5" hidden="1" customWidth="1"/>
     <col min="12" max="14" width="22.33203125" customWidth="1"/>
-    <col min="15" max="15" width="30.5546875" customWidth="1"/>
+    <col min="15" max="15" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="72">
+    <row r="1" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -8563,7 +8927,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="158.4">
+    <row r="2" spans="1:15" ht="160" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
         <v>601</v>
       </c>
@@ -8596,7 +8960,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:15" ht="43.2">
+    <row r="3" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
         <v>604</v>
       </c>
@@ -8634,35 +8998,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="67" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="66" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="62" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8686,22 +9050,236 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6D3B52-437B-734C-B0BB-62A8603A4A6B}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="272" x14ac:dyDescent="0.2">
+      <c r="A1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="91" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="90" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="90" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="218" t="s">
+        <v>679</v>
+      </c>
+      <c r="M1" s="229" t="s">
+        <v>689</v>
+      </c>
+      <c r="N1" s="228" t="s">
+        <v>680</v>
+      </c>
+      <c r="O1" s="233" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="288" x14ac:dyDescent="0.2">
+      <c r="A2" s="84" t="s">
+        <v>683</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>688</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>685</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>687</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="115" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="47"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" ht="192" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
+        <v>682</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>686</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>684</v>
+      </c>
+      <c r="D3" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>690</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H2:H3">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="19" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:I1 F1">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{1E9612B5-4C26-A54F-A21A-A1EFC8A78C99}">
+      <formula1>"Mandatory, Recommended, Optional, Conditional, Not added"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{08A261FB-F401-7641-928A-0ED66A3CB93C}">
+      <formula1>"DCAT-AP v3, HealthDCAT-AP, DCAT-AP NL, HRI v1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{E5FDED36-F749-F347-86E9-0ABD637771E3}">
+      <formula1>"Identical to v1, Adapted from v1, new"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{D57261FB-665E-0148-8005-E1D65239456A}">
+      <formula1>"Mandatory, Recommended, Optional, Conditional"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{CB7D5334-DDD1-4546-9B26-FDBB304C1859}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB048F93-E797-4F9D-B044-1487CE8C21FF}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="20.109375" customWidth="1"/>
-    <col min="5" max="5" width="33.5546875" customWidth="1"/>
-    <col min="6" max="10" width="20.109375" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="33.5" customWidth="1"/>
+    <col min="6" max="10" width="20.1640625" customWidth="1"/>
+    <col min="11" max="11" width="20.1640625" hidden="1" customWidth="1"/>
     <col min="12" max="14" width="16.33203125" customWidth="1"/>
-    <col min="15" max="15" width="27.5546875" customWidth="1"/>
+    <col min="15" max="15" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="72">
+    <row r="1" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -8748,7 +9326,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="100.8">
+    <row r="2" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
         <v>612</v>
       </c>
@@ -8781,7 +9359,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:15" ht="57.6">
+    <row r="3" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
         <v>616</v>
       </c>
@@ -8819,35 +9397,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="57" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8870,25 +9448,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D9DD92-C939-4751-8A55-ABA6494CBB01}">
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.44140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="53.44140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="54.44140625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="22.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="9" customWidth="1"/>
+    <col min="3" max="3" width="53.5" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="9" customWidth="1"/>
+    <col min="5" max="5" width="54.5" style="9" customWidth="1"/>
+    <col min="6" max="6" width="22.1640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="2"/>
+    <col min="11" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57.6">
+    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
@@ -8920,7 +9498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.8">
+    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="63" t="s">
         <v>621</v>
       </c>
@@ -8948,7 +9526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.2">
+    <row r="3" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="67" t="s">
         <v>625</v>
       </c>
@@ -8976,7 +9554,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.2">
+    <row r="4" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="63" t="s">
         <v>630</v>
       </c>
@@ -9004,7 +9582,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.2">
+    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="67" t="s">
         <v>635</v>
       </c>
@@ -9034,7 +9612,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.8">
+    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="63" t="s">
         <v>641</v>
       </c>
@@ -9062,7 +9640,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="28.8">
+    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="67" t="s">
         <v>644</v>
       </c>
@@ -9090,7 +9668,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="86.4">
+    <row r="8" spans="1:10" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
         <v>647</v>
       </c>
@@ -9120,7 +9698,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.8">
+    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="67" t="s">
         <v>652</v>
       </c>
@@ -9148,7 +9726,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.8">
+    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="63" t="s">
         <v>656</v>
       </c>
@@ -9178,7 +9756,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="8"/>
       <c r="C11" s="16"/>
@@ -9187,7 +9765,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="8"/>
       <c r="C12" s="16"/>
@@ -9197,7 +9775,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="8"/>
       <c r="C13" s="13"/>
@@ -9206,7 +9784,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="13"/>
       <c r="B14" s="8"/>
       <c r="C14" s="13"/>
@@ -9215,7 +9793,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
       <c r="B15" s="8"/>
       <c r="C15" s="13"/>
@@ -9225,7 +9803,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="8"/>
       <c r="C16" s="13"/>
@@ -9235,7 +9813,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="8"/>
       <c r="C17" s="13"/>
@@ -9245,7 +9823,7 @@
       <c r="G17" s="12"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="8"/>
       <c r="C18" s="13"/>
@@ -9255,7 +9833,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
@@ -9265,7 +9843,7 @@
       <c r="G19" s="12"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="8"/>
       <c r="C20" s="13"/>
@@ -9275,7 +9853,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="8"/>
       <c r="C21" s="13"/>
@@ -9285,7 +9863,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="8"/>
       <c r="C22" s="13"/>
@@ -9295,7 +9873,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="8"/>
       <c r="C23" s="13"/>
@@ -9305,7 +9883,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="8"/>
       <c r="C24" s="13"/>
@@ -9315,7 +9893,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="8"/>
       <c r="C25" s="13"/>
@@ -9325,7 +9903,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="8"/>
       <c r="C26" s="13"/>
@@ -9335,7 +9913,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="8"/>
       <c r="C27" s="13"/>
@@ -9345,7 +9923,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="8"/>
       <c r="C28" s="13"/>
@@ -9355,7 +9933,7 @@
       <c r="G28" s="12"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="8"/>
       <c r="C29" s="13"/>
@@ -9365,7 +9943,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="8"/>
       <c r="C30" s="13"/>
@@ -9375,7 +9953,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="8"/>
       <c r="C31" s="13"/>
@@ -9385,7 +9963,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="8"/>
       <c r="C32" s="13"/>
@@ -9395,7 +9973,7 @@
       <c r="G32" s="12"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="8"/>
       <c r="C33" s="13"/>
@@ -9404,7 +9982,7 @@
       <c r="F33" s="13"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="11"/>
       <c r="C34" s="13"/>
@@ -9414,7 +9992,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="11"/>
       <c r="C35" s="13"/>
@@ -9424,7 +10002,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="8"/>
       <c r="C36" s="13"/>
@@ -9434,7 +10012,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="8"/>
       <c r="C37" s="13"/>
@@ -9444,7 +10022,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="8"/>
       <c r="C38" s="13"/>
@@ -9459,96 +10037,96 @@
     <sortCondition ref="A2:A10"/>
   </sortState>
   <conditionalFormatting sqref="A27:B28">
-    <cfRule type="cellIs" dxfId="49" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="41" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="42" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="43" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="44" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26:E28">
-    <cfRule type="cellIs" dxfId="45" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="45" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="46" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="47" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="48" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="cellIs" dxfId="41" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="51" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="52" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="53" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="54" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F7 E8">
-    <cfRule type="cellIs" dxfId="37" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="40" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F38">
-    <cfRule type="cellIs" dxfId="36" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="33" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="36" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="37" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="38" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="39" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H11">
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="10" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H27 H36:H38">
-    <cfRule type="cellIs" dxfId="29" priority="49" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="49" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F7">
-    <cfRule type="cellIs" dxfId="27" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9574,29 +10152,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AED35DC-FECA-41E4-9CA3-956572264BDD}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:N52"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" style="9" customWidth="1"/>
-    <col min="3" max="4" width="17.88671875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.44140625" style="2" customWidth="1"/>
-    <col min="8" max="10" width="17.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="33.109375" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="17.83203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="9" customWidth="1"/>
+    <col min="3" max="4" width="17.83203125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5" style="2" customWidth="1"/>
+    <col min="8" max="10" width="17.83203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="33.1640625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="71.25" customHeight="1">
+    <row r="1" spans="1:14" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -9640,7 +10218,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="72">
+    <row r="2" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
         <v>663</v>
       </c>
@@ -9672,7 +10250,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="71.25" customHeight="1">
+    <row r="3" spans="1:14" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49" t="s">
         <v>669</v>
       </c>
@@ -9705,7 +10283,7 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
       <c r="B4" s="8"/>
       <c r="C4" s="13"/>
@@ -9715,7 +10293,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
       <c r="B5" s="8"/>
       <c r="C5" s="13"/>
@@ -9725,7 +10303,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
       <c r="B6" s="8"/>
       <c r="C6" s="13"/>
@@ -9735,7 +10313,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="B7" s="8"/>
       <c r="C7" s="21"/>
@@ -9745,7 +10323,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
       <c r="B8" s="8"/>
       <c r="C8" s="13"/>
@@ -9755,7 +10333,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13"/>
@@ -9764,7 +10342,7 @@
       <c r="F9" s="3"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="8"/>
       <c r="C10" s="21"/>
@@ -9774,7 +10352,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="8"/>
       <c r="C11" s="13"/>
@@ -9784,7 +10362,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="8"/>
       <c r="C12" s="13"/>
@@ -9794,7 +10372,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="8"/>
       <c r="C13" s="13"/>
@@ -9804,7 +10382,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="13"/>
       <c r="B14" s="8"/>
       <c r="C14" s="13"/>
@@ -9814,7 +10392,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
       <c r="B15" s="8"/>
       <c r="C15" s="13"/>
@@ -9823,7 +10401,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="11"/>
       <c r="D16" s="17"/>
@@ -9832,7 +10410,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="8"/>
       <c r="C17" s="13"/>
@@ -9842,7 +10420,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="20"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="8"/>
       <c r="C18" s="13"/>
@@ -9852,7 +10430,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
@@ -9862,7 +10440,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="8"/>
       <c r="C20" s="13"/>
@@ -9872,7 +10450,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="8"/>
       <c r="C21" s="13"/>
@@ -9882,7 +10460,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="8"/>
       <c r="C22" s="13"/>
@@ -9891,7 +10469,7 @@
       <c r="F22" s="6"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="8"/>
       <c r="C23" s="13"/>
@@ -9901,7 +10479,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="8"/>
       <c r="C24" s="13"/>
@@ -9911,7 +10489,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="8"/>
       <c r="C25" s="13"/>
@@ -9921,7 +10499,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="8"/>
       <c r="D26" s="13"/>
@@ -9930,7 +10508,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="8"/>
       <c r="C27" s="13"/>
@@ -9939,7 +10517,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="8"/>
       <c r="C28" s="13"/>
@@ -9948,7 +10526,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="8"/>
       <c r="C29" s="13"/>
@@ -9958,7 +10536,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="8"/>
       <c r="C30" s="13"/>
@@ -9968,7 +10546,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="8"/>
       <c r="C31" s="13"/>
@@ -9978,7 +10556,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="8"/>
       <c r="C32" s="13"/>
@@ -9988,7 +10566,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="8"/>
       <c r="C33" s="13"/>
@@ -9998,7 +10576,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="8"/>
       <c r="C34" s="13"/>
@@ -10008,7 +10586,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="8"/>
       <c r="C35" s="13"/>
@@ -10018,7 +10596,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="8"/>
       <c r="C36" s="13"/>
@@ -10028,7 +10606,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="8"/>
       <c r="C37" s="13"/>
@@ -10038,7 +10616,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="8"/>
       <c r="C38" s="13"/>
@@ -10048,7 +10626,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="8"/>
       <c r="C39" s="13"/>
@@ -10058,7 +10636,7 @@
       <c r="G39" s="12"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="8"/>
       <c r="C40" s="13"/>
@@ -10068,7 +10646,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="8"/>
       <c r="C41" s="13"/>
@@ -10078,7 +10656,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="13"/>
       <c r="B42" s="8"/>
       <c r="C42" s="13"/>
@@ -10088,7 +10666,7 @@
       <c r="G42" s="12"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="13"/>
       <c r="B43" s="8"/>
       <c r="C43" s="13"/>
@@ -10098,7 +10676,7 @@
       <c r="G43" s="12"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="8"/>
       <c r="C44" s="13"/>
@@ -10108,7 +10686,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="8"/>
       <c r="C45" s="13"/>
@@ -10118,7 +10696,7 @@
       <c r="G45" s="12"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="B46" s="8"/>
       <c r="C46" s="13"/>
@@ -10128,7 +10706,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
       <c r="B47" s="8"/>
       <c r="C47" s="13"/>
@@ -10137,7 +10715,7 @@
       <c r="F47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="11"/>
       <c r="C48" s="13"/>
@@ -10147,7 +10725,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="B49" s="11"/>
       <c r="C49" s="13"/>
@@ -10157,7 +10735,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="8"/>
       <c r="C50" s="13"/>
@@ -10167,7 +10745,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="13"/>
       <c r="B51" s="8"/>
       <c r="C51" s="13"/>
@@ -10177,7 +10755,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="13"/>
       <c r="B52" s="8"/>
       <c r="C52" s="13"/>
@@ -10192,88 +10770,88 @@
     <sortCondition ref="A2:A3"/>
   </sortState>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="23" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="22" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="23" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="24" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="19" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="25" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="26" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="27" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="28" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G3">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="16" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="17" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="18" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="19" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="29" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="30" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10305,7 +10883,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E2C641-7C5D-47E8-9C29-F3A4B74AE3E2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10318,25 +10896,25 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:M56"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.5546875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5546875" style="34" customWidth="1"/>
-    <col min="5" max="5" width="54.44140625" style="41" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="32" customWidth="1"/>
+    <col min="2" max="2" width="40.5" style="41" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="34" customWidth="1"/>
+    <col min="5" max="5" width="54.5" style="41" customWidth="1"/>
+    <col min="6" max="6" width="22.1640625" style="32" customWidth="1"/>
     <col min="7" max="7" width="24" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="32" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="32" customWidth="1"/>
     <col min="10" max="10" width="16" style="32" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" style="32" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="26.44140625" style="32" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="32" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="26.5" style="32" customWidth="1"/>
     <col min="13" max="13" width="27" style="32" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="32"/>
+    <col min="14" max="16384" width="9.1640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="199" customFormat="1" ht="57.6">
+    <row r="1" spans="1:13" s="199" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -10377,7 +10955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="131" t="s">
         <v>13</v>
       </c>
@@ -10412,7 +10990,7 @@
       <c r="L2" s="107"/>
       <c r="M2" s="107"/>
     </row>
-    <row r="3" spans="1:13" ht="43.2">
+    <row r="3" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="125" t="s">
         <v>23</v>
       </c>
@@ -10449,7 +11027,7 @@
       </c>
       <c r="M3" s="129"/>
     </row>
-    <row r="4" spans="1:13" ht="95.25" customHeight="1">
+    <row r="4" spans="1:13" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="131" t="s">
         <v>31</v>
       </c>
@@ -10490,7 +11068,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="201.6">
+    <row r="5" spans="1:13" ht="208" x14ac:dyDescent="0.2">
       <c r="A5" s="125" t="s">
         <v>40</v>
       </c>
@@ -10529,7 +11107,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="43.2">
+    <row r="6" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="121" t="s">
         <v>47</v>
       </c>
@@ -10566,7 +11144,7 @@
       </c>
       <c r="M6" s="107"/>
     </row>
-    <row r="7" spans="1:13" ht="29.1" customHeight="1">
+    <row r="7" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
         <v>54</v>
       </c>
@@ -10603,110 +11181,110 @@
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
     </row>
-    <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="237" t="s">
+    <row r="8" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="C8" s="236" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="239" t="s">
+      <c r="E8" s="238" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="236" t="s">
+      <c r="F8" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="236" t="s">
+      <c r="G8" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="236" t="s">
+      <c r="H8" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="235" t="s">
+      <c r="I8" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="235" t="s">
+      <c r="J8" s="239" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
-    </row>
-    <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="237"/>
-      <c r="B9" s="238"/>
-      <c r="C9" s="237"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
+    </row>
+    <row r="9" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="236"/>
+      <c r="B9" s="237"/>
+      <c r="C9" s="236"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-    </row>
-    <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="237"/>
-      <c r="B10" s="238"/>
-      <c r="C10" s="237"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
+    </row>
+    <row r="10" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="236"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="236"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="239"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-    </row>
-    <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="237"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="237"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+    </row>
+    <row r="11" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="236"/>
+      <c r="B11" s="237"/>
+      <c r="C11" s="236"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="239"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
+      <c r="E11" s="238"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="235"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="237"/>
-      <c r="B12" s="238"/>
-      <c r="C12" s="237"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="236"/>
+      <c r="B12" s="237"/>
+      <c r="C12" s="236"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="239"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="239"/>
+      <c r="J12" s="239"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="235"/>
-    </row>
-    <row r="13" spans="1:13" ht="43.2">
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
+    </row>
+    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="125" t="s">
         <v>71</v>
       </c>
@@ -10743,7 +11321,7 @@
       </c>
       <c r="M13" s="129"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="121" t="s">
         <v>76</v>
       </c>
@@ -10778,7 +11356,7 @@
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
-    <row r="15" spans="1:13" ht="57.6">
+    <row r="15" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="125" t="s">
         <v>82</v>
       </c>
@@ -10815,7 +11393,7 @@
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
     </row>
-    <row r="16" spans="1:13" ht="43.2">
+    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="121" t="s">
         <v>89</v>
       </c>
@@ -10852,7 +11430,7 @@
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="125" t="s">
         <v>96</v>
       </c>
@@ -10887,7 +11465,7 @@
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
     </row>
-    <row r="18" spans="1:13" ht="43.2">
+    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="121" t="s">
         <v>101</v>
       </c>
@@ -10928,7 +11506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="125" t="s">
         <v>107</v>
       </c>
@@ -10963,7 +11541,7 @@
       <c r="L19" s="129"/>
       <c r="M19" s="129"/>
     </row>
-    <row r="20" spans="1:13" ht="43.2">
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>111</v>
       </c>
@@ -10998,7 +11576,7 @@
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
-    <row r="21" spans="1:13" ht="72">
+    <row r="21" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A21" s="125" t="s">
         <v>116</v>
       </c>
@@ -11035,7 +11613,7 @@
       </c>
       <c r="M21" s="129"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="121" t="s">
         <v>122</v>
       </c>
@@ -11070,7 +11648,7 @@
       <c r="L22" s="107"/>
       <c r="M22" s="107"/>
     </row>
-    <row r="23" spans="1:13" ht="57.6">
+    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="125" t="s">
         <v>127</v>
       </c>
@@ -11105,7 +11683,7 @@
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
     </row>
-    <row r="24" spans="1:13" ht="28.8">
+    <row r="24" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="121" t="s">
         <v>132</v>
       </c>
@@ -11142,7 +11720,7 @@
       <c r="L24" s="107"/>
       <c r="M24" s="107"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="33"/>
       <c r="B25" s="34"/>
       <c r="C25" s="33"/>
@@ -11153,7 +11731,7 @@
       <c r="H25" s="37"/>
       <c r="K25" s="95"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="33"/>
       <c r="B26" s="34"/>
       <c r="C26" s="33"/>
@@ -11164,7 +11742,7 @@
       <c r="H26" s="37"/>
       <c r="K26" s="93"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="33"/>
       <c r="B27" s="34"/>
       <c r="C27" s="33"/>
@@ -11175,7 +11753,7 @@
       <c r="H27" s="37"/>
       <c r="K27" s="93"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="33"/>
       <c r="B28" s="34"/>
       <c r="C28" s="33"/>
@@ -11186,7 +11764,7 @@
       <c r="H28" s="37"/>
       <c r="K28" s="93"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="33"/>
       <c r="B29" s="34"/>
       <c r="C29" s="33"/>
@@ -11197,7 +11775,7 @@
       <c r="H29" s="37"/>
       <c r="K29" s="93"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="33"/>
       <c r="B30" s="34"/>
       <c r="D30" s="38"/>
@@ -11207,7 +11785,7 @@
       <c r="H30" s="37"/>
       <c r="K30" s="93"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="33"/>
       <c r="B31" s="34"/>
       <c r="C31" s="33"/>
@@ -11218,7 +11796,7 @@
       <c r="H31" s="37"/>
       <c r="K31" s="93"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="33"/>
       <c r="B32" s="34"/>
       <c r="C32" s="33"/>
@@ -11229,7 +11807,7 @@
       <c r="H32" s="37"/>
       <c r="K32" s="103"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="33"/>
       <c r="B33" s="34"/>
       <c r="C33" s="33"/>
@@ -11240,7 +11818,7 @@
       <c r="H33" s="37"/>
       <c r="K33" s="93"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="33"/>
       <c r="B34" s="34"/>
       <c r="C34" s="33"/>
@@ -11251,7 +11829,7 @@
       <c r="H34" s="37"/>
       <c r="K34" s="93"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="33"/>
       <c r="B35" s="34"/>
       <c r="C35" s="33"/>
@@ -11262,7 +11840,7 @@
       <c r="H35" s="37"/>
       <c r="K35" s="93"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="33"/>
       <c r="B36" s="34"/>
       <c r="D36" s="38"/>
@@ -11272,7 +11850,7 @@
       <c r="H36" s="37"/>
       <c r="K36" s="93"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="33"/>
       <c r="B37" s="34"/>
       <c r="C37" s="33"/>
@@ -11283,7 +11861,7 @@
       <c r="H37" s="37"/>
       <c r="K37" s="93"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="33"/>
       <c r="B38" s="34"/>
       <c r="C38" s="33"/>
@@ -11296,7 +11874,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="33"/>
       <c r="B39" s="34"/>
       <c r="C39" s="33"/>
@@ -11307,7 +11885,7 @@
       <c r="H39" s="37"/>
       <c r="K39" s="96"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="33"/>
       <c r="B40" s="34"/>
       <c r="C40" s="33"/>
@@ -11320,7 +11898,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="33"/>
       <c r="B41" s="34"/>
       <c r="C41" s="33"/>
@@ -11331,7 +11909,7 @@
       <c r="H41" s="37"/>
       <c r="K41" s="96"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="33"/>
       <c r="B42" s="34"/>
       <c r="C42" s="33"/>
@@ -11344,7 +11922,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="33"/>
       <c r="B43" s="34"/>
       <c r="C43" s="33"/>
@@ -11357,7 +11935,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="33"/>
       <c r="B44" s="34"/>
       <c r="C44" s="33"/>
@@ -11370,7 +11948,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="33"/>
       <c r="B45" s="34"/>
       <c r="C45" s="33"/>
@@ -11383,7 +11961,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="33"/>
       <c r="B46" s="34"/>
       <c r="D46" s="38"/>
@@ -11395,7 +11973,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="33"/>
       <c r="B47" s="34"/>
       <c r="C47" s="33"/>
@@ -11408,7 +11986,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="33"/>
       <c r="B48" s="34"/>
       <c r="C48" s="33"/>
@@ -11421,7 +11999,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="33"/>
       <c r="B49" s="34"/>
       <c r="C49" s="33"/>
@@ -11434,7 +12012,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="33"/>
       <c r="B50" s="34"/>
       <c r="C50" s="33"/>
@@ -11447,7 +12025,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="33"/>
       <c r="B51" s="34"/>
       <c r="C51" s="33"/>
@@ -11460,7 +12038,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="33"/>
       <c r="B52" s="34"/>
       <c r="C52" s="33"/>
@@ -11473,7 +12051,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="33"/>
       <c r="B53" s="34"/>
       <c r="C53" s="33"/>
@@ -11486,7 +12064,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="33"/>
       <c r="B54" s="34"/>
       <c r="D54" s="38"/>
@@ -11496,7 +12074,7 @@
       <c r="H54" s="37"/>
       <c r="K54" s="96"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="33"/>
       <c r="B55" s="34"/>
       <c r="C55" s="33"/>
@@ -11507,7 +12085,7 @@
       <c r="H55" s="37"/>
       <c r="K55" s="93"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="33"/>
       <c r="B56" s="34"/>
       <c r="C56" s="33"/>
@@ -11523,84 +12101,84 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <mergeCells count="11">
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="J8:J12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="F8:F12"/>
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="190" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="211" priority="16" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:F56">
-    <cfRule type="cellIs" dxfId="189" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="210" priority="26" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="29" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="30" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="31" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="32" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H8 H13:H56">
-    <cfRule type="cellIs" dxfId="184" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="205" priority="17" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="204" priority="18" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F8">
-    <cfRule type="cellIs" dxfId="182" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="201" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J8 J13:J56">
-    <cfRule type="containsText" dxfId="178" priority="13" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="199" priority="13" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="177" priority="14" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="198" priority="14" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="176" priority="15" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="197" priority="15" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="175" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="196" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="194" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="193" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11651,27 +12229,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.5546875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="28.88671875" style="41" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="34" customWidth="1"/>
-    <col min="5" max="5" width="68.88671875" style="34" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.88671875" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" style="32" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="32" customWidth="1"/>
-    <col min="10" max="10" width="24.44140625" style="32" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" style="32" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="31.5546875" style="32" customWidth="1"/>
-    <col min="13" max="13" width="23.44140625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="25.5" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5" style="41" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="41" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="34" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="34" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="32" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" style="32" customWidth="1"/>
+    <col min="10" max="10" width="24.5" style="32" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="32" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="31.5" style="32" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="32" customWidth="1"/>
     <col min="14" max="14" width="25.6640625" style="32" customWidth="1"/>
-    <col min="15" max="15" width="25.88671875" style="32" customWidth="1"/>
-    <col min="16" max="16384" width="9.109375" style="32"/>
+    <col min="15" max="15" width="25.83203125" style="32" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="199" customFormat="1" ht="41.4">
+    <row r="1" spans="1:14" s="199" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
@@ -11715,7 +12293,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="209.25" customHeight="1">
+    <row r="2" spans="1:14" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="121" t="s">
         <v>150</v>
       </c>
@@ -11751,7 +12329,7 @@
       </c>
       <c r="L2" s="107"/>
     </row>
-    <row r="3" spans="1:14" ht="72">
+    <row r="3" spans="1:14" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" s="125" t="s">
         <v>156</v>
       </c>
@@ -11791,7 +12369,7 @@
       <c r="M3" s="129"/>
       <c r="N3" s="129"/>
     </row>
-    <row r="4" spans="1:14" s="117" customFormat="1" ht="144">
+    <row r="4" spans="1:14" s="117" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A4" s="131" t="s">
         <v>13</v>
       </c>
@@ -11827,7 +12405,7 @@
       </c>
       <c r="L4" s="107"/>
     </row>
-    <row r="5" spans="1:14" ht="57.6">
+    <row r="5" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="125" t="s">
         <v>164</v>
       </c>
@@ -11865,7 +12443,7 @@
       <c r="M5" s="129"/>
       <c r="N5" s="129"/>
     </row>
-    <row r="6" spans="1:14" ht="28.8">
+    <row r="6" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="121" t="s">
         <v>170</v>
       </c>
@@ -11901,7 +12479,7 @@
       </c>
       <c r="L6" s="107"/>
     </row>
-    <row r="7" spans="1:14" ht="43.2">
+    <row r="7" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
         <v>176</v>
       </c>
@@ -11939,7 +12517,7 @@
       <c r="M7" s="129"/>
       <c r="N7" s="129"/>
     </row>
-    <row r="8" spans="1:14" ht="123.75" customHeight="1">
+    <row r="8" spans="1:14" ht="123.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="121" t="s">
         <v>31</v>
       </c>
@@ -11983,7 +12561,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="187.2">
+    <row r="9" spans="1:14" ht="176" x14ac:dyDescent="0.2">
       <c r="A9" s="125" t="s">
         <v>40</v>
       </c>
@@ -12027,7 +12605,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="57.6">
+    <row r="10" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="121" t="s">
         <v>54</v>
       </c>
@@ -12063,7 +12641,7 @@
       </c>
       <c r="L10" s="107"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="125" t="s">
         <v>185</v>
       </c>
@@ -12105,7 +12683,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8">
+    <row r="12" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="121" t="s">
         <v>190</v>
       </c>
@@ -12141,7 +12719,7 @@
       </c>
       <c r="L12" s="107"/>
     </row>
-    <row r="13" spans="1:14" ht="69.75" customHeight="1">
+    <row r="13" spans="1:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="125" t="s">
         <v>195</v>
       </c>
@@ -12179,105 +12757,105 @@
       <c r="M13" s="129"/>
       <c r="N13" s="129"/>
     </row>
-    <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="237" t="s">
+    <row r="14" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="240" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="237" t="s">
+      <c r="C14" s="236" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="239" t="s">
+      <c r="E14" s="238" t="s">
         <v>201</v>
       </c>
-      <c r="F14" s="236" t="s">
+      <c r="F14" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="236" t="s">
+      <c r="G14" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="236" t="s">
+      <c r="H14" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="235" t="s">
+      <c r="I14" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="235" t="s">
+      <c r="J14" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="240"/>
-      <c r="L14" s="235"/>
-    </row>
-    <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="237"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="237"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="239"/>
+    </row>
+    <row r="15" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="236"/>
+      <c r="B15" s="240"/>
+      <c r="C15" s="236"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="239"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="240"/>
-      <c r="L15" s="235"/>
-    </row>
-    <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="237"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="237"/>
+      <c r="E15" s="238"/>
+      <c r="F15" s="235"/>
+      <c r="G15" s="235"/>
+      <c r="H15" s="235"/>
+      <c r="I15" s="239"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="239"/>
+    </row>
+    <row r="16" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="236"/>
+      <c r="B16" s="240"/>
+      <c r="C16" s="236"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="239"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="235"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="237"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="237"/>
+      <c r="E16" s="238"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="239"/>
+    </row>
+    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="236"/>
+      <c r="B17" s="240"/>
+      <c r="C17" s="236"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="239"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="235"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="237"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="237"/>
+      <c r="E17" s="238"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="239"/>
+    </row>
+    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="236"/>
+      <c r="B18" s="240"/>
+      <c r="C18" s="236"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="239"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="235"/>
-    </row>
-    <row r="19" spans="1:14" ht="28.8">
+      <c r="E18" s="238"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="239"/>
+    </row>
+    <row r="19" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="125" t="s">
         <v>202</v>
       </c>
@@ -12317,7 +12895,7 @@
       <c r="M19" s="129"/>
       <c r="N19" s="129"/>
     </row>
-    <row r="20" spans="1:14" ht="86.4">
+    <row r="20" spans="1:14" ht="96" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>208</v>
       </c>
@@ -12353,7 +12931,7 @@
       </c>
       <c r="L20" s="107"/>
     </row>
-    <row r="21" spans="1:14" ht="100.8">
+    <row r="21" spans="1:14" ht="96" x14ac:dyDescent="0.2">
       <c r="A21" s="125" t="s">
         <v>213</v>
       </c>
@@ -12391,7 +12969,7 @@
       <c r="M21" s="129"/>
       <c r="N21" s="129"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="121" t="s">
         <v>218</v>
       </c>
@@ -12427,7 +13005,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="43.2">
+    <row r="23" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="125" t="s">
         <v>224</v>
       </c>
@@ -12465,7 +13043,7 @@
       <c r="M23" s="129"/>
       <c r="N23" s="129"/>
     </row>
-    <row r="24" spans="1:14" ht="43.2">
+    <row r="24" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="121" t="s">
         <v>230</v>
       </c>
@@ -12501,7 +13079,7 @@
       </c>
       <c r="L24" s="107"/>
     </row>
-    <row r="25" spans="1:14" ht="43.2">
+    <row r="25" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="125" t="s">
         <v>82</v>
       </c>
@@ -12539,7 +13117,7 @@
       <c r="M25" s="129"/>
       <c r="N25" s="129"/>
     </row>
-    <row r="26" spans="1:14" ht="115.2">
+    <row r="26" spans="1:14" ht="128" x14ac:dyDescent="0.2">
       <c r="A26" s="121" t="s">
         <v>236</v>
       </c>
@@ -12575,7 +13153,7 @@
       </c>
       <c r="L26" s="107"/>
     </row>
-    <row r="27" spans="1:14" ht="43.2">
+    <row r="27" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="125" t="s">
         <v>243</v>
       </c>
@@ -12613,7 +13191,7 @@
       <c r="M27" s="129"/>
       <c r="N27" s="129"/>
     </row>
-    <row r="28" spans="1:14" ht="28.8">
+    <row r="28" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="121" t="s">
         <v>249</v>
       </c>
@@ -12649,7 +13227,7 @@
       </c>
       <c r="L28" s="107"/>
     </row>
-    <row r="29" spans="1:14" ht="43.2">
+    <row r="29" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="125" t="s">
         <v>96</v>
       </c>
@@ -12687,7 +13265,7 @@
       <c r="M29" s="129"/>
       <c r="N29" s="129"/>
     </row>
-    <row r="30" spans="1:14" ht="28.8">
+    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="121" t="s">
         <v>255</v>
       </c>
@@ -12723,7 +13301,7 @@
       </c>
       <c r="L30" s="107"/>
     </row>
-    <row r="31" spans="1:14" ht="28.8">
+    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="125" t="s">
         <v>261</v>
       </c>
@@ -12761,7 +13339,7 @@
       <c r="M31" s="129"/>
       <c r="N31" s="129"/>
     </row>
-    <row r="32" spans="1:14" ht="57.6">
+    <row r="32" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A32" s="121" t="s">
         <v>266</v>
       </c>
@@ -12797,7 +13375,7 @@
       </c>
       <c r="L32" s="107"/>
     </row>
-    <row r="33" spans="1:14" ht="57.6">
+    <row r="33" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A33" s="125" t="s">
         <v>272</v>
       </c>
@@ -12835,7 +13413,7 @@
       <c r="M33" s="129"/>
       <c r="N33" s="129"/>
     </row>
-    <row r="34" spans="1:14" ht="43.2">
+    <row r="34" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A34" s="121" t="s">
         <v>279</v>
       </c>
@@ -12871,7 +13449,7 @@
       </c>
       <c r="L34" s="107"/>
     </row>
-    <row r="35" spans="1:14" ht="115.2">
+    <row r="35" spans="1:14" ht="112" x14ac:dyDescent="0.2">
       <c r="A35" s="125" t="s">
         <v>101</v>
       </c>
@@ -12915,7 +13493,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="43.2">
+    <row r="36" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A36" s="121" t="s">
         <v>285</v>
       </c>
@@ -12951,7 +13529,7 @@
       </c>
       <c r="L36" s="107"/>
     </row>
-    <row r="37" spans="1:14" ht="228" customHeight="1">
+    <row r="37" spans="1:14" ht="228" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="125" t="s">
         <v>291</v>
       </c>
@@ -12993,7 +13571,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="57.6">
+    <row r="38" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A38" s="121" t="s">
         <v>297</v>
       </c>
@@ -13037,7 +13615,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="43.2">
+    <row r="39" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A39" s="125" t="s">
         <v>303</v>
       </c>
@@ -13079,7 +13657,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="28.8">
+    <row r="40" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="121" t="s">
         <v>107</v>
       </c>
@@ -13115,7 +13693,7 @@
       </c>
       <c r="L40" s="107"/>
     </row>
-    <row r="41" spans="1:14" ht="28.8">
+    <row r="41" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" s="125" t="s">
         <v>310</v>
       </c>
@@ -13159,7 +13737,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="72">
+    <row r="42" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A42" s="121" t="s">
         <v>315</v>
       </c>
@@ -13199,7 +13777,7 @@
       <c r="M42" s="107"/>
       <c r="N42" s="107"/>
     </row>
-    <row r="43" spans="1:14" ht="28.8">
+    <row r="43" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="125" t="s">
         <v>320</v>
       </c>
@@ -13239,7 +13817,7 @@
       <c r="M43" s="129"/>
       <c r="N43" s="129"/>
     </row>
-    <row r="44" spans="1:14" ht="57.6">
+    <row r="44" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A44" s="121" t="s">
         <v>325</v>
       </c>
@@ -13277,7 +13855,7 @@
       <c r="M44" s="107"/>
       <c r="N44" s="107"/>
     </row>
-    <row r="45" spans="1:14" ht="28.8">
+    <row r="45" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="125" t="s">
         <v>122</v>
       </c>
@@ -13321,7 +13899,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="57.6">
+    <row r="46" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A46" s="121" t="s">
         <v>331</v>
       </c>
@@ -13359,7 +13937,7 @@
       <c r="M46" s="107"/>
       <c r="N46" s="107"/>
     </row>
-    <row r="47" spans="1:14" ht="74.25" customHeight="1">
+    <row r="47" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="125" t="s">
         <v>336</v>
       </c>
@@ -13397,7 +13975,7 @@
       <c r="M47" s="129"/>
       <c r="N47" s="129"/>
     </row>
-    <row r="48" spans="1:14" ht="28.8">
+    <row r="48" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="121" t="s">
         <v>132</v>
       </c>
@@ -13435,7 +14013,7 @@
       <c r="M48" s="107"/>
       <c r="N48" s="107"/>
     </row>
-    <row r="49" spans="1:14" ht="57.6">
+    <row r="49" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A49" s="125" t="s">
         <v>341</v>
       </c>
@@ -13473,7 +14051,7 @@
       <c r="M49" s="129"/>
       <c r="N49" s="129"/>
     </row>
-    <row r="50" spans="1:14" ht="28.8">
+    <row r="50" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="121" t="s">
         <v>346</v>
       </c>
@@ -13511,7 +14089,7 @@
       <c r="M50" s="107"/>
       <c r="N50" s="107"/>
     </row>
-    <row r="51" spans="1:14" ht="28.8">
+    <row r="51" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="125" t="s">
         <v>350</v>
       </c>
@@ -13549,7 +14127,7 @@
       <c r="M51" s="129"/>
       <c r="N51" s="129"/>
     </row>
-    <row r="52" spans="1:14" ht="84.75" customHeight="1">
+    <row r="52" spans="1:14" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="121" t="s">
         <v>354</v>
       </c>
@@ -13583,7 +14161,7 @@
       <c r="M52" s="107"/>
       <c r="N52" s="107"/>
     </row>
-    <row r="53" spans="1:14" s="118" customFormat="1">
+    <row r="53" spans="1:14" s="118" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="145"/>
       <c r="B53" s="146"/>
       <c r="C53" s="145"/>
@@ -13603,67 +14181,67 @@
     <sortCondition ref="A2:A53"/>
   </sortState>
   <mergeCells count="11">
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
     <mergeCell ref="L14:L18"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="J14:J18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F14 F19:F53">
-    <cfRule type="cellIs" dxfId="171" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="8" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H14 H19:H53">
-    <cfRule type="cellIs" dxfId="170" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="191" priority="17" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="190" priority="18" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F14 F19:F53">
-    <cfRule type="cellIs" dxfId="168" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="188" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="187" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J14 J19:J53">
-    <cfRule type="containsText" dxfId="164" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="185" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="163" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="184" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="162" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="183" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="161" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13723,29 +14301,29 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:V57"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" style="178" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" style="178" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" style="178" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.44140625" style="175" customWidth="1"/>
-    <col min="5" max="5" width="65.88671875" style="178" customWidth="1"/>
-    <col min="6" max="6" width="18.5546875" style="136" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" style="136" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="182" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5546875" style="136" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="178" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5" style="175" customWidth="1"/>
+    <col min="5" max="5" width="65.83203125" style="178" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="136" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="136" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="182" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" style="136" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="136" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="156" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="40.44140625" style="136" customWidth="1"/>
-    <col min="13" max="13" width="39.109375" style="136" customWidth="1"/>
-    <col min="14" max="19" width="28.88671875" style="136" customWidth="1"/>
-    <col min="20" max="20" width="34.5546875" style="136" customWidth="1"/>
-    <col min="21" max="21" width="35.5546875" style="136" customWidth="1"/>
-    <col min="22" max="22" width="36.5546875" style="136" customWidth="1"/>
-    <col min="23" max="16384" width="8.88671875" style="136"/>
+    <col min="11" max="11" width="39.5" style="156" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="40.5" style="136" customWidth="1"/>
+    <col min="13" max="13" width="39.1640625" style="136" customWidth="1"/>
+    <col min="14" max="19" width="28.83203125" style="136" customWidth="1"/>
+    <col min="20" max="20" width="34.5" style="136" customWidth="1"/>
+    <col min="21" max="21" width="35.5" style="136" customWidth="1"/>
+    <col min="22" max="22" width="36.5" style="136" customWidth="1"/>
+    <col min="23" max="16384" width="8.83203125" style="136"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="201" customFormat="1" ht="86.4">
+    <row r="1" spans="1:22" s="201" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -13813,7 +14391,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="28.8">
+    <row r="2" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
         <v>369</v>
       </c>
@@ -13845,7 +14423,7 @@
       <c r="K2" s="161"/>
       <c r="L2" s="107"/>
     </row>
-    <row r="3" spans="1:22" ht="115.2">
+    <row r="3" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
         <v>372</v>
       </c>
@@ -13890,7 +14468,7 @@
       <c r="T3" s="129"/>
       <c r="U3" s="129"/>
     </row>
-    <row r="4" spans="1:22" ht="129.6">
+    <row r="4" spans="1:22" ht="112" x14ac:dyDescent="0.2">
       <c r="A4" s="64" t="s">
         <v>213</v>
       </c>
@@ -13926,7 +14504,7 @@
       </c>
       <c r="L4" s="107"/>
     </row>
-    <row r="5" spans="1:22" ht="43.2">
+    <row r="5" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="165" t="s">
         <v>381</v>
       </c>
@@ -13971,7 +14549,7 @@
       <c r="T5" s="129"/>
       <c r="U5" s="129"/>
     </row>
-    <row r="6" spans="1:22" ht="72">
+    <row r="6" spans="1:22" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" s="168" t="s">
         <v>386</v>
       </c>
@@ -14005,7 +14583,7 @@
       <c r="K6" s="161"/>
       <c r="L6" s="107"/>
     </row>
-    <row r="7" spans="1:22" ht="115.2">
+    <row r="7" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
         <v>390</v>
       </c>
@@ -14048,7 +14626,7 @@
       <c r="T7" s="129"/>
       <c r="U7" s="129"/>
     </row>
-    <row r="8" spans="1:22" ht="28.8">
+    <row r="8" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="64" t="s">
         <v>341</v>
       </c>
@@ -14084,7 +14662,7 @@
       </c>
       <c r="L8" s="107"/>
     </row>
-    <row r="9" spans="1:22" ht="43.2">
+    <row r="9" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="165" t="s">
         <v>397</v>
       </c>
@@ -14129,7 +14707,7 @@
       <c r="T9" s="129"/>
       <c r="U9" s="129"/>
     </row>
-    <row r="10" spans="1:22" ht="14.4">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="174"/>
       <c r="B10" s="175"/>
       <c r="C10" s="174"/>
@@ -14142,7 +14720,7 @@
       <c r="J10" s="156"/>
       <c r="K10" s="98"/>
     </row>
-    <row r="11" spans="1:22" ht="14.4">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="174"/>
       <c r="B11" s="175"/>
       <c r="D11" s="176"/>
@@ -14154,7 +14732,7 @@
       <c r="J11" s="156"/>
       <c r="K11" s="99"/>
     </row>
-    <row r="12" spans="1:22" ht="14.4">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="174"/>
       <c r="B12" s="175"/>
       <c r="C12" s="174"/>
@@ -14167,7 +14745,7 @@
       <c r="J12" s="156"/>
       <c r="K12" s="98"/>
     </row>
-    <row r="13" spans="1:22" ht="14.4">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" s="174"/>
       <c r="B13" s="175"/>
       <c r="C13" s="174"/>
@@ -14180,7 +14758,7 @@
       <c r="J13" s="156"/>
       <c r="K13" s="98"/>
     </row>
-    <row r="14" spans="1:22" ht="14.4">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="174"/>
       <c r="B14" s="175"/>
       <c r="C14" s="174"/>
@@ -14193,7 +14771,7 @@
       <c r="J14" s="156"/>
       <c r="K14" s="98"/>
     </row>
-    <row r="15" spans="1:22" ht="14.4">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="174"/>
       <c r="B15" s="175"/>
       <c r="C15" s="179"/>
@@ -14206,7 +14784,7 @@
       <c r="J15" s="156"/>
       <c r="K15" s="98"/>
     </row>
-    <row r="16" spans="1:22" ht="14.4">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="174"/>
       <c r="B16" s="175"/>
       <c r="C16" s="174"/>
@@ -14219,7 +14797,7 @@
       <c r="J16" s="156"/>
       <c r="K16" s="98"/>
     </row>
-    <row r="17" spans="1:11" ht="14.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="174"/>
       <c r="B17" s="175"/>
       <c r="D17" s="176"/>
@@ -14231,7 +14809,7 @@
       <c r="J17" s="156"/>
       <c r="K17" s="98"/>
     </row>
-    <row r="18" spans="1:11" ht="14.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="174"/>
       <c r="B18" s="175"/>
       <c r="C18" s="174"/>
@@ -14244,7 +14822,7 @@
       <c r="J18" s="156"/>
       <c r="K18" s="98"/>
     </row>
-    <row r="19" spans="1:11" ht="14.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="174"/>
       <c r="B19" s="175"/>
       <c r="C19" s="174"/>
@@ -14257,7 +14835,7 @@
       <c r="J19" s="156"/>
       <c r="K19" s="101"/>
     </row>
-    <row r="20" spans="1:11" ht="14.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="174"/>
       <c r="B20" s="175"/>
       <c r="C20" s="174"/>
@@ -14270,7 +14848,7 @@
       <c r="J20" s="156"/>
       <c r="K20" s="99"/>
     </row>
-    <row r="21" spans="1:11" ht="14.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="174"/>
       <c r="B21" s="175"/>
       <c r="C21" s="179"/>
@@ -14283,7 +14861,7 @@
       <c r="J21" s="156"/>
       <c r="K21" s="98"/>
     </row>
-    <row r="22" spans="1:11" ht="14.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="174"/>
       <c r="B22" s="175"/>
       <c r="C22" s="174"/>
@@ -14296,7 +14874,7 @@
       <c r="J22" s="156"/>
       <c r="K22" s="98"/>
     </row>
-    <row r="23" spans="1:11" ht="14.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="174"/>
       <c r="B23" s="175"/>
       <c r="D23" s="122"/>
@@ -14308,7 +14886,7 @@
       <c r="J23" s="156"/>
       <c r="K23" s="98"/>
     </row>
-    <row r="24" spans="1:11" ht="14.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="174"/>
       <c r="B24" s="175"/>
       <c r="C24" s="174"/>
@@ -14321,7 +14899,7 @@
       <c r="J24" s="156"/>
       <c r="K24" s="100"/>
     </row>
-    <row r="25" spans="1:11" ht="14.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="174"/>
       <c r="B25" s="175"/>
       <c r="C25" s="174"/>
@@ -14334,7 +14912,7 @@
       <c r="J25" s="156"/>
       <c r="K25" s="98"/>
     </row>
-    <row r="26" spans="1:11" ht="14.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="174"/>
       <c r="B26" s="175"/>
       <c r="C26" s="174"/>
@@ -14347,7 +14925,7 @@
       <c r="J26" s="156"/>
       <c r="K26" s="100"/>
     </row>
-    <row r="27" spans="1:11" ht="14.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="174"/>
       <c r="B27" s="175"/>
       <c r="C27" s="179"/>
@@ -14360,7 +14938,7 @@
       <c r="J27" s="156"/>
       <c r="K27" s="98"/>
     </row>
-    <row r="28" spans="1:11" ht="14.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="174"/>
       <c r="B28" s="175"/>
       <c r="C28" s="174"/>
@@ -14373,7 +14951,7 @@
       <c r="J28" s="156"/>
       <c r="K28" s="98"/>
     </row>
-    <row r="29" spans="1:11" ht="14.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="174"/>
       <c r="B29" s="175"/>
       <c r="D29" s="176"/>
@@ -14385,7 +14963,7 @@
       <c r="J29" s="156"/>
       <c r="K29" s="98"/>
     </row>
-    <row r="30" spans="1:11" ht="14.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="174"/>
       <c r="B30" s="175"/>
       <c r="C30" s="174"/>
@@ -14398,7 +14976,7 @@
       <c r="J30" s="156"/>
       <c r="K30" s="98"/>
     </row>
-    <row r="31" spans="1:11" ht="14.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="174"/>
       <c r="B31" s="175"/>
       <c r="C31" s="174"/>
@@ -14411,7 +14989,7 @@
       <c r="J31" s="156"/>
       <c r="K31" s="98"/>
     </row>
-    <row r="32" spans="1:11" ht="14.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="174"/>
       <c r="B32" s="175"/>
       <c r="C32" s="174"/>
@@ -14424,7 +15002,7 @@
       <c r="J32" s="156"/>
       <c r="K32" s="98"/>
     </row>
-    <row r="33" spans="1:11" ht="14.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="174"/>
       <c r="B33" s="175"/>
       <c r="C33" s="179"/>
@@ -14437,7 +15015,7 @@
       <c r="J33" s="156"/>
       <c r="K33" s="98"/>
     </row>
-    <row r="34" spans="1:11" ht="14.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="174"/>
       <c r="B34" s="175"/>
       <c r="C34" s="174"/>
@@ -14450,7 +15028,7 @@
       <c r="J34" s="156"/>
       <c r="K34" s="98"/>
     </row>
-    <row r="35" spans="1:11" ht="14.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="174"/>
       <c r="B35" s="175"/>
       <c r="D35" s="176"/>
@@ -14462,7 +15040,7 @@
       <c r="J35" s="156"/>
       <c r="K35" s="98"/>
     </row>
-    <row r="36" spans="1:11" ht="14.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="174"/>
       <c r="B36" s="175"/>
       <c r="C36" s="174"/>
@@ -14475,7 +15053,7 @@
       <c r="J36" s="156"/>
       <c r="K36" s="98"/>
     </row>
-    <row r="37" spans="1:11" ht="14.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="174"/>
       <c r="B37" s="175"/>
       <c r="C37" s="174"/>
@@ -14488,7 +15066,7 @@
       <c r="J37" s="156"/>
       <c r="K37" s="98"/>
     </row>
-    <row r="38" spans="1:11" ht="14.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="174"/>
       <c r="B38" s="175"/>
       <c r="C38" s="174"/>
@@ -14501,7 +15079,7 @@
       <c r="J38" s="156"/>
       <c r="K38" s="98"/>
     </row>
-    <row r="39" spans="1:11" ht="14.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="174"/>
       <c r="B39" s="175"/>
       <c r="C39" s="179"/>
@@ -14514,7 +15092,7 @@
       <c r="J39" s="156"/>
       <c r="K39" s="98"/>
     </row>
-    <row r="40" spans="1:11" ht="14.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="174"/>
       <c r="B40" s="175"/>
       <c r="C40" s="174"/>
@@ -14527,7 +15105,7 @@
       <c r="J40" s="156"/>
       <c r="K40" s="98"/>
     </row>
-    <row r="41" spans="1:11" ht="14.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="174"/>
       <c r="B41" s="175"/>
       <c r="C41" s="174"/>
@@ -14540,7 +15118,7 @@
       <c r="J41" s="156"/>
       <c r="K41" s="98"/>
     </row>
-    <row r="42" spans="1:11" ht="14.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="174"/>
       <c r="B42" s="175"/>
       <c r="C42" s="174"/>
@@ -14553,7 +15131,7 @@
       <c r="J42" s="156"/>
       <c r="K42" s="98"/>
     </row>
-    <row r="43" spans="1:11" ht="14.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="174"/>
       <c r="B43" s="175"/>
       <c r="C43" s="179"/>
@@ -14566,7 +15144,7 @@
       <c r="J43" s="156"/>
       <c r="K43" s="98"/>
     </row>
-    <row r="44" spans="1:11" ht="14.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="174"/>
       <c r="B44" s="175"/>
       <c r="C44" s="174"/>
@@ -14579,7 +15157,7 @@
       <c r="J44" s="156"/>
       <c r="K44" s="98"/>
     </row>
-    <row r="45" spans="1:11" ht="14.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="174"/>
       <c r="B45" s="175"/>
       <c r="D45" s="176"/>
@@ -14591,7 +15169,7 @@
       <c r="J45" s="156"/>
       <c r="K45" s="98"/>
     </row>
-    <row r="46" spans="1:11" ht="14.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="174"/>
       <c r="B46" s="175"/>
       <c r="C46" s="174"/>
@@ -14604,7 +15182,7 @@
       <c r="J46" s="156"/>
       <c r="K46" s="98"/>
     </row>
-    <row r="47" spans="1:11" ht="14.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="174"/>
       <c r="B47" s="175"/>
       <c r="C47" s="174"/>
@@ -14617,7 +15195,7 @@
       <c r="J47" s="156"/>
       <c r="K47" s="98"/>
     </row>
-    <row r="48" spans="1:11" ht="14.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="174"/>
       <c r="B48" s="175"/>
       <c r="C48" s="174"/>
@@ -14630,7 +15208,7 @@
       <c r="J48" s="156"/>
       <c r="K48" s="98"/>
     </row>
-    <row r="49" spans="1:11" ht="14.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="174"/>
       <c r="B49" s="175"/>
       <c r="C49" s="179"/>
@@ -14643,7 +15221,7 @@
       <c r="J49" s="156"/>
       <c r="K49" s="98"/>
     </row>
-    <row r="50" spans="1:11" ht="14.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="174"/>
       <c r="B50" s="175"/>
       <c r="C50" s="174"/>
@@ -14656,7 +15234,7 @@
       <c r="J50" s="156"/>
       <c r="K50" s="98"/>
     </row>
-    <row r="51" spans="1:11" ht="14.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="174"/>
       <c r="B51" s="175"/>
       <c r="C51" s="174"/>
@@ -14669,7 +15247,7 @@
       <c r="J51" s="156"/>
       <c r="K51" s="98"/>
     </row>
-    <row r="52" spans="1:11" ht="14.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="174"/>
       <c r="B52" s="175"/>
       <c r="C52" s="174"/>
@@ -14682,7 +15260,7 @@
       <c r="J52" s="156"/>
       <c r="K52" s="98"/>
     </row>
-    <row r="53" spans="1:11" ht="14.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="174"/>
       <c r="B53" s="175"/>
       <c r="D53" s="176"/>
@@ -14694,7 +15272,7 @@
       <c r="J53" s="156"/>
       <c r="K53" s="98"/>
     </row>
-    <row r="54" spans="1:11" ht="14.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="174"/>
       <c r="B54" s="175"/>
       <c r="C54" s="174"/>
@@ -14707,7 +15285,7 @@
       <c r="J54" s="156"/>
       <c r="K54" s="98"/>
     </row>
-    <row r="55" spans="1:11" ht="14.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="174"/>
       <c r="B55" s="175"/>
       <c r="C55" s="174"/>
@@ -14720,10 +15298,10 @@
       <c r="J55" s="156"/>
       <c r="K55" s="98"/>
     </row>
-    <row r="56" spans="1:11" ht="14.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K56" s="98"/>
     </row>
-    <row r="57" spans="1:11" ht="14.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K57" s="99"/>
     </row>
   </sheetData>
@@ -14732,40 +15310,40 @@
     <sortCondition ref="A2:A9"/>
   </sortState>
   <conditionalFormatting sqref="F2:F55">
-    <cfRule type="cellIs" dxfId="157" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="8" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H55">
-    <cfRule type="cellIs" dxfId="156" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="177" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="10" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F55">
-    <cfRule type="cellIs" dxfId="154" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J55">
-    <cfRule type="containsText" dxfId="150" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="171" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="149" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="170" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="148" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="169" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14805,28 +15383,28 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.44140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="53.44140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="54.44140625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="84" customWidth="1"/>
-    <col min="7" max="7" width="22.44140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" style="87" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="84" customWidth="1"/>
+    <col min="1" max="1" width="24.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="9" customWidth="1"/>
+    <col min="3" max="3" width="53.5" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="9" customWidth="1"/>
+    <col min="5" max="5" width="54.5" style="9" customWidth="1"/>
+    <col min="6" max="6" width="22.1640625" style="84" customWidth="1"/>
+    <col min="7" max="7" width="22.5" style="84" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="87" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="84" customWidth="1"/>
     <col min="10" max="10" width="16" style="84" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="39.5" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="33.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="31.109375" style="84" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="31.1640625" style="84" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="31.33203125" style="84" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.44140625" style="84" customWidth="1"/>
-    <col min="17" max="17" width="33.5546875" style="84" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="84"/>
+    <col min="16" max="16" width="34.5" style="84" customWidth="1"/>
+    <col min="17" max="17" width="33.5" style="84" customWidth="1"/>
+    <col min="18" max="16384" width="8.83203125" style="84"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="201" customFormat="1" ht="86.4">
+    <row r="1" spans="1:17" s="201" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -14879,7 +15457,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="64.349999999999994" customHeight="1">
+    <row r="2" spans="1:17" ht="64.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
         <v>406</v>
       </c>
@@ -14915,7 +15493,7 @@
       </c>
       <c r="L2" s="136"/>
     </row>
-    <row r="3" spans="1:17" ht="129.6">
+    <row r="3" spans="1:17" ht="128" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
         <v>411</v>
       </c>
@@ -14955,7 +15533,7 @@
       <c r="O3" s="61"/>
       <c r="P3" s="61"/>
     </row>
-    <row r="4" spans="1:17" ht="28.8">
+    <row r="4" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="64" t="s">
         <v>415</v>
       </c>
@@ -14991,7 +15569,7 @@
       </c>
       <c r="L4" s="136"/>
     </row>
-    <row r="5" spans="1:17" ht="14.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="8"/>
       <c r="C5" s="23"/>
@@ -15005,7 +15583,7 @@
       <c r="K5" s="84"/>
       <c r="L5" s="84"/>
     </row>
-    <row r="6" spans="1:17" ht="14.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="23"/>
       <c r="B6" s="8"/>
       <c r="C6" s="23"/>
@@ -15019,7 +15597,7 @@
       <c r="K6" s="84"/>
       <c r="L6" s="84"/>
     </row>
-    <row r="7" spans="1:17" ht="14.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="23"/>
       <c r="B7" s="8"/>
       <c r="C7" s="29"/>
@@ -15033,7 +15611,7 @@
       <c r="K7" s="84"/>
       <c r="L7" s="84"/>
     </row>
-    <row r="8" spans="1:17" ht="14.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
       <c r="B8" s="8"/>
       <c r="C8" s="23"/>
@@ -15047,7 +15625,7 @@
       <c r="K8" s="84"/>
       <c r="L8" s="84"/>
     </row>
-    <row r="9" spans="1:17" ht="14.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="23"/>
       <c r="B9" s="8"/>
       <c r="D9" s="23"/>
@@ -15060,7 +15638,7 @@
       <c r="K9" s="84"/>
       <c r="L9" s="84"/>
     </row>
-    <row r="10" spans="1:17" ht="14.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="23"/>
       <c r="B10" s="8"/>
       <c r="C10" s="23"/>
@@ -15074,7 +15652,7 @@
       <c r="K10" s="98"/>
       <c r="L10" s="98"/>
     </row>
-    <row r="11" spans="1:17" ht="14.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="23"/>
       <c r="B11" s="8"/>
       <c r="C11" s="23"/>
@@ -15088,7 +15666,7 @@
       <c r="K11" s="99"/>
       <c r="L11" s="99"/>
     </row>
-    <row r="12" spans="1:17" ht="14.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="23"/>
       <c r="B12" s="8"/>
       <c r="C12" s="23"/>
@@ -15102,7 +15680,7 @@
       <c r="K12" s="98"/>
       <c r="L12" s="98"/>
     </row>
-    <row r="13" spans="1:17" ht="14.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="23"/>
       <c r="B13" s="8"/>
       <c r="C13" s="29"/>
@@ -15116,7 +15694,7 @@
       <c r="K13" s="98"/>
       <c r="L13" s="98"/>
     </row>
-    <row r="14" spans="1:17" ht="14.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="23"/>
       <c r="B14" s="8"/>
       <c r="C14" s="23"/>
@@ -15130,7 +15708,7 @@
       <c r="K14" s="98"/>
       <c r="L14" s="98"/>
     </row>
-    <row r="15" spans="1:17" ht="14.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="23"/>
       <c r="B15" s="8"/>
       <c r="D15" s="23"/>
@@ -15143,7 +15721,7 @@
       <c r="K15" s="98"/>
       <c r="L15" s="98"/>
     </row>
-    <row r="16" spans="1:17" ht="14.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="23"/>
       <c r="B16" s="8"/>
       <c r="C16" s="23"/>
@@ -15157,7 +15735,7 @@
       <c r="K16" s="98"/>
       <c r="L16" s="98"/>
     </row>
-    <row r="17" spans="1:12" ht="14.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="23"/>
       <c r="B17" s="8"/>
       <c r="C17" s="23"/>
@@ -15171,7 +15749,7 @@
       <c r="K17" s="98"/>
       <c r="L17" s="98"/>
     </row>
-    <row r="18" spans="1:12" ht="14.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="23"/>
       <c r="B18" s="8"/>
       <c r="C18" s="23"/>
@@ -15185,7 +15763,7 @@
       <c r="K18" s="98"/>
       <c r="L18" s="98"/>
     </row>
-    <row r="19" spans="1:12" ht="14.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="23"/>
       <c r="B19" s="8"/>
       <c r="C19" s="29"/>
@@ -15199,7 +15777,7 @@
       <c r="K19" s="101"/>
       <c r="L19" s="101"/>
     </row>
-    <row r="20" spans="1:12" ht="14.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
       <c r="B20" s="8"/>
       <c r="C20" s="23"/>
@@ -15213,7 +15791,7 @@
       <c r="K20" s="99"/>
       <c r="L20" s="99"/>
     </row>
-    <row r="21" spans="1:12" ht="14.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="23"/>
       <c r="B21" s="8"/>
       <c r="D21" s="30"/>
@@ -15226,7 +15804,7 @@
       <c r="K21" s="98"/>
       <c r="L21" s="98"/>
     </row>
-    <row r="22" spans="1:12" ht="14.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="23"/>
       <c r="B22" s="8"/>
       <c r="C22" s="23"/>
@@ -15240,7 +15818,7 @@
       <c r="K22" s="98"/>
       <c r="L22" s="98"/>
     </row>
-    <row r="23" spans="1:12" ht="14.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="23"/>
       <c r="B23" s="8"/>
       <c r="C23" s="23"/>
@@ -15254,7 +15832,7 @@
       <c r="K23" s="98"/>
       <c r="L23" s="98"/>
     </row>
-    <row r="24" spans="1:12" ht="14.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="23"/>
       <c r="B24" s="8"/>
       <c r="C24" s="23"/>
@@ -15268,7 +15846,7 @@
       <c r="K24" s="100"/>
       <c r="L24" s="100"/>
     </row>
-    <row r="25" spans="1:12" ht="14.4">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="23"/>
       <c r="B25" s="8"/>
       <c r="C25" s="29"/>
@@ -15282,7 +15860,7 @@
       <c r="K25" s="98"/>
       <c r="L25" s="98"/>
     </row>
-    <row r="26" spans="1:12" ht="14.4">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="23"/>
       <c r="B26" s="8"/>
       <c r="C26" s="23"/>
@@ -15296,7 +15874,7 @@
       <c r="K26" s="100"/>
       <c r="L26" s="100"/>
     </row>
-    <row r="27" spans="1:12" ht="14.4">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="23"/>
       <c r="B27" s="8"/>
       <c r="D27" s="23"/>
@@ -15309,7 +15887,7 @@
       <c r="K27" s="98"/>
       <c r="L27" s="98"/>
     </row>
-    <row r="28" spans="1:12" ht="14.4">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="23"/>
       <c r="B28" s="8"/>
       <c r="C28" s="23"/>
@@ -15323,7 +15901,7 @@
       <c r="K28" s="98"/>
       <c r="L28" s="98"/>
     </row>
-    <row r="29" spans="1:12" ht="14.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="23"/>
       <c r="B29" s="8"/>
       <c r="C29" s="23"/>
@@ -15337,7 +15915,7 @@
       <c r="K29" s="98"/>
       <c r="L29" s="98"/>
     </row>
-    <row r="30" spans="1:12" ht="14.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="23"/>
       <c r="B30" s="8"/>
       <c r="C30" s="23"/>
@@ -15351,7 +15929,7 @@
       <c r="K30" s="98"/>
       <c r="L30" s="98"/>
     </row>
-    <row r="31" spans="1:12" ht="14.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="23"/>
       <c r="B31" s="8"/>
       <c r="C31" s="29"/>
@@ -15365,7 +15943,7 @@
       <c r="K31" s="98"/>
       <c r="L31" s="98"/>
     </row>
-    <row r="32" spans="1:12" ht="14.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="23"/>
       <c r="B32" s="8"/>
       <c r="C32" s="23"/>
@@ -15379,7 +15957,7 @@
       <c r="K32" s="98"/>
       <c r="L32" s="98"/>
     </row>
-    <row r="33" spans="1:12" ht="14.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="23"/>
       <c r="B33" s="8"/>
       <c r="D33" s="23"/>
@@ -15392,7 +15970,7 @@
       <c r="K33" s="102"/>
       <c r="L33" s="102"/>
     </row>
-    <row r="34" spans="1:12" ht="14.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="23"/>
       <c r="B34" s="8"/>
       <c r="C34" s="23"/>
@@ -15406,7 +15984,7 @@
       <c r="K34" s="98"/>
       <c r="L34" s="98"/>
     </row>
-    <row r="35" spans="1:12" ht="14.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="23"/>
       <c r="B35" s="8"/>
       <c r="C35" s="23"/>
@@ -15420,7 +15998,7 @@
       <c r="K35" s="98"/>
       <c r="L35" s="98"/>
     </row>
-    <row r="36" spans="1:12" ht="14.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="23"/>
       <c r="B36" s="8"/>
       <c r="C36" s="23"/>
@@ -15434,7 +16012,7 @@
       <c r="K36" s="98"/>
       <c r="L36" s="98"/>
     </row>
-    <row r="37" spans="1:12" ht="14.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="23"/>
       <c r="B37" s="8"/>
       <c r="C37" s="29"/>
@@ -15448,7 +16026,7 @@
       <c r="K37" s="98"/>
       <c r="L37" s="98"/>
     </row>
-    <row r="38" spans="1:12" ht="14.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="23"/>
       <c r="B38" s="8"/>
       <c r="C38" s="23"/>
@@ -15462,7 +16040,7 @@
       <c r="K38" s="98"/>
       <c r="L38" s="98"/>
     </row>
-    <row r="39" spans="1:12" ht="14.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="23"/>
       <c r="B39" s="8"/>
       <c r="C39" s="23"/>
@@ -15476,7 +16054,7 @@
       <c r="K39" s="98"/>
       <c r="L39" s="98"/>
     </row>
-    <row r="40" spans="1:12" ht="14.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="23"/>
       <c r="B40" s="8"/>
       <c r="C40" s="23"/>
@@ -15490,7 +16068,7 @@
       <c r="K40" s="98"/>
       <c r="L40" s="98"/>
     </row>
-    <row r="41" spans="1:12" ht="14.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="23"/>
       <c r="B41" s="8"/>
       <c r="C41" s="29"/>
@@ -15504,7 +16082,7 @@
       <c r="K41" s="98"/>
       <c r="L41" s="98"/>
     </row>
-    <row r="42" spans="1:12" ht="14.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="23"/>
       <c r="B42" s="8"/>
       <c r="C42" s="23"/>
@@ -15518,7 +16096,7 @@
       <c r="K42" s="98"/>
       <c r="L42" s="98"/>
     </row>
-    <row r="43" spans="1:12" ht="14.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="23"/>
       <c r="B43" s="8"/>
       <c r="D43" s="23"/>
@@ -15531,7 +16109,7 @@
       <c r="K43" s="98"/>
       <c r="L43" s="98"/>
     </row>
-    <row r="44" spans="1:12" ht="14.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="23"/>
       <c r="B44" s="8"/>
       <c r="C44" s="23"/>
@@ -15545,7 +16123,7 @@
       <c r="K44" s="98"/>
       <c r="L44" s="98"/>
     </row>
-    <row r="45" spans="1:12" ht="14.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="23"/>
       <c r="B45" s="8"/>
       <c r="C45" s="23"/>
@@ -15559,7 +16137,7 @@
       <c r="K45" s="98"/>
       <c r="L45" s="98"/>
     </row>
-    <row r="46" spans="1:12" ht="14.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="23"/>
       <c r="B46" s="8"/>
       <c r="C46" s="23"/>
@@ -15573,7 +16151,7 @@
       <c r="K46" s="98"/>
       <c r="L46" s="98"/>
     </row>
-    <row r="47" spans="1:12" ht="14.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="23"/>
       <c r="B47" s="8"/>
       <c r="C47" s="29"/>
@@ -15587,7 +16165,7 @@
       <c r="K47" s="98"/>
       <c r="L47" s="98"/>
     </row>
-    <row r="48" spans="1:12" ht="14.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="23"/>
       <c r="B48" s="8"/>
       <c r="C48" s="23"/>
@@ -15601,7 +16179,7 @@
       <c r="K48" s="98"/>
       <c r="L48" s="98"/>
     </row>
-    <row r="49" spans="1:12" ht="14.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="23"/>
       <c r="B49" s="8"/>
       <c r="C49" s="23"/>
@@ -15615,7 +16193,7 @@
       <c r="K49" s="98"/>
       <c r="L49" s="98"/>
     </row>
-    <row r="50" spans="1:12" ht="14.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="23"/>
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
@@ -15629,7 +16207,7 @@
       <c r="K50" s="98"/>
       <c r="L50" s="98"/>
     </row>
-    <row r="51" spans="1:12" ht="14.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="23"/>
       <c r="B51" s="8"/>
       <c r="D51" s="23"/>
@@ -15642,7 +16220,7 @@
       <c r="K51" s="98"/>
       <c r="L51" s="98"/>
     </row>
-    <row r="52" spans="1:12" ht="14.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="23"/>
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
@@ -15656,7 +16234,7 @@
       <c r="K52" s="98"/>
       <c r="L52" s="98"/>
     </row>
-    <row r="53" spans="1:12" ht="14.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="23"/>
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
@@ -15670,19 +16248,19 @@
       <c r="K53" s="98"/>
       <c r="L53" s="98"/>
     </row>
-    <row r="54" spans="1:12" ht="14.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K54" s="98"/>
       <c r="L54" s="98"/>
     </row>
-    <row r="55" spans="1:12" ht="14.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K55" s="98"/>
       <c r="L55" s="98"/>
     </row>
-    <row r="56" spans="1:12" ht="14.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K56" s="98"/>
       <c r="L56" s="98"/>
     </row>
-    <row r="57" spans="1:12" ht="14.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K57" s="99"/>
       <c r="L57" s="99"/>
     </row>
@@ -15691,40 +16269,40 @@
     <sortCondition ref="A2:A4"/>
   </sortState>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="147" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="8" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="146" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="167" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="10" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="144" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="140" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="161" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="139" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="160" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="138" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="159" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15757,25 +16335,25 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="42.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="57.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="42.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="8" customWidth="1"/>
+    <col min="5" max="5" width="57.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="28.109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="28.88671875" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="8" max="8" width="11.83203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.5" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="28.1640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="28.83203125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="201" customFormat="1" ht="57.6">
+    <row r="1" spans="1:13" s="201" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -15816,7 +16394,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8">
+    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="121" t="s">
         <v>423</v>
       </c>
@@ -15857,7 +16435,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="72">
+    <row r="3" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="125" t="s">
         <v>429</v>
       </c>
@@ -15894,7 +16472,7 @@
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
     </row>
-    <row r="4" spans="1:13" ht="28.8">
+    <row r="4" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="131" t="s">
         <v>13</v>
       </c>
@@ -15931,7 +16509,7 @@
       <c r="L4" s="107"/>
       <c r="M4" s="107"/>
     </row>
-    <row r="5" spans="1:13" ht="43.2">
+    <row r="5" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="125" t="s">
         <v>435</v>
       </c>
@@ -15968,7 +16546,7 @@
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
     </row>
-    <row r="6" spans="1:13" ht="57.6">
+    <row r="6" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="121" t="s">
         <v>441</v>
       </c>
@@ -16009,7 +16587,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="43.2">
+    <row r="7" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
         <v>448</v>
       </c>
@@ -16046,7 +16624,7 @@
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2">
+    <row r="8" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="121" t="s">
         <v>54</v>
       </c>
@@ -16083,7 +16661,7 @@
       <c r="L8" s="107"/>
       <c r="M8" s="107"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="125" t="s">
         <v>190</v>
       </c>
@@ -16120,7 +16698,7 @@
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
     </row>
-    <row r="10" spans="1:13" ht="57.6">
+    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="121" t="s">
         <v>459</v>
       </c>
@@ -16157,7 +16735,7 @@
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
-    <row r="11" spans="1:13" ht="72">
+    <row r="11" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A11" s="125" t="s">
         <v>464</v>
       </c>
@@ -16194,7 +16772,7 @@
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
     </row>
-    <row r="12" spans="1:13" ht="99" customHeight="1">
+    <row r="12" spans="1:13" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="121" t="s">
         <v>82</v>
       </c>
@@ -16231,7 +16809,7 @@
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
-    <row r="13" spans="1:13" ht="72">
+    <row r="13" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A13" s="125" t="s">
         <v>473</v>
       </c>
@@ -16268,7 +16846,7 @@
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
-    <row r="14" spans="1:13" ht="72">
+    <row r="14" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A14" s="121" t="s">
         <v>477</v>
       </c>
@@ -16305,7 +16883,7 @@
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
-    <row r="15" spans="1:13" ht="100.8">
+    <row r="15" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A15" s="125" t="s">
         <v>480</v>
       </c>
@@ -16342,7 +16920,7 @@
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="121" t="s">
         <v>96</v>
       </c>
@@ -16377,7 +16955,7 @@
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
-    <row r="17" spans="1:13" ht="57.6">
+    <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="125" t="s">
         <v>486</v>
       </c>
@@ -16414,7 +16992,7 @@
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="121" t="s">
         <v>107</v>
       </c>
@@ -16451,7 +17029,7 @@
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
     </row>
-    <row r="19" spans="1:13" ht="28.8">
+    <row r="19" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="125" t="s">
         <v>310</v>
       </c>
@@ -16488,7 +17066,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="129.6">
+    <row r="20" spans="1:13" ht="144" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>111</v>
       </c>
@@ -16525,7 +17103,7 @@
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
-    <row r="21" spans="1:13" ht="43.2">
+    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="125" t="s">
         <v>325</v>
       </c>
@@ -16562,7 +17140,7 @@
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
     </row>
-    <row r="22" spans="1:13" ht="57.6">
+    <row r="22" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A22" s="121" t="s">
         <v>331</v>
       </c>
@@ -16597,7 +17175,7 @@
       <c r="L22" s="107"/>
       <c r="M22" s="107"/>
     </row>
-    <row r="23" spans="1:13" ht="28.8">
+    <row r="23" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="125" t="s">
         <v>132</v>
       </c>
@@ -16634,7 +17212,7 @@
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="23"/>
       <c r="B24" s="8"/>
       <c r="C24" s="23"/>
@@ -16647,7 +17225,7 @@
       <c r="L24" s="32"/>
       <c r="M24" s="32"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="23"/>
       <c r="B25" s="8"/>
       <c r="C25" s="29"/>
@@ -16660,7 +17238,7 @@
       <c r="L25" s="32"/>
       <c r="M25" s="32"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="23"/>
       <c r="B26" s="8"/>
       <c r="C26" s="23"/>
@@ -16671,7 +17249,7 @@
       <c r="H26" s="24"/>
       <c r="K26" s="100"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="23"/>
       <c r="B27" s="8"/>
       <c r="D27" s="25"/>
@@ -16681,7 +17259,7 @@
       <c r="H27" s="24"/>
       <c r="K27" s="98"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="23"/>
       <c r="B28" s="8"/>
       <c r="C28" s="23"/>
@@ -16692,7 +17270,7 @@
       <c r="H28" s="24"/>
       <c r="K28" s="98"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="23"/>
       <c r="B29" s="8"/>
       <c r="C29" s="23"/>
@@ -16702,7 +17280,7 @@
       <c r="H29" s="24"/>
       <c r="K29" s="98"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="23"/>
       <c r="B30" s="8"/>
       <c r="C30" s="23"/>
@@ -16713,7 +17291,7 @@
       <c r="H30" s="24"/>
       <c r="K30" s="98"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="23"/>
       <c r="B31" s="8"/>
       <c r="C31" s="29"/>
@@ -16724,7 +17302,7 @@
       <c r="H31" s="24"/>
       <c r="K31" s="98"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="23"/>
       <c r="B32" s="8"/>
       <c r="C32" s="23"/>
@@ -16735,7 +17313,7 @@
       <c r="H32" s="24"/>
       <c r="K32" s="98"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="23"/>
       <c r="B33" s="8"/>
       <c r="D33" s="25"/>
@@ -16745,7 +17323,7 @@
       <c r="H33" s="24"/>
       <c r="K33" s="102"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="23"/>
       <c r="B34" s="8"/>
       <c r="C34" s="23"/>
@@ -16756,7 +17334,7 @@
       <c r="H34" s="24"/>
       <c r="K34" s="98"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="23"/>
       <c r="B35" s="8"/>
       <c r="C35" s="23"/>
@@ -16766,7 +17344,7 @@
       <c r="H35" s="24"/>
       <c r="K35" s="98"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="23"/>
       <c r="B36" s="8"/>
       <c r="C36" s="23"/>
@@ -16777,7 +17355,7 @@
       <c r="H36" s="24"/>
       <c r="K36" s="98"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="23"/>
       <c r="B37" s="8"/>
       <c r="C37" s="29"/>
@@ -16788,7 +17366,7 @@
       <c r="H37" s="24"/>
       <c r="K37" s="98"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="23"/>
       <c r="B38" s="8"/>
       <c r="C38" s="23"/>
@@ -16799,7 +17377,7 @@
       <c r="H38" s="24"/>
       <c r="K38" s="98"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="23"/>
       <c r="B39" s="8"/>
       <c r="C39" s="23"/>
@@ -16809,7 +17387,7 @@
       <c r="H39" s="24"/>
       <c r="K39" s="98"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="23"/>
       <c r="B40" s="8"/>
       <c r="C40" s="23"/>
@@ -16820,7 +17398,7 @@
       <c r="H40" s="24"/>
       <c r="K40" s="98"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="23"/>
       <c r="B41" s="8"/>
       <c r="C41" s="29"/>
@@ -16831,7 +17409,7 @@
       <c r="H41" s="24"/>
       <c r="K41" s="98"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="23"/>
       <c r="B42" s="8"/>
       <c r="C42" s="23"/>
@@ -16842,7 +17420,7 @@
       <c r="H42" s="24"/>
       <c r="K42" s="98"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="23"/>
       <c r="B43" s="8"/>
       <c r="D43" s="25"/>
@@ -16852,7 +17430,7 @@
       <c r="H43" s="24"/>
       <c r="K43" s="98"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="23"/>
       <c r="B44" s="8"/>
       <c r="C44" s="23"/>
@@ -16863,7 +17441,7 @@
       <c r="H44" s="24"/>
       <c r="K44" s="98"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="23"/>
       <c r="B45" s="8"/>
       <c r="C45" s="23"/>
@@ -16873,7 +17451,7 @@
       <c r="H45" s="24"/>
       <c r="K45" s="98"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="23"/>
       <c r="B46" s="8"/>
       <c r="C46" s="23"/>
@@ -16884,7 +17462,7 @@
       <c r="H46" s="24"/>
       <c r="K46" s="98"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="23"/>
       <c r="B47" s="8"/>
       <c r="C47" s="29"/>
@@ -16895,7 +17473,7 @@
       <c r="H47" s="24"/>
       <c r="K47" s="98"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="23"/>
       <c r="B48" s="8"/>
       <c r="C48" s="23"/>
@@ -16905,7 +17483,7 @@
       <c r="H48" s="24"/>
       <c r="K48" s="98"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="23"/>
       <c r="B49" s="8"/>
       <c r="C49" s="23"/>
@@ -16915,7 +17493,7 @@
       <c r="H49" s="24"/>
       <c r="K49" s="98"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="23"/>
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
@@ -16926,7 +17504,7 @@
       <c r="H50" s="24"/>
       <c r="K50" s="98"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="23"/>
       <c r="B51" s="8"/>
       <c r="D51" s="25"/>
@@ -16936,7 +17514,7 @@
       <c r="H51" s="24"/>
       <c r="K51" s="98"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="23"/>
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
@@ -16947,7 +17525,7 @@
       <c r="H52" s="24"/>
       <c r="K52" s="98"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="23"/>
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
@@ -16958,16 +17536,16 @@
       <c r="H53" s="24"/>
       <c r="K53" s="98"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K54" s="98"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K55" s="98"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K56" s="98"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K57" s="99"/>
     </row>
   </sheetData>
@@ -16976,40 +17554,40 @@
     <sortCondition ref="A2:A23"/>
   </sortState>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="137" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="136" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="157" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="134" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="130" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="151" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="150" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="128" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="149" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17058,25 +17636,25 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" style="41" customWidth="1"/>
+    <col min="1" max="1" width="22.5" style="41" customWidth="1"/>
+    <col min="2" max="2" width="43.5" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" style="41" customWidth="1"/>
     <col min="4" max="4" width="24" style="34" customWidth="1"/>
-    <col min="5" max="5" width="76.5546875" style="41" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="32" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" style="32" customWidth="1"/>
-    <col min="11" max="11" width="39.44140625" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="76.5" style="41" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="32" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5" style="32" customWidth="1"/>
+    <col min="11" max="11" width="39.5" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="24.6640625" style="32" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="32"/>
+    <col min="13" max="16384" width="9.1640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="199" customFormat="1" ht="43.2">
+    <row r="1" spans="1:12" s="199" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -17114,7 +17692,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="191" t="s">
         <v>13</v>
       </c>
@@ -17150,7 +17728,7 @@
       </c>
       <c r="L2" s="129"/>
     </row>
-    <row r="3" spans="1:12" ht="57.6">
+    <row r="3" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="121" t="s">
         <v>31</v>
       </c>
@@ -17188,7 +17766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="125" t="s">
         <v>54</v>
       </c>
@@ -17224,7 +17802,7 @@
       </c>
       <c r="L4" s="129"/>
     </row>
-    <row r="5" spans="1:12" ht="43.2">
+    <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="121" t="s">
         <v>195</v>
       </c>
@@ -17258,107 +17836,107 @@
       <c r="K5" s="105"/>
       <c r="L5" s="107"/>
     </row>
-    <row r="6" spans="1:12" ht="28.8">
-      <c r="A6" s="245" t="s">
+    <row r="6" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="246" t="s">
+      <c r="B6" s="244" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="245" t="s">
+      <c r="C6" s="243" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="247" t="s">
+      <c r="E6" s="245" t="s">
         <v>201</v>
       </c>
-      <c r="F6" s="244" t="s">
+      <c r="F6" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="244" t="s">
+      <c r="G6" s="242" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="244" t="s">
+      <c r="H6" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="242" t="s">
+      <c r="I6" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="235" t="s">
+      <c r="J6" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="243" t="s">
+      <c r="K6" s="247" t="s">
         <v>510</v>
       </c>
-      <c r="L6" s="242"/>
-    </row>
-    <row r="7" spans="1:12" ht="28.8">
-      <c r="A7" s="245"/>
-      <c r="B7" s="246"/>
-      <c r="C7" s="245"/>
+      <c r="L6" s="246"/>
+    </row>
+    <row r="7" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="243"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="247"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="242"/>
-    </row>
-    <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="246"/>
+    </row>
+    <row r="8" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="243"/>
+      <c r="B8" s="244"/>
+      <c r="C8" s="243"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="247"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="243"/>
-      <c r="L8" s="242"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="245"/>
-      <c r="B9" s="246"/>
-      <c r="C9" s="245"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="247"/>
+      <c r="L8" s="246"/>
+    </row>
+    <row r="9" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="243"/>
+      <c r="B9" s="244"/>
+      <c r="C9" s="243"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="247"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="243"/>
-      <c r="L9" s="242"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="245"/>
-      <c r="B10" s="246"/>
-      <c r="C10" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="246"/>
+    </row>
+    <row r="10" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="243"/>
+      <c r="B10" s="244"/>
+      <c r="C10" s="243"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="247"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="243"/>
-      <c r="L10" s="242"/>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="E10" s="245"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="247"/>
+      <c r="L10" s="246"/>
+    </row>
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="121" t="s">
         <v>96</v>
       </c>
@@ -17394,7 +17972,7 @@
       </c>
       <c r="L11" s="107"/>
     </row>
-    <row r="12" spans="1:12" ht="28.8">
+    <row r="12" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="125" t="s">
         <v>101</v>
       </c>
@@ -17432,7 +18010,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="28.8">
+    <row r="13" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="121" t="s">
         <v>107</v>
       </c>
@@ -17468,27 +18046,27 @@
       </c>
       <c r="L13" s="107"/>
     </row>
-    <row r="14" spans="1:12" ht="48.9" customHeight="1">
+    <row r="14" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="125" t="s">
-        <v>122</v>
+        <v>675</v>
       </c>
       <c r="B14" s="125" t="s">
-        <v>123</v>
+        <v>677</v>
       </c>
       <c r="C14" s="125" t="s">
-        <v>124</v>
+        <v>676</v>
       </c>
       <c r="D14" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>516</v>
-      </c>
-      <c r="F14" s="124" t="s">
+        <v>678</v>
+      </c>
+      <c r="F14" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="128" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="H14" s="193" t="s">
         <v>19</v>
@@ -17496,258 +18074,298 @@
       <c r="I14" s="193" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="107" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="98" t="s">
-        <v>517</v>
-      </c>
-      <c r="L14" s="129" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="J14" s="107"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="129"/>
+    </row>
+    <row r="15" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="121" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="121" t="s">
-        <v>133</v>
+        <v>122</v>
+      </c>
+      <c r="B15" s="132" t="s">
+        <v>123</v>
       </c>
       <c r="C15" s="121" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D15" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="121" t="s">
-        <v>518</v>
+      <c r="E15" s="132" t="s">
+        <v>516</v>
       </c>
       <c r="F15" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="124" t="s">
-        <v>58</v>
+        <v>17</v>
+      </c>
+      <c r="G15" s="128" t="s">
+        <v>125</v>
       </c>
       <c r="H15" s="124" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="I15" s="124" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J15" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
+        <v>517</v>
+      </c>
+      <c r="L15" s="107" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="125" t="s">
         <v>132</v>
       </c>
-      <c r="L15" s="107"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="K16" s="32"/>
-    </row>
-    <row r="17" spans="11:11">
+      <c r="B16" s="125" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="125" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="126" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="126" t="s">
+        <v>518</v>
+      </c>
+      <c r="F16" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="124" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="193" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="193" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="107" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="98" t="s">
+        <v>132</v>
+      </c>
+      <c r="L16" s="129"/>
+    </row>
+    <row r="17" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K17" s="32"/>
     </row>
-    <row r="18" spans="11:11">
+    <row r="18" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K18" s="32"/>
     </row>
-    <row r="19" spans="11:11">
+    <row r="19" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K19" s="32"/>
     </row>
-    <row r="20" spans="11:11">
+    <row r="20" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K20" s="32"/>
     </row>
-    <row r="21" spans="11:11">
+    <row r="21" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K21" s="32"/>
     </row>
-    <row r="22" spans="11:11">
-      <c r="K22" s="100"/>
-    </row>
-    <row r="23" spans="11:11">
-      <c r="K23" s="98"/>
-    </row>
-    <row r="24" spans="11:11">
-      <c r="K24" s="100"/>
-    </row>
-    <row r="25" spans="11:11">
-      <c r="K25" s="98"/>
-    </row>
-    <row r="26" spans="11:11">
+    <row r="22" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="32"/>
+    </row>
+    <row r="23" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="100"/>
+    </row>
+    <row r="24" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="98"/>
+    </row>
+    <row r="25" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="100"/>
+    </row>
+    <row r="26" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K26" s="98"/>
     </row>
-    <row r="27" spans="11:11">
+    <row r="27" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K27" s="98"/>
     </row>
-    <row r="28" spans="11:11">
+    <row r="28" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K28" s="98"/>
     </row>
-    <row r="29" spans="11:11">
+    <row r="29" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K29" s="98"/>
     </row>
-    <row r="30" spans="11:11">
+    <row r="30" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K30" s="98"/>
     </row>
-    <row r="31" spans="11:11">
-      <c r="K31" s="102"/>
-    </row>
-    <row r="32" spans="11:11">
-      <c r="K32" s="98"/>
-    </row>
-    <row r="33" spans="11:11">
+    <row r="31" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="98"/>
+    </row>
+    <row r="32" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="102"/>
+    </row>
+    <row r="33" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K33" s="98"/>
     </row>
-    <row r="34" spans="11:11">
+    <row r="34" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K34" s="98"/>
     </row>
-    <row r="35" spans="11:11">
+    <row r="35" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K35" s="98"/>
     </row>
-    <row r="36" spans="11:11">
+    <row r="36" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K36" s="98"/>
     </row>
-    <row r="37" spans="11:11">
+    <row r="37" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K37" s="98"/>
     </row>
-    <row r="38" spans="11:11">
+    <row r="38" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K38" s="98"/>
     </row>
-    <row r="39" spans="11:11">
+    <row r="39" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K39" s="98"/>
     </row>
-    <row r="40" spans="11:11">
+    <row r="40" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K40" s="98"/>
     </row>
-    <row r="41" spans="11:11">
+    <row r="41" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K41" s="98"/>
     </row>
-    <row r="42" spans="11:11">
+    <row r="42" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K42" s="98"/>
     </row>
-    <row r="43" spans="11:11">
+    <row r="43" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K43" s="98"/>
     </row>
-    <row r="44" spans="11:11">
+    <row r="44" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K44" s="98"/>
     </row>
-    <row r="45" spans="11:11">
+    <row r="45" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K45" s="98"/>
     </row>
-    <row r="46" spans="11:11">
+    <row r="46" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K46" s="98"/>
     </row>
-    <row r="47" spans="11:11">
+    <row r="47" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K47" s="98"/>
     </row>
-    <row r="48" spans="11:11">
+    <row r="48" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K48" s="98"/>
     </row>
-    <row r="49" spans="11:11">
+    <row r="49" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K49" s="98"/>
     </row>
-    <row r="50" spans="11:11">
+    <row r="50" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K50" s="98"/>
     </row>
-    <row r="51" spans="11:11">
+    <row r="51" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K51" s="98"/>
     </row>
-    <row r="52" spans="11:11">
+    <row r="52" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K52" s="98"/>
     </row>
-    <row r="53" spans="11:11">
+    <row r="53" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K53" s="98"/>
     </row>
-    <row r="54" spans="11:11">
+    <row r="54" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K54" s="98"/>
     </row>
-    <row r="55" spans="11:11">
-      <c r="K55" s="99"/>
+    <row r="55" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K55" s="98"/>
+    </row>
+    <row r="56" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K56" s="99"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L15" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
+  <autoFilter ref="A1:L16" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
   <mergeCells count="11">
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="J6:J10"/>
   </mergeCells>
-  <conditionalFormatting sqref="F2:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
+  <conditionalFormatting sqref="F2:F6 F11:F16">
+    <cfRule type="cellIs" dxfId="148" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H6 H11 G12:I12">
-    <cfRule type="cellIs" dxfId="126" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="147" priority="10" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="11" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:I1 F1:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="124" priority="10" operator="equal">
+  <conditionalFormatting sqref="H1:I1 F1:F6 F11:F16">
+    <cfRule type="cellIs" dxfId="145" priority="12" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="13" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="14" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="15" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="containsText" dxfId="120" priority="1" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="141" priority="3" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="119" priority="2" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="140" priority="4" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="118" priority="3" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="139" priority="5" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J15">
-    <cfRule type="containsText" dxfId="117" priority="4" operator="containsText" text="Health and NL">
+  <conditionalFormatting sqref="J11:J16">
+    <cfRule type="containsText" dxfId="138" priority="6" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="116" priority="5" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="137" priority="7" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="115" priority="6" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="136" priority="8" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="greaterThan">
+      <formula>"reviewd"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6 H2:H4 H11:H12 H15" xr:uid="{5D775F4F-080B-374B-8A00-A929984DE8EA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6 H2:H4 H11:H12 H16" xr:uid="{5D775F4F-080B-374B-8A00-A929984DE8EA}">
       <formula1>"0..n, 0..1, 1, 1..n"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{53D8202B-692B-B648-8083-8AD470955AEE}">
       <formula1>"Mandatory, Recommended, Optional, Conditional"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6 F11:F15" xr:uid="{B6D62F25-23AE-9D43-BEDB-A452691FAB34}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6 F11:F16" xr:uid="{B6D62F25-23AE-9D43-BEDB-A452691FAB34}">
       <formula1>"Mandatory, Recommended, Optional, Conditional, Not added"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J16:J1048576" xr:uid="{710F50F8-8184-3643-9F3C-6943B596CC47}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J17:J1048576" xr:uid="{710F50F8-8184-3643-9F3C-6943B596CC47}">
       <formula1>"DCAT-AP v3, HealthDCAT-AP, DCAT-AP NL, HRI v1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I6 I11:I1048576" xr:uid="{C90BD7D7-2AEA-F848-AF4B-6B7A98B1BC5C}">
       <formula1>"Identical to v1, Adapted from v1, new"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J15" xr:uid="{B11D4639-FC60-DF48-B32D-9DB24D194931}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J11:J14 J2:J6" xr:uid="{81B7949E-3EB9-ED45-A064-CB5457A9EB69}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J16" xr:uid="{B11D4639-FC60-DF48-B32D-9DB24D194931}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J11:J15 J2:J6" xr:uid="{81B7949E-3EB9-ED45-A064-CB5457A9EB69}">
       <formula1>"DCAT-AP v3, HealthDCAT-AP, DCAT-AP NL, HRI v1, Health and NL"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use the Agent tab and create column for DatasetSeries (Publisher)" sqref="A12" xr:uid="{8BB03C66-ADAD-40F6-95E3-6941C2983400}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Please use PeriodOfTime tab to fill out values" sqref="A14" xr:uid="{9E68EE80-E28C-452E-91AE-AEEE80572101}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Please use PeriodOfTime tab to fill out values" sqref="A15" xr:uid="{9E68EE80-E28C-452E-91AE-AEEE80572101}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{C0660312-7187-8E42-AA68-40C0FC7895B1}"/>
@@ -17768,23 +18386,23 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="33.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" style="112" customWidth="1"/>
-    <col min="5" max="5" width="67.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.44140625" customWidth="1"/>
-    <col min="11" max="11" width="33.44140625" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="25.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.5" style="19" customWidth="1"/>
+    <col min="2" max="2" width="33.5" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" style="19" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" style="112" customWidth="1"/>
+    <col min="5" max="5" width="67.5" style="19" customWidth="1"/>
+    <col min="6" max="6" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" customWidth="1"/>
+    <col min="8" max="8" width="16.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="33.5" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="202" customFormat="1" ht="43.2">
+    <row r="1" spans="1:12" s="202" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -17822,7 +18440,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="92.4">
+    <row r="2" spans="1:12" ht="84" x14ac:dyDescent="0.2">
       <c r="A2" s="131" t="s">
         <v>150</v>
       </c>
@@ -17858,7 +18476,7 @@
       </c>
       <c r="L2" s="186"/>
     </row>
-    <row r="3" spans="1:12" ht="28.8">
+    <row r="3" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="125" t="s">
         <v>13</v>
       </c>
@@ -17890,7 +18508,7 @@
       <c r="K3" s="106"/>
       <c r="L3" s="129"/>
     </row>
-    <row r="4" spans="1:12" ht="92.25" customHeight="1">
+    <row r="4" spans="1:12" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="121" t="s">
         <v>522</v>
       </c>
@@ -17924,7 +18542,7 @@
       <c r="K4" s="107"/>
       <c r="L4" s="107"/>
     </row>
-    <row r="5" spans="1:12" ht="57.6">
+    <row r="5" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="191" t="s">
         <v>31</v>
       </c>
@@ -17960,7 +18578,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="158.4">
+    <row r="6" spans="1:12" ht="160" x14ac:dyDescent="0.2">
       <c r="A6" s="121" t="s">
         <v>40</v>
       </c>
@@ -17996,7 +18614,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="28.8">
+    <row r="7" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
         <v>111</v>
       </c>
@@ -18028,7 +18646,7 @@
       <c r="K7" s="107"/>
       <c r="L7" s="129"/>
     </row>
-    <row r="8" spans="1:12" ht="39.6">
+    <row r="8" spans="1:12" ht="42" x14ac:dyDescent="0.2">
       <c r="A8" s="131" t="s">
         <v>54</v>
       </c>
@@ -18064,7 +18682,7 @@
       </c>
       <c r="L8" s="107"/>
     </row>
-    <row r="9" spans="1:12" ht="43.2">
+    <row r="9" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="125" t="s">
         <v>526</v>
       </c>
@@ -18100,7 +18718,7 @@
       </c>
       <c r="L9" s="129"/>
     </row>
-    <row r="10" spans="1:12" ht="43.2">
+    <row r="10" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="121" t="s">
         <v>531</v>
       </c>
@@ -18136,7 +18754,7 @@
       </c>
       <c r="L10" s="107"/>
     </row>
-    <row r="11" spans="1:12" ht="43.2">
+    <row r="11" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="125" t="s">
         <v>464</v>
       </c>
@@ -18168,7 +18786,7 @@
       <c r="K11" s="107"/>
       <c r="L11" s="129"/>
     </row>
-    <row r="12" spans="1:12" ht="28.8">
+    <row r="12" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="121" t="s">
         <v>536</v>
       </c>
@@ -18200,7 +18818,7 @@
       <c r="K12" s="106"/>
       <c r="L12" s="107"/>
     </row>
-    <row r="13" spans="1:12" ht="57.6">
+    <row r="13" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="191" t="s">
         <v>213</v>
       </c>
@@ -18234,7 +18852,7 @@
       <c r="K13" s="106"/>
       <c r="L13" s="129"/>
     </row>
-    <row r="14" spans="1:12" ht="28.8">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="121" t="s">
         <v>230</v>
       </c>
@@ -18266,7 +18884,7 @@
       <c r="K14" s="106"/>
       <c r="L14" s="107"/>
     </row>
-    <row r="15" spans="1:12" ht="57.6">
+    <row r="15" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="125" t="s">
         <v>540</v>
       </c>
@@ -18300,7 +18918,7 @@
       <c r="K15" s="106"/>
       <c r="L15" s="129"/>
     </row>
-    <row r="16" spans="1:12" ht="43.2">
+    <row r="16" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="121" t="s">
         <v>82</v>
       </c>
@@ -18334,7 +18952,7 @@
       <c r="K16" s="106"/>
       <c r="L16" s="107"/>
     </row>
-    <row r="17" spans="1:12" ht="57.6">
+    <row r="17" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="125" t="s">
         <v>89</v>
       </c>
@@ -18370,7 +18988,7 @@
       </c>
       <c r="L17" s="129"/>
     </row>
-    <row r="18" spans="1:12" ht="57.6">
+    <row r="18" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="121" t="s">
         <v>96</v>
       </c>
@@ -18404,7 +19022,7 @@
       <c r="K18" s="106"/>
       <c r="L18" s="107"/>
     </row>
-    <row r="19" spans="1:12" ht="28.8">
+    <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="125" t="s">
         <v>266</v>
       </c>
@@ -18438,7 +19056,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="43.2">
+    <row r="20" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>101</v>
       </c>
@@ -18474,7 +19092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="57.6">
+    <row r="21" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="125" t="s">
         <v>550</v>
       </c>
@@ -18512,7 +19130,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="43.2">
+    <row r="22" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="121" t="s">
         <v>336</v>
       </c>
@@ -18546,7 +19164,7 @@
       <c r="K22" s="106"/>
       <c r="L22" s="107"/>
     </row>
-    <row r="23" spans="1:12" ht="28.8">
+    <row r="23" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="125" t="s">
         <v>132</v>
       </c>
@@ -18582,7 +19200,7 @@
       </c>
       <c r="L23" s="195"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="23"/>
       <c r="B24" s="8"/>
       <c r="C24" s="23"/>
@@ -18595,7 +19213,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="100"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="23"/>
       <c r="B25" s="8"/>
       <c r="C25" s="29"/>
@@ -18608,7 +19226,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="98"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="23"/>
       <c r="B26" s="8"/>
       <c r="C26" s="23"/>
@@ -18621,7 +19239,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="100"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="23"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
@@ -18634,7 +19252,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="98"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="23"/>
       <c r="B28" s="8"/>
       <c r="C28" s="23"/>
@@ -18647,7 +19265,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="98"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="23"/>
       <c r="B29" s="8"/>
       <c r="C29" s="23"/>
@@ -18660,7 +19278,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="98"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="23"/>
       <c r="B30" s="8"/>
       <c r="C30" s="23"/>
@@ -18673,7 +19291,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="98"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="23"/>
       <c r="B31" s="8"/>
       <c r="C31" s="29"/>
@@ -18686,7 +19304,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="98"/>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="23"/>
       <c r="B32" s="8"/>
       <c r="C32" s="23"/>
@@ -18699,7 +19317,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="98"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="23"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9"/>
@@ -18712,7 +19330,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="102"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="23"/>
       <c r="B34" s="8"/>
       <c r="C34" s="23"/>
@@ -18725,7 +19343,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="98"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="23"/>
       <c r="B35" s="8"/>
       <c r="C35" s="23"/>
@@ -18738,7 +19356,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="98"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="23"/>
       <c r="B36" s="8"/>
       <c r="C36" s="23"/>
@@ -18751,7 +19369,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="98"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="23"/>
       <c r="B37" s="8"/>
       <c r="C37" s="29"/>
@@ -18764,7 +19382,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="98"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="23"/>
       <c r="B38" s="8"/>
       <c r="C38" s="23"/>
@@ -18777,7 +19395,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="98"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="23"/>
       <c r="B39" s="8"/>
       <c r="C39" s="23"/>
@@ -18790,7 +19408,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="98"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="23"/>
       <c r="B40" s="8"/>
       <c r="C40" s="23"/>
@@ -18803,7 +19421,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="98"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="23"/>
       <c r="B41" s="8"/>
       <c r="C41" s="29"/>
@@ -18816,7 +19434,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="98"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="23"/>
       <c r="B42" s="8"/>
       <c r="C42" s="23"/>
@@ -18829,7 +19447,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="98"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="23"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
@@ -18842,7 +19460,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="98"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="23"/>
       <c r="B44" s="8"/>
       <c r="C44" s="23"/>
@@ -18855,7 +19473,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="98"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="23"/>
       <c r="B45" s="8"/>
       <c r="C45" s="23"/>
@@ -18868,7 +19486,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="98"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="23"/>
       <c r="B46" s="8"/>
       <c r="C46" s="23"/>
@@ -18881,7 +19499,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="98"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="23"/>
       <c r="B47" s="8"/>
       <c r="C47" s="29"/>
@@ -18894,7 +19512,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="98"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="23"/>
       <c r="B48" s="8"/>
       <c r="C48" s="23"/>
@@ -18907,7 +19525,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="98"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="23"/>
       <c r="B49" s="8"/>
       <c r="C49" s="23"/>
@@ -18920,7 +19538,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="98"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="23"/>
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
@@ -18933,7 +19551,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="98"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="23"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
@@ -18946,7 +19564,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="98"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="23"/>
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
@@ -18959,7 +19577,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="98"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="23"/>
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
@@ -18972,16 +19590,16 @@
       <c r="J53" s="2"/>
       <c r="K53" s="98"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K54" s="98"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K55" s="98"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K56" s="98"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K57" s="99"/>
     </row>
   </sheetData>
@@ -18990,40 +19608,40 @@
     <sortCondition ref="A2:A23"/>
   </sortState>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="114" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="8" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="113" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="10" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="111" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="107" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="128" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="106" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="127" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="126" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19070,6 +19688,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Status xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">Draft</Status>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -19312,18 +19942,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Status xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">Draft</Status>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
   <ds:schemaRefs>
@@ -19333,6 +19951,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
+    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19349,15 +19978,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
-    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anakonrad/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424B36F4-CD4D-ED4C-B2CE-D33BD863D11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616AA07E-76D5-7B4D-A220-EE7A7862A61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="680" windowWidth="30240" windowHeight="17380" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17380" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="692">
   <si>
     <t>Property label</t>
   </si>
@@ -1841,30 +1841,6 @@
   </si>
   <si>
     <t>fill in in 'Periof of Time' tab</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A statement that concerns all rights not addressed in fields License or Access rights. In case of not open data (as specified in the dct:licence property), further agreements regarding data reuse (eg. Data Transfer Agreement, DTA,) should be stated in this property.
-The rights statement should be a free-text statement placed at an web-accessible location such that the value of this property is the IRI pointing to that statement.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Display"/>
-      </rPr>
-      <t xml:space="preserve">Current status: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Display"/>
-      </rPr>
-      <t>This recommendation on how to state data transfer/reuse conditions will be pilotted in 2025.</t>
-    </r>
   </si>
   <si>
     <t>resource:rights</t>
@@ -2765,12 +2741,38 @@
   <si>
     <t>This property allows free text description of the rights.</t>
   </si>
+  <si>
+    <t>dct:RightsStatement</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A statement that concerns all rights not addressed in fields license or access rights. In case of not open data (as specified in the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+      </rPr>
+      <t>dct:licence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Display"/>
+      </rPr>
+      <t xml:space="preserve"> property), further agreements regarding data reuse (e.g., Data Transfer Agreement, DTA) should be stated in this property. 
+The rights statement can be a document placed at a web-accessible location, or a free-text statement. See RightsStatement class for further information.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="56" x14ac:knownFonts="1">
+  <fonts count="57" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3127,6 +3129,12 @@
       <color rgb="FF000000"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
     </font>
   </fonts>
   <fills count="14">
@@ -7801,33 +7809,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>558</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>559</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>560</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>561</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="196" t="s">
+        <v>562</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>563</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="76" t="s">
         <v>564</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>565</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7836,7 +7844,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7851,13 +7859,13 @@
     </row>
     <row r="3" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>568</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="77" t="s">
         <v>569</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>570</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7996,36 +8004,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>570</v>
+      </c>
+      <c r="M1" s="220" t="s">
         <v>571</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="N1" s="226" t="s">
         <v>572</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="O1" s="230" t="s">
         <v>573</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="P1" s="227" t="s">
         <v>574</v>
       </c>
-      <c r="P1" s="227" t="s">
+      <c r="Q1" s="231" t="s">
         <v>575</v>
       </c>
-      <c r="Q1" s="231" t="s">
+      <c r="R1" s="233" t="s">
         <v>576</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
+        <v>577</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>578</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="76" t="s">
         <v>579</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>580</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -8053,13 +8061,13 @@
     </row>
     <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>581</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>582</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>583</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8721,33 +8729,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>583</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>584</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>585</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>586</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
+        <v>587</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>588</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>589</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>590</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8777,19 +8785,19 @@
     </row>
     <row r="3" spans="1:15" ht="144" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>592</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>593</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="D3" s="234" t="s">
         <v>594</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="E3" s="50" t="s">
         <v>595</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>596</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -8915,33 +8923,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>596</v>
+      </c>
+      <c r="M1" s="229" t="s">
         <v>597</v>
       </c>
-      <c r="M1" s="229" t="s">
+      <c r="N1" s="228" t="s">
         <v>598</v>
       </c>
-      <c r="N1" s="228" t="s">
+      <c r="O1" s="233" t="s">
         <v>599</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="160" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
+        <v>600</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>593</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>601</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>593</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>594</v>
-      </c>
-      <c r="D2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>602</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>603</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
@@ -8962,19 +8970,19 @@
     </row>
     <row r="3" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>604</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>605</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>606</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
@@ -9099,33 +9107,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>678</v>
+      </c>
+      <c r="M1" s="229" t="s">
+        <v>688</v>
+      </c>
+      <c r="N1" s="228" t="s">
         <v>679</v>
       </c>
-      <c r="M1" s="229" t="s">
-        <v>689</v>
-      </c>
-      <c r="N1" s="228" t="s">
+      <c r="O1" s="233" t="s">
         <v>680</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="288" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D2" s="59" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F2" s="51" t="s">
         <v>17</v>
@@ -9144,19 +9152,19 @@
     </row>
     <row r="3" spans="1:15" ht="192" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -9314,33 +9322,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>607</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>608</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>609</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>610</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
+        <v>611</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>612</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>613</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>614</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -9361,19 +9369,19 @@
     </row>
     <row r="3" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>615</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>616</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>617</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>618</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -9477,7 +9485,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -9500,13 +9508,13 @@
     </row>
     <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="63" t="s">
+        <v>620</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>621</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="C2" s="44" t="s">
         <v>622</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>623</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -9514,7 +9522,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -9528,13 +9536,13 @@
     </row>
     <row r="3" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>625</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>626</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>627</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -9542,10 +9550,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="H3" s="48" t="s">
         <v>628</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>629</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -9556,13 +9564,13 @@
     </row>
     <row r="4" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="63" t="s">
+        <v>629</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>630</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="C4" s="44" t="s">
         <v>631</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>632</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -9570,10 +9578,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="H4" s="65" t="s">
         <v>633</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>634</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9584,26 +9592,26 @@
     </row>
     <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="67" t="s">
+        <v>634</v>
+      </c>
+      <c r="B5" s="50" t="s">
         <v>635</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>636</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>637</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
+        <v>638</v>
+      </c>
+      <c r="H5" s="48" t="s">
         <v>639</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>640</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9614,13 +9622,13 @@
     </row>
     <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="63" t="s">
+        <v>640</v>
+      </c>
+      <c r="B6" s="73" t="s">
         <v>641</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="C6" s="44" t="s">
         <v>642</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>643</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9631,7 +9639,7 @@
         <v>99</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9642,13 +9650,13 @@
     </row>
     <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="67" t="s">
+        <v>643</v>
+      </c>
+      <c r="B7" s="50" t="s">
         <v>644</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>645</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>646</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9670,23 +9678,23 @@
     </row>
     <row r="8" spans="1:10" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
+        <v>646</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>647</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="C8" s="44" t="s">
         <v>648</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>649</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9700,13 +9708,13 @@
     </row>
     <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="67" t="s">
+        <v>651</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>652</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>653</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>654</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9714,7 +9722,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9728,23 +9736,23 @@
     </row>
     <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="63" t="s">
+        <v>655</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>656</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="44" t="s">
         <v>657</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>658</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -10209,36 +10217,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>659</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>660</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="233" t="s">
         <v>661</v>
-      </c>
-      <c r="N1" s="233" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
+        <v>662</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>663</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>664</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="78" t="s">
         <v>665</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="E2" s="197" t="s">
         <v>666</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>667</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -10252,13 +10260,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49" t="s">
+        <v>668</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>669</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="48" t="s">
         <v>670</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>671</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -10268,7 +10276,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -12312,8 +12320,8 @@
       <c r="F2" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="124" t="s">
-        <v>115</v>
+      <c r="G2" s="128" t="s">
+        <v>690</v>
       </c>
       <c r="H2" s="124">
         <v>1</v>
@@ -14437,7 +14445,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
@@ -15507,7 +15515,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
@@ -17066,7 +17074,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="144" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>111</v>
       </c>
@@ -17080,13 +17088,13 @@
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>495</v>
+        <v>691</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="124" t="s">
-        <v>115</v>
+      <c r="G20" s="128" t="s">
+        <v>690</v>
       </c>
       <c r="H20" s="133">
         <v>1</v>
@@ -17098,7 +17106,7 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
@@ -17114,10 +17122,10 @@
         <v>327</v>
       </c>
       <c r="D21" s="154" t="s">
+        <v>496</v>
+      </c>
+      <c r="E21" s="81" t="s">
         <v>497</v>
-      </c>
-      <c r="E21" s="81" t="s">
-        <v>498</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -17135,7 +17143,7 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
@@ -17154,7 +17162,7 @@
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
@@ -17189,7 +17197,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -17207,7 +17215,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17689,7 +17697,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -17706,7 +17714,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17724,7 +17732,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17760,7 +17768,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17780,7 +17788,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17798,7 +17806,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L4" s="129"/>
     </row>
@@ -17816,7 +17824,7 @@
         <v>198</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
@@ -17868,7 +17876,7 @@
         <v>66</v>
       </c>
       <c r="K6" s="247" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L6" s="246"/>
     </row>
@@ -17950,7 +17958,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -17968,7 +17976,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L11" s="107"/>
     </row>
@@ -17986,7 +17994,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -18004,7 +18012,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -18024,7 +18032,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
@@ -18042,25 +18050,25 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L13" s="107"/>
     </row>
     <row r="14" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="125" t="s">
+        <v>674</v>
+      </c>
+      <c r="B14" s="125" t="s">
+        <v>676</v>
+      </c>
+      <c r="C14" s="125" t="s">
         <v>675</v>
-      </c>
-      <c r="B14" s="125" t="s">
-        <v>677</v>
-      </c>
-      <c r="C14" s="125" t="s">
-        <v>676</v>
       </c>
       <c r="D14" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F14" s="127" t="s">
         <v>17</v>
@@ -18092,7 +18100,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="132" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18110,7 +18118,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L15" s="107" t="s">
         <v>314</v>
@@ -18130,7 +18138,7 @@
         <v>16</v>
       </c>
       <c r="E16" s="126" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>35</v>
@@ -18437,7 +18445,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="84" x14ac:dyDescent="0.2">
@@ -18454,7 +18462,7 @@
         <v>153</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
@@ -18472,7 +18480,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -18510,7 +18518,7 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="121" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>177</v>
@@ -18522,7 +18530,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -18660,7 +18668,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18678,25 +18686,25 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="125" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" s="74" t="s">
         <v>526</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="C9" s="125" t="s">
         <v>527</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>528</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
@@ -18714,25 +18722,25 @@
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="121" t="s">
+        <v>530</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>531</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="121" t="s">
         <v>532</v>
-      </c>
-      <c r="C10" s="121" t="s">
-        <v>533</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
@@ -18750,7 +18758,7 @@
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L10" s="107"/>
     </row>
@@ -18788,13 +18796,13 @@
     </row>
     <row r="12" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="121" t="s">
+        <v>535</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>536</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>537</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>538</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18832,7 +18840,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18886,19 +18894,19 @@
     </row>
     <row r="15" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="125" t="s">
+        <v>539</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>540</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>541</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>542</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18932,7 +18940,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18966,7 +18974,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
@@ -18984,7 +18992,7 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L17" s="129"/>
     </row>
@@ -19002,7 +19010,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -19053,7 +19061,7 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="48" x14ac:dyDescent="0.2">
@@ -19070,7 +19078,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -19094,19 +19102,19 @@
     </row>
     <row r="21" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="125" t="s">
+        <v>549</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>550</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>551</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>552</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -19124,10 +19132,10 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
+        <v>553</v>
+      </c>
+      <c r="L21" s="192" t="s">
         <v>554</v>
-      </c>
-      <c r="L21" s="192" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="48" x14ac:dyDescent="0.2">
@@ -19144,7 +19152,7 @@
         <v>338</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
@@ -19178,7 +19186,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -19196,7 +19204,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L23" s="195"/>
     </row>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E62AF80-5461-4F05-88C6-9AD4988BAB39}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8958F1D5-0A21-4FE0-BA8C-AACF2C87639E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-17388" windowWidth="30936" windowHeight="16776" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -370,9 +370,6 @@
   </si>
   <si>
     <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
-  </si>
-  <si>
-    <t>The licence under which the catalogue (with resource description) is made available. In the description of distributions and data services the licences of that resources are taken up.</t>
   </si>
   <si>
     <t>dct:LicenseDocument (IRI)</t>
@@ -2617,6 +2614,10 @@
 This protects their privacy and enables contact about the resource even after the individual has left the institution.
 The email address has to be provided starting with mailto: prefix.
 For example: mailto:info@example.com</t>
+  </si>
+  <si>
+    <t>The licence under which the catalogue (with resource description) is made available.
+The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
   </si>
 </sst>
 </file>
@@ -3764,9 +3765,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3778,10 +3776,25 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3789,18 +3802,6 @@
     </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7437,33 +7438,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>558</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>559</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>560</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>561</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="72">
       <c r="A2" s="196" t="s">
+        <v>562</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>563</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="76" t="s">
         <v>564</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>565</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7472,7 +7473,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7487,13 +7488,13 @@
     </row>
     <row r="3" spans="1:15" ht="28.8">
       <c r="A3" s="68" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>568</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="77" t="s">
         <v>569</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>570</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7632,36 +7633,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>570</v>
+      </c>
+      <c r="M1" s="220" t="s">
         <v>571</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="N1" s="226" t="s">
         <v>572</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="O1" s="230" t="s">
         <v>573</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="P1" s="227" t="s">
         <v>574</v>
       </c>
-      <c r="P1" s="227" t="s">
+      <c r="Q1" s="231" t="s">
         <v>575</v>
       </c>
-      <c r="Q1" s="231" t="s">
+      <c r="R1" s="233" t="s">
         <v>576</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="58" t="s">
+        <v>577</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>578</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="76" t="s">
         <v>579</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>580</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -7671,7 +7672,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>81</v>
@@ -7689,13 +7690,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>581</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>582</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>583</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -7705,7 +7706,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8357,33 +8358,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>583</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>584</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>585</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>586</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2">
       <c r="A2" s="84" t="s">
+        <v>587</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>588</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>589</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>590</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8413,25 +8414,25 @@
     </row>
     <row r="3" spans="1:15" ht="129.6">
       <c r="A3" s="48" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>592</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>593</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="D3" s="234" t="s">
         <v>594</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="E3" s="50" t="s">
         <v>595</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>596</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8551,39 +8552,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>596</v>
+      </c>
+      <c r="M1" s="229" t="s">
         <v>597</v>
       </c>
-      <c r="M1" s="229" t="s">
+      <c r="N1" s="228" t="s">
         <v>598</v>
       </c>
-      <c r="N1" s="228" t="s">
+      <c r="O1" s="233" t="s">
         <v>599</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="158.4">
       <c r="A2" s="84" t="s">
+        <v>600</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>593</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>601</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>593</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>594</v>
-      </c>
-      <c r="D2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>602</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>603</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="115" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>52</v>
@@ -8598,25 +8599,25 @@
     </row>
     <row r="3" spans="1:15" ht="43.2">
       <c r="A3" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>604</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>605</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>606</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>52</v>
@@ -8736,39 +8737,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>607</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>608</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>609</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>610</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="100.8">
       <c r="A2" s="84" t="s">
+        <v>611</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>612</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>613</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>614</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>81</v>
@@ -8783,25 +8784,25 @@
     </row>
     <row r="3" spans="1:15" ht="57.6">
       <c r="A3" s="48" t="s">
+        <v>615</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>616</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>617</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>618</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8899,7 +8900,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -8922,13 +8923,13 @@
     </row>
     <row r="2" spans="1:10" ht="28.8">
       <c r="A2" s="63" t="s">
+        <v>620</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>621</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="C2" s="44" t="s">
         <v>622</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>623</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -8936,7 +8937,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -8950,13 +8951,13 @@
     </row>
     <row r="3" spans="1:10" ht="43.2">
       <c r="A3" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>625</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>626</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>627</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8964,10 +8965,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="H3" s="48" t="s">
         <v>628</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>629</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -8978,13 +8979,13 @@
     </row>
     <row r="4" spans="1:10" ht="43.2">
       <c r="A4" s="63" t="s">
+        <v>629</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>630</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="C4" s="44" t="s">
         <v>631</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>632</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -8992,10 +8993,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="H4" s="65" t="s">
         <v>633</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>634</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9006,26 +9007,26 @@
     </row>
     <row r="5" spans="1:10" ht="43.2">
       <c r="A5" s="67" t="s">
+        <v>634</v>
+      </c>
+      <c r="B5" s="50" t="s">
         <v>635</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>636</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>637</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
+        <v>638</v>
+      </c>
+      <c r="H5" s="48" t="s">
         <v>639</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>640</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9036,13 +9037,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8">
       <c r="A6" s="63" t="s">
+        <v>640</v>
+      </c>
+      <c r="B6" s="73" t="s">
         <v>641</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="C6" s="44" t="s">
         <v>642</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>643</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9050,10 +9051,10 @@
       <c r="E6" s="53"/>
       <c r="F6" s="64"/>
       <c r="G6" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9064,13 +9065,13 @@
     </row>
     <row r="7" spans="1:10" ht="28.8">
       <c r="A7" s="67" t="s">
+        <v>643</v>
+      </c>
+      <c r="B7" s="50" t="s">
         <v>644</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>645</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>646</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9078,7 +9079,7 @@
       <c r="E7" s="54"/>
       <c r="F7" s="68"/>
       <c r="G7" s="67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="48">
         <v>1</v>
@@ -9092,23 +9093,23 @@
     </row>
     <row r="8" spans="1:10" ht="86.4">
       <c r="A8" s="63" t="s">
+        <v>646</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>647</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="C8" s="44" t="s">
         <v>648</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>649</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9122,13 +9123,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.8">
       <c r="A9" s="67" t="s">
+        <v>651</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>652</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>653</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>654</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9136,7 +9137,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9150,23 +9151,23 @@
     </row>
     <row r="10" spans="1:10" ht="28.8">
       <c r="A10" s="63" t="s">
+        <v>655</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>656</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="44" t="s">
         <v>657</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>658</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -9631,36 +9632,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>659</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>660</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="233" t="s">
         <v>661</v>
-      </c>
-      <c r="N1" s="233" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="72">
       <c r="A2" s="44" t="s">
+        <v>662</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>663</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>664</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="78" t="s">
         <v>665</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="E2" s="197" t="s">
         <v>666</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>667</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -9674,13 +9675,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1">
       <c r="A3" s="49" t="s">
+        <v>668</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>669</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="48" t="s">
         <v>670</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>671</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -9690,7 +9691,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -10604,107 +10605,107 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="237" t="s">
+      <c r="A8" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="C8" s="236" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="239" t="s">
+      <c r="E8" s="238" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="236" t="s">
+      <c r="F8" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="236" t="s">
+      <c r="G8" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="236" t="s">
+      <c r="H8" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="235" t="s">
+      <c r="I8" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="235" t="s">
+      <c r="J8" s="239" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="237"/>
-      <c r="B9" s="238"/>
-      <c r="C9" s="237"/>
+      <c r="A9" s="236"/>
+      <c r="B9" s="237"/>
+      <c r="C9" s="236"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="237"/>
-      <c r="B10" s="238"/>
-      <c r="C10" s="237"/>
+      <c r="A10" s="236"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="236"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="239"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="237"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="237"/>
+      <c r="A11" s="236"/>
+      <c r="B11" s="237"/>
+      <c r="C11" s="236"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="239"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
+      <c r="E11" s="238"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="235"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="237"/>
-      <c r="B12" s="238"/>
-      <c r="C12" s="237"/>
+      <c r="A12" s="236"/>
+      <c r="B12" s="237"/>
+      <c r="C12" s="236"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="239"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="239"/>
+      <c r="J12" s="239"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="235"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
     </row>
     <row r="13" spans="1:13" ht="43.2">
       <c r="A13" s="125" t="s">
@@ -10815,7 +10816,7 @@
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
     </row>
-    <row r="16" spans="1:13" ht="43.2">
+    <row r="16" spans="1:13" ht="85.2" customHeight="1">
       <c r="A16" s="121" t="s">
         <v>89</v>
       </c>
@@ -10829,13 +10830,13 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>93</v>
+        <v>674</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="124" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H16" s="124" t="s">
         <v>81</v>
@@ -10847,20 +10848,20 @@
         <v>29</v>
       </c>
       <c r="K16" s="155" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="C17" s="125" t="s">
         <v>97</v>
-      </c>
-      <c r="C17" s="125" t="s">
-        <v>98</v>
       </c>
       <c r="D17" s="126" t="s">
         <v>16</v>
@@ -10870,7 +10871,7 @@
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -10882,26 +10883,26 @@
         <v>29</v>
       </c>
       <c r="K17" s="155" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
     </row>
     <row r="18" spans="1:13" ht="43.2">
       <c r="A18" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="141" t="s">
         <v>102</v>
-      </c>
-      <c r="C18" s="141" t="s">
-        <v>103</v>
       </c>
       <c r="D18" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>35</v>
@@ -10913,13 +10914,13 @@
         <v>1</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K18" s="155" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L18" s="107" t="s">
         <v>46</v>
@@ -10930,13 +10931,13 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="C19" s="125" t="s">
         <v>108</v>
-      </c>
-      <c r="C19" s="125" t="s">
-        <v>109</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
@@ -10946,7 +10947,7 @@
         <v>17</v>
       </c>
       <c r="G19" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>81</v>
@@ -10958,32 +10959,32 @@
         <v>29</v>
       </c>
       <c r="K19" s="207" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L19" s="129"/>
       <c r="M19" s="129"/>
     </row>
     <row r="20" spans="1:13" ht="43.2">
       <c r="A20" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>112</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>113</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="124" t="s">
         <v>81</v>
@@ -11000,25 +11001,25 @@
     </row>
     <row r="21" spans="1:13" ht="72">
       <c r="A21" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>117</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>118</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="127" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H21" s="127" t="s">
         <v>19</v>
@@ -11031,19 +11032,19 @@
       </c>
       <c r="K21" s="130"/>
       <c r="L21" s="134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>123</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>124</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
@@ -11053,7 +11054,7 @@
         <v>17</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>19</v>
@@ -11065,32 +11066,32 @@
         <v>29</v>
       </c>
       <c r="K22" s="106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L22" s="107"/>
       <c r="M22" s="107"/>
     </row>
     <row r="23" spans="1:13" ht="57.6">
       <c r="A23" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="134" t="s">
         <v>128</v>
-      </c>
-      <c r="C23" s="134" t="s">
-        <v>129</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H23" s="127" t="s">
         <v>19</v>
@@ -11107,19 +11108,19 @@
     </row>
     <row r="24" spans="1:13" ht="28.8">
       <c r="A24" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="C24" s="121" t="s">
         <v>133</v>
-      </c>
-      <c r="C24" s="121" t="s">
-        <v>134</v>
       </c>
       <c r="D24" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="211" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>35</v>
@@ -11137,7 +11138,7 @@
         <v>29</v>
       </c>
       <c r="K24" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L24" s="107"/>
       <c r="M24" s="107"/>
@@ -11293,7 +11294,7 @@
       <c r="G38" s="36"/>
       <c r="H38" s="37"/>
       <c r="K38" s="94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -11317,7 +11318,7 @@
       <c r="G40" s="36"/>
       <c r="H40" s="37"/>
       <c r="K40" s="94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -11341,7 +11342,7 @@
       <c r="G42" s="36"/>
       <c r="H42" s="37"/>
       <c r="K42" s="94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -11354,7 +11355,7 @@
       <c r="G43" s="36"/>
       <c r="H43" s="37"/>
       <c r="K43" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -11367,7 +11368,7 @@
       <c r="G44" s="36"/>
       <c r="H44" s="37"/>
       <c r="K44" s="94" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -11380,7 +11381,7 @@
       <c r="G45" s="36"/>
       <c r="H45" s="37"/>
       <c r="K45" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -11392,7 +11393,7 @@
       <c r="G46" s="36"/>
       <c r="H46" s="37"/>
       <c r="K46" s="94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -11405,7 +11406,7 @@
       <c r="G47" s="36"/>
       <c r="H47" s="37"/>
       <c r="K47" s="93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -11418,7 +11419,7 @@
       <c r="G48" s="36"/>
       <c r="H48" s="37"/>
       <c r="K48" s="94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -11431,7 +11432,7 @@
       <c r="G49" s="36"/>
       <c r="H49" s="37"/>
       <c r="K49" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -11444,7 +11445,7 @@
       <c r="G50" s="36"/>
       <c r="H50" s="37"/>
       <c r="K50" s="94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -11457,7 +11458,7 @@
       <c r="G51" s="36"/>
       <c r="H51" s="37"/>
       <c r="K51" s="93" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -11470,7 +11471,7 @@
       <c r="G52" s="36"/>
       <c r="H52" s="37"/>
       <c r="K52" s="94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -11483,7 +11484,7 @@
       <c r="G53" s="36"/>
       <c r="H53" s="37"/>
       <c r="K53" s="93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -11523,17 +11524,17 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <mergeCells count="11">
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="J8:J12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="F8:F12"/>
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="190" priority="16" operator="equal">
@@ -11706,36 +11707,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>147</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="N1" s="224" t="s">
         <v>148</v>
-      </c>
-      <c r="N1" s="224" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="209.25" customHeight="1">
       <c r="A2" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="D2" s="122" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="E2" s="123" t="s">
         <v>153</v>
-      </c>
-      <c r="E2" s="123" t="s">
-        <v>154</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H2" s="124">
         <v>1</v>
@@ -11747,31 +11748,31 @@
         <v>21</v>
       </c>
       <c r="K2" s="106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L2" s="107"/>
     </row>
     <row r="3" spans="1:14" ht="72">
       <c r="A3" s="125" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="C3" s="125" t="s">
         <v>157</v>
-      </c>
-      <c r="C3" s="125" t="s">
-        <v>158</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H3" s="127" t="s">
         <v>19</v>
@@ -11783,10 +11784,10 @@
         <v>66</v>
       </c>
       <c r="K3" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="134" t="s">
         <v>161</v>
-      </c>
-      <c r="L3" s="134" t="s">
-        <v>162</v>
       </c>
       <c r="M3" s="129"/>
       <c r="N3" s="129"/>
@@ -11805,7 +11806,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>35</v>
@@ -11829,25 +11830,25 @@
     </row>
     <row r="5" spans="1:14" ht="57.6">
       <c r="A5" s="125" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="C5" s="134" t="s">
         <v>165</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>166</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H5" s="127" t="s">
         <v>19</v>
@@ -11859,7 +11860,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="130" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -11867,25 +11868,25 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="121" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="121" t="s">
         <v>171</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>172</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="132" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="124" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>19</v>
@@ -11897,31 +11898,31 @@
         <v>66</v>
       </c>
       <c r="K6" s="106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L6" s="107"/>
     </row>
     <row r="7" spans="1:14" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>177</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>178</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>19</v>
@@ -11933,7 +11934,7 @@
         <v>66</v>
       </c>
       <c r="K7" s="130" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -11965,13 +11966,13 @@
         <v>1</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K8" s="106" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L8" s="107" t="s">
         <v>39</v>
@@ -11997,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
@@ -12015,7 +12016,7 @@
         <v>37</v>
       </c>
       <c r="K9" s="130" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L9" s="129" t="s">
         <v>46</v>
@@ -12041,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
@@ -12065,25 +12066,25 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="125" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="125" t="s">
         <v>186</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>187</v>
       </c>
       <c r="D11" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="140" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -12096,30 +12097,30 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="129" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M11" s="129" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N11" s="129" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>191</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>192</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="132" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -12137,31 +12138,31 @@
         <v>66</v>
       </c>
       <c r="K12" s="106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L12" s="107"/>
     </row>
     <row r="13" spans="1:14" ht="69.75" customHeight="1">
       <c r="A13" s="125" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="74" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="C13" s="125" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="D13" s="142" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="142" t="s">
+      <c r="E13" s="80" t="s">
         <v>198</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>199</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" s="127" t="s">
         <v>81</v>
@@ -12173,125 +12174,125 @@
         <v>66</v>
       </c>
       <c r="K13" s="130" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="237" t="s">
+      <c r="A14" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="240" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="237" t="s">
+      <c r="C14" s="236" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="239" t="s">
-        <v>201</v>
-      </c>
-      <c r="F14" s="236" t="s">
+      <c r="E14" s="238" t="s">
+        <v>200</v>
+      </c>
+      <c r="F14" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="236" t="s">
+      <c r="G14" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="236" t="s">
+      <c r="H14" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="235" t="s">
+      <c r="I14" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="235" t="s">
+      <c r="J14" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="240"/>
-      <c r="L14" s="235"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="239"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="237"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="237"/>
+      <c r="A15" s="236"/>
+      <c r="B15" s="240"/>
+      <c r="C15" s="236"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="239"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="240"/>
-      <c r="L15" s="235"/>
+      <c r="E15" s="238"/>
+      <c r="F15" s="235"/>
+      <c r="G15" s="235"/>
+      <c r="H15" s="235"/>
+      <c r="I15" s="239"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="239"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="237"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="237"/>
+      <c r="A16" s="236"/>
+      <c r="B16" s="240"/>
+      <c r="C16" s="236"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="239"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="235"/>
+      <c r="E16" s="238"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="239"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="237"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="237"/>
+      <c r="A17" s="236"/>
+      <c r="B17" s="240"/>
+      <c r="C17" s="236"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="239"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="235"/>
+      <c r="E17" s="238"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="239"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="237"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="237"/>
+      <c r="A18" s="236"/>
+      <c r="B18" s="240"/>
+      <c r="C18" s="236"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="239"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="235"/>
+      <c r="E18" s="238"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>202</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="C19" s="125" t="s">
         <v>203</v>
-      </c>
-      <c r="C19" s="125" t="s">
-        <v>204</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -12309,35 +12310,35 @@
         <v>29</v>
       </c>
       <c r="K19" s="207" t="s">
+        <v>205</v>
+      </c>
+      <c r="L19" s="134" t="s">
         <v>206</v>
-      </c>
-      <c r="L19" s="134" t="s">
-        <v>207</v>
       </c>
       <c r="M19" s="129"/>
       <c r="N19" s="129"/>
     </row>
     <row r="20" spans="1:14" ht="86.4">
       <c r="A20" s="121" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>209</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>210</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H20" s="124" t="s">
         <v>19</v>
@@ -12349,25 +12350,25 @@
         <v>66</v>
       </c>
       <c r="K20" s="106" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L20" s="107"/>
     </row>
     <row r="21" spans="1:14" ht="100.8">
       <c r="A21" s="125" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>213</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>214</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>215</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="208" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>35</v>
@@ -12385,7 +12386,7 @@
         <v>37</v>
       </c>
       <c r="K21" s="130" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
@@ -12393,25 +12394,25 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="121" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>219</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>220</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>19</v>
@@ -12424,30 +12425,30 @@
       </c>
       <c r="K22" s="106"/>
       <c r="L22" s="141" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="43.2">
       <c r="A23" s="125" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="125" t="s">
         <v>225</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>226</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H23" s="127" t="s">
         <v>19</v>
@@ -12459,7 +12460,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="207" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -12467,19 +12468,19 @@
     </row>
     <row r="24" spans="1:14" ht="43.2">
       <c r="A24" s="121" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="C24" s="141" t="s">
         <v>231</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>232</v>
       </c>
       <c r="D24" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>35</v>
@@ -12491,13 +12492,13 @@
         <v>52</v>
       </c>
       <c r="I24" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="106" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L24" s="107"/>
     </row>
@@ -12515,7 +12516,7 @@
         <v>85</v>
       </c>
       <c r="E25" s="126" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F25" s="127" t="s">
         <v>17</v>
@@ -12541,25 +12542,25 @@
     </row>
     <row r="26" spans="1:14" ht="115.2">
       <c r="A26" s="121" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="C26" s="141" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="141" t="s">
+      <c r="D26" s="122" t="s">
         <v>238</v>
       </c>
-      <c r="D26" s="122" t="s">
+      <c r="E26" s="132" t="s">
         <v>239</v>
-      </c>
-      <c r="E26" s="132" t="s">
-        <v>240</v>
       </c>
       <c r="F26" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="124" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H26" s="124" t="s">
         <v>19</v>
@@ -12571,31 +12572,31 @@
         <v>66</v>
       </c>
       <c r="K26" s="106" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L26" s="107"/>
     </row>
     <row r="27" spans="1:14" ht="43.2">
       <c r="A27" s="125" t="s">
+        <v>242</v>
+      </c>
+      <c r="B27" s="74" t="s">
         <v>243</v>
       </c>
-      <c r="B27" s="74" t="s">
+      <c r="C27" s="125" t="s">
         <v>244</v>
-      </c>
-      <c r="C27" s="125" t="s">
-        <v>245</v>
       </c>
       <c r="D27" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="126" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F27" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="127" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H27" s="127" t="s">
         <v>81</v>
@@ -12607,7 +12608,7 @@
         <v>66</v>
       </c>
       <c r="K27" s="130" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L27" s="129"/>
       <c r="M27" s="129"/>
@@ -12615,25 +12616,25 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="121" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="C28" s="141" t="s">
         <v>250</v>
-      </c>
-      <c r="C28" s="141" t="s">
-        <v>251</v>
       </c>
       <c r="D28" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="132" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F28" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="124" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H28" s="124" t="s">
         <v>81</v>
@@ -12645,43 +12646,43 @@
         <v>66</v>
       </c>
       <c r="K28" s="106" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L28" s="107"/>
     </row>
     <row r="29" spans="1:14" ht="43.2">
       <c r="A29" s="125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="C29" s="125" t="s">
         <v>97</v>
-      </c>
-      <c r="C29" s="125" t="s">
-        <v>98</v>
       </c>
       <c r="D29" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F29" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H29" s="127" t="s">
         <v>81</v>
       </c>
       <c r="I29" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J29" s="129" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L29" s="129"/>
       <c r="M29" s="129"/>
@@ -12689,25 +12690,25 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="121" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="C30" s="121" t="s">
         <v>256</v>
-      </c>
-      <c r="C30" s="121" t="s">
-        <v>257</v>
       </c>
       <c r="D30" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="132" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F30" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H30" s="124" t="s">
         <v>81</v>
@@ -12719,31 +12720,31 @@
         <v>66</v>
       </c>
       <c r="K30" s="106" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L30" s="107"/>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="125" t="s">
+        <v>260</v>
+      </c>
+      <c r="B31" s="74" t="s">
         <v>261</v>
       </c>
-      <c r="B31" s="74" t="s">
+      <c r="C31" s="125" t="s">
         <v>262</v>
-      </c>
-      <c r="C31" s="125" t="s">
-        <v>263</v>
       </c>
       <c r="D31" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F31" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="127" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H31" s="127" t="s">
         <v>81</v>
@@ -12755,7 +12756,7 @@
         <v>66</v>
       </c>
       <c r="K31" s="130" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L31" s="129"/>
       <c r="M31" s="129"/>
@@ -12763,25 +12764,25 @@
     </row>
     <row r="32" spans="1:14" ht="57.6">
       <c r="A32" s="121" t="s">
+        <v>265</v>
+      </c>
+      <c r="B32" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="C32" s="121" t="s">
         <v>267</v>
-      </c>
-      <c r="C32" s="121" t="s">
-        <v>268</v>
       </c>
       <c r="D32" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F32" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="124" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H32" s="124" t="s">
         <v>19</v>
@@ -12793,31 +12794,31 @@
         <v>29</v>
       </c>
       <c r="K32" s="106" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L32" s="107"/>
     </row>
     <row r="33" spans="1:14" ht="57.6">
       <c r="A33" s="125" t="s">
+        <v>271</v>
+      </c>
+      <c r="B33" s="74" t="s">
         <v>272</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="C33" s="125" t="s">
         <v>273</v>
       </c>
-      <c r="C33" s="125" t="s">
+      <c r="D33" s="142" t="s">
         <v>274</v>
       </c>
-      <c r="D33" s="142" t="s">
+      <c r="E33" s="80" t="s">
         <v>275</v>
-      </c>
-      <c r="E33" s="80" t="s">
-        <v>276</v>
       </c>
       <c r="F33" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="127" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H33" s="127" t="s">
         <v>19</v>
@@ -12829,7 +12830,7 @@
         <v>66</v>
       </c>
       <c r="K33" s="130" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L33" s="129"/>
       <c r="M33" s="129"/>
@@ -12837,19 +12838,19 @@
     </row>
     <row r="34" spans="1:14" ht="43.2">
       <c r="A34" s="121" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="C34" s="121" t="s">
         <v>280</v>
-      </c>
-      <c r="C34" s="121" t="s">
-        <v>281</v>
       </c>
       <c r="D34" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="132" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F34" s="124" t="s">
         <v>17</v>
@@ -12867,25 +12868,25 @@
         <v>66</v>
       </c>
       <c r="K34" s="106" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L34" s="107"/>
     </row>
     <row r="35" spans="1:14" ht="115.2">
       <c r="A35" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="74" t="s">
+      <c r="C35" s="125" t="s">
         <v>102</v>
-      </c>
-      <c r="C35" s="125" t="s">
-        <v>103</v>
       </c>
       <c r="D35" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="205" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F35" s="127" t="s">
         <v>35</v>
@@ -12897,13 +12898,13 @@
         <v>1</v>
       </c>
       <c r="I35" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J35" s="129" t="s">
         <v>21</v>
       </c>
       <c r="K35" s="130" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L35" s="129" t="s">
         <v>46</v>
@@ -12917,25 +12918,25 @@
     </row>
     <row r="36" spans="1:14" ht="43.2">
       <c r="A36" s="121" t="s">
+        <v>284</v>
+      </c>
+      <c r="B36" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="C36" s="121" t="s">
         <v>286</v>
       </c>
-      <c r="C36" s="121" t="s">
+      <c r="D36" s="122" t="s">
         <v>287</v>
       </c>
-      <c r="D36" s="122" t="s">
+      <c r="E36" s="138" t="s">
         <v>288</v>
-      </c>
-      <c r="E36" s="138" t="s">
-        <v>289</v>
       </c>
       <c r="F36" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H36" s="124" t="s">
         <v>19</v>
@@ -12947,31 +12948,31 @@
         <v>66</v>
       </c>
       <c r="K36" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L36" s="107"/>
     </row>
     <row r="37" spans="1:14" ht="228" customHeight="1">
       <c r="A37" s="125" t="s">
+        <v>290</v>
+      </c>
+      <c r="B37" s="74" t="s">
         <v>291</v>
       </c>
-      <c r="B37" s="74" t="s">
+      <c r="C37" s="134" t="s">
         <v>292</v>
-      </c>
-      <c r="C37" s="134" t="s">
-        <v>293</v>
       </c>
       <c r="D37" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="126" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F37" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="128" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H37" s="127" t="s">
         <v>19</v>
@@ -12984,36 +12985,36 @@
       </c>
       <c r="K37" s="130"/>
       <c r="L37" s="129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M37" s="129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N37" s="129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="57.6">
       <c r="A38" s="121" t="s">
+        <v>296</v>
+      </c>
+      <c r="B38" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="B38" s="35" t="s">
+      <c r="C38" s="121" t="s">
         <v>298</v>
-      </c>
-      <c r="C38" s="121" t="s">
-        <v>299</v>
       </c>
       <c r="D38" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E38" s="132" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F38" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="128" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H38" s="124" t="s">
         <v>19</v>
@@ -13025,39 +13026,39 @@
         <v>29</v>
       </c>
       <c r="K38" s="106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L38" s="107" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M38" s="107" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N38" s="107" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2">
       <c r="A39" s="125" t="s">
+        <v>302</v>
+      </c>
+      <c r="B39" s="74" t="s">
         <v>303</v>
       </c>
-      <c r="B39" s="74" t="s">
+      <c r="C39" s="125" t="s">
         <v>304</v>
-      </c>
-      <c r="C39" s="125" t="s">
-        <v>305</v>
       </c>
       <c r="D39" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="126" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F39" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="128" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H39" s="127" t="s">
         <v>19</v>
@@ -13070,72 +13071,72 @@
       </c>
       <c r="K39" s="130"/>
       <c r="L39" s="129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M39" s="129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N39" s="129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="C40" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="C40" s="121" t="s">
-        <v>109</v>
       </c>
       <c r="D40" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="132" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F40" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I40" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J40" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K40" s="106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L40" s="107"/>
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="125" t="s">
+        <v>309</v>
+      </c>
+      <c r="B41" s="74" t="s">
         <v>310</v>
       </c>
-      <c r="B41" s="74" t="s">
+      <c r="C41" s="125" t="s">
         <v>311</v>
-      </c>
-      <c r="C41" s="125" t="s">
-        <v>312</v>
       </c>
       <c r="D41" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F41" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" s="127" t="s">
         <v>81</v>
@@ -13147,39 +13148,39 @@
         <v>66</v>
       </c>
       <c r="K41" s="130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L41" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M41" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N41" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
       <c r="A42" s="121" t="s">
+        <v>314</v>
+      </c>
+      <c r="B42" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="C42" s="121" t="s">
         <v>316</v>
-      </c>
-      <c r="C42" s="121" t="s">
-        <v>317</v>
       </c>
       <c r="D42" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="132" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F42" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H42" s="124" t="s">
         <v>19</v>
@@ -13191,29 +13192,29 @@
         <v>66</v>
       </c>
       <c r="K42" s="106" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L42" s="141" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M42" s="107"/>
       <c r="N42" s="107"/>
     </row>
     <row r="43" spans="1:14" ht="28.8">
       <c r="A43" s="125" t="s">
+        <v>319</v>
+      </c>
+      <c r="B43" s="74" t="s">
         <v>320</v>
       </c>
-      <c r="B43" s="74" t="s">
+      <c r="C43" s="125" t="s">
         <v>321</v>
-      </c>
-      <c r="C43" s="125" t="s">
-        <v>322</v>
       </c>
       <c r="D43" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="205" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F43" s="127" t="s">
         <v>17</v>
@@ -13231,35 +13232,35 @@
         <v>29</v>
       </c>
       <c r="K43" s="130" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L43" s="134" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M43" s="129"/>
       <c r="N43" s="129"/>
     </row>
     <row r="44" spans="1:14" ht="57.6">
       <c r="A44" s="121" t="s">
+        <v>324</v>
+      </c>
+      <c r="B44" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="C44" s="121" t="s">
         <v>326</v>
       </c>
-      <c r="C44" s="121" t="s">
+      <c r="D44" s="143" t="s">
         <v>327</v>
       </c>
-      <c r="D44" s="143" t="s">
+      <c r="E44" s="132" t="s">
         <v>328</v>
-      </c>
-      <c r="E44" s="132" t="s">
-        <v>329</v>
       </c>
       <c r="F44" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="124" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H44" s="124" t="s">
         <v>81</v>
@@ -13271,7 +13272,7 @@
         <v>37</v>
       </c>
       <c r="K44" s="106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L44" s="107"/>
       <c r="M44" s="107"/>
@@ -13279,25 +13280,25 @@
     </row>
     <row r="45" spans="1:14" ht="28.8">
       <c r="A45" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="74" t="s">
+      <c r="C45" s="125" t="s">
         <v>123</v>
-      </c>
-      <c r="C45" s="125" t="s">
-        <v>124</v>
       </c>
       <c r="D45" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E45" s="74" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F45" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G45" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H45" s="127" t="s">
         <v>19</v>
@@ -13309,39 +13310,39 @@
         <v>29</v>
       </c>
       <c r="K45" s="130" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L45" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M45" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N45" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="57.6">
       <c r="A46" s="121" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="C46" s="141" t="s">
         <v>332</v>
-      </c>
-      <c r="C46" s="141" t="s">
-        <v>333</v>
       </c>
       <c r="D46" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="132" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F46" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="124" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H46" s="124" t="s">
         <v>81</v>
@@ -13353,7 +13354,7 @@
         <v>37</v>
       </c>
       <c r="K46" s="106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L46" s="107"/>
       <c r="M46" s="107"/>
@@ -13361,25 +13362,25 @@
     </row>
     <row r="47" spans="1:14" ht="74.25" customHeight="1">
       <c r="A47" s="125" t="s">
+        <v>335</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="125" t="s">
         <v>336</v>
       </c>
-      <c r="B47" s="74" t="s">
-        <v>128</v>
-      </c>
-      <c r="C47" s="125" t="s">
+      <c r="D47" s="142" t="s">
         <v>337</v>
       </c>
-      <c r="D47" s="142" t="s">
+      <c r="E47" s="74" t="s">
         <v>338</v>
-      </c>
-      <c r="E47" s="74" t="s">
-        <v>339</v>
       </c>
       <c r="F47" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H47" s="127" t="s">
         <v>52</v>
@@ -13391,7 +13392,7 @@
         <v>66</v>
       </c>
       <c r="K47" s="130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L47" s="129"/>
       <c r="M47" s="129"/>
@@ -13399,19 +13400,19 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="C48" s="121" t="s">
         <v>133</v>
-      </c>
-      <c r="C48" s="121" t="s">
-        <v>134</v>
       </c>
       <c r="D48" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E48" s="132" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F48" s="124" t="s">
         <v>35</v>
@@ -13429,7 +13430,7 @@
         <v>29</v>
       </c>
       <c r="K48" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L48" s="107"/>
       <c r="M48" s="107"/>
@@ -13437,37 +13438,37 @@
     </row>
     <row r="49" spans="1:14" ht="57.6">
       <c r="A49" s="125" t="s">
+        <v>340</v>
+      </c>
+      <c r="B49" s="74" t="s">
         <v>341</v>
       </c>
-      <c r="B49" s="74" t="s">
+      <c r="C49" s="125" t="s">
         <v>342</v>
       </c>
-      <c r="C49" s="125" t="s">
+      <c r="D49" s="217" t="s">
         <v>343</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="E49" s="83" t="s">
         <v>344</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>345</v>
       </c>
       <c r="F49" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H49" s="127" t="s">
         <v>19</v>
       </c>
       <c r="I49" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J49" s="129" t="s">
         <v>66</v>
       </c>
       <c r="K49" s="130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L49" s="129"/>
       <c r="M49" s="129"/>
@@ -13475,19 +13476,19 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="121" t="s">
+        <v>345</v>
+      </c>
+      <c r="B50" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="C50" s="121" t="s">
         <v>347</v>
-      </c>
-      <c r="C50" s="121" t="s">
-        <v>348</v>
       </c>
       <c r="D50" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="132" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F50" s="124" t="s">
         <v>17</v>
@@ -13499,13 +13500,13 @@
         <v>81</v>
       </c>
       <c r="I50" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J50" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K50" s="106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L50" s="107"/>
       <c r="M50" s="107"/>
@@ -13513,19 +13514,19 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="125" t="s">
+        <v>349</v>
+      </c>
+      <c r="B51" s="74" t="s">
         <v>350</v>
       </c>
-      <c r="B51" s="74" t="s">
+      <c r="C51" s="125" t="s">
         <v>351</v>
-      </c>
-      <c r="C51" s="125" t="s">
-        <v>352</v>
       </c>
       <c r="D51" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F51" s="127" t="s">
         <v>17</v>
@@ -13543,7 +13544,7 @@
         <v>29</v>
       </c>
       <c r="K51" s="130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L51" s="129"/>
       <c r="M51" s="129"/>
@@ -13551,13 +13552,13 @@
     </row>
     <row r="52" spans="1:14" ht="84.75" customHeight="1">
       <c r="A52" s="121" t="s">
+        <v>353</v>
+      </c>
+      <c r="B52" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="C52" s="121" t="s">
         <v>355</v>
-      </c>
-      <c r="C52" s="121" t="s">
-        <v>356</v>
       </c>
       <c r="D52" s="132" t="s">
         <v>16</v>
@@ -13567,7 +13568,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="124" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H52" s="124" t="s">
         <v>19</v>
@@ -13603,17 +13604,17 @@
     <sortCondition ref="A2:A53"/>
   </sortState>
   <mergeCells count="11">
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
     <mergeCell ref="L14:L18"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="J14:J18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F14 F19:F53">
     <cfRule type="cellIs" dxfId="171" priority="8" operator="equal">
@@ -13780,42 +13781,42 @@
         <v>10</v>
       </c>
       <c r="L1" s="223" t="s">
+        <v>357</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>358</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="N1" s="108" t="s">
         <v>359</v>
       </c>
-      <c r="N1" s="108" t="s">
+      <c r="O1" s="108" t="s">
         <v>360</v>
       </c>
-      <c r="O1" s="108" t="s">
+      <c r="P1" s="223" t="s">
         <v>361</v>
       </c>
-      <c r="P1" s="223" t="s">
+      <c r="Q1" s="223" t="s">
         <v>362</v>
       </c>
-      <c r="Q1" s="223" t="s">
+      <c r="R1" s="224" t="s">
         <v>363</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="S1" s="224" t="s">
         <v>364</v>
       </c>
-      <c r="S1" s="224" t="s">
+      <c r="T1" s="224" t="s">
         <v>365</v>
       </c>
-      <c r="T1" s="224" t="s">
+      <c r="U1" s="224" t="s">
         <v>366</v>
       </c>
-      <c r="U1" s="224" t="s">
+      <c r="V1" s="233" t="s">
         <v>367</v>
-      </c>
-      <c r="V1" s="233" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="28.8">
       <c r="A2" s="64" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B2" s="157" t="s">
         <v>61</v>
@@ -13824,10 +13825,10 @@
         <v>62</v>
       </c>
       <c r="D2" s="152" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" s="158" t="s">
         <v>370</v>
-      </c>
-      <c r="E2" s="158" t="s">
-        <v>371</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
@@ -13847,25 +13848,25 @@
     </row>
     <row r="3" spans="1:22" ht="115.2">
       <c r="A3" s="68" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>372</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="68" t="s">
         <v>373</v>
-      </c>
-      <c r="C3" s="68" t="s">
-        <v>374</v>
       </c>
       <c r="D3" s="162" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -13877,7 +13878,7 @@
         <v>66</v>
       </c>
       <c r="K3" s="136" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -13892,19 +13893,19 @@
     </row>
     <row r="4" spans="1:22" ht="129.6">
       <c r="A4" s="64" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="157" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="C4" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="64" t="s">
-        <v>215</v>
-      </c>
       <c r="D4" s="71" t="s">
+        <v>376</v>
+      </c>
+      <c r="E4" s="158" t="s">
         <v>377</v>
-      </c>
-      <c r="E4" s="158" t="s">
-        <v>378</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
@@ -13919,28 +13920,28 @@
         <v>28</v>
       </c>
       <c r="J4" s="160" t="s">
+        <v>378</v>
+      </c>
+      <c r="K4" s="136" t="s">
         <v>379</v>
-      </c>
-      <c r="K4" s="136" t="s">
-        <v>380</v>
       </c>
       <c r="L4" s="107"/>
     </row>
     <row r="5" spans="1:22" ht="43.2">
       <c r="A5" s="165" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="75" t="s">
         <v>381</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="C5" s="165" t="s">
         <v>382</v>
-      </c>
-      <c r="C5" s="165" t="s">
-        <v>383</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F5" s="166" t="s">
         <v>35</v>
@@ -13958,7 +13959,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="136" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -13973,19 +13974,19 @@
     </row>
     <row r="6" spans="1:22" ht="72">
       <c r="A6" s="168" t="s">
+        <v>385</v>
+      </c>
+      <c r="B6" s="151" t="s">
         <v>386</v>
       </c>
-      <c r="B6" s="151" t="s">
+      <c r="C6" s="168" t="s">
         <v>387</v>
-      </c>
-      <c r="C6" s="168" t="s">
-        <v>388</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F6" s="133" t="s">
         <v>17</v>
@@ -14007,25 +14008,25 @@
     </row>
     <row r="7" spans="1:22" ht="115.2">
       <c r="A7" s="125" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>390</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>391</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="D7" s="171" t="s">
         <v>392</v>
       </c>
-      <c r="D7" s="171" t="s">
+      <c r="E7" s="81" t="s">
         <v>393</v>
-      </c>
-      <c r="E7" s="81" t="s">
-        <v>394</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -14050,25 +14051,25 @@
     </row>
     <row r="8" spans="1:22" ht="28.8">
       <c r="A8" s="64" t="s">
+        <v>340</v>
+      </c>
+      <c r="B8" s="157" t="s">
         <v>341</v>
       </c>
-      <c r="B8" s="157" t="s">
+      <c r="C8" s="172" t="s">
         <v>342</v>
       </c>
-      <c r="C8" s="172" t="s">
-        <v>343</v>
-      </c>
       <c r="D8" s="143" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E8" s="135" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F8" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="159" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H8" s="159" t="s">
         <v>81</v>
@@ -14080,13 +14081,13 @@
         <v>29</v>
       </c>
       <c r="K8" s="136" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:22" ht="43.2">
       <c r="A9" s="165" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>77</v>
@@ -14098,13 +14099,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="173" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F9" s="166" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="166" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H9" s="166">
         <v>1</v>
@@ -14116,7 +14117,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="136" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
@@ -14861,45 +14862,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="225" t="s">
+        <v>399</v>
+      </c>
+      <c r="M1" s="108" t="s">
         <v>400</v>
       </c>
-      <c r="M1" s="108" t="s">
+      <c r="N1" s="223" t="s">
         <v>401</v>
       </c>
-      <c r="N1" s="223" t="s">
+      <c r="O1" s="224" t="s">
         <v>402</v>
       </c>
-      <c r="O1" s="224" t="s">
+      <c r="P1" s="232" t="s">
         <v>403</v>
       </c>
-      <c r="P1" s="232" t="s">
+      <c r="Q1" s="233" t="s">
         <v>404</v>
-      </c>
-      <c r="Q1" s="233" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="64.349999999999994" customHeight="1">
       <c r="A2" s="64" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>406</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="172" t="s">
         <v>407</v>
-      </c>
-      <c r="C2" s="172" t="s">
-        <v>408</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>19</v>
@@ -14911,31 +14912,31 @@
         <v>29</v>
       </c>
       <c r="K2" s="156" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L2" s="136"/>
     </row>
     <row r="3" spans="1:17" ht="129.6">
       <c r="A3" s="68" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>411</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="68" t="s">
         <v>412</v>
-      </c>
-      <c r="C3" s="68" t="s">
-        <v>413</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -14947,7 +14948,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L3" s="75"/>
       <c r="M3" s="61"/>
@@ -14957,25 +14958,25 @@
     </row>
     <row r="4" spans="1:17" ht="28.8">
       <c r="A4" s="64" t="s">
+        <v>414</v>
+      </c>
+      <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="C4" s="64" t="s">
         <v>416</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>417</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H4" s="159">
         <v>1</v>
@@ -14987,7 +14988,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="156" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L4" s="136"/>
     </row>
@@ -15810,86 +15811,86 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
+        <v>420</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>421</v>
-      </c>
-      <c r="M1" s="223" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8">
       <c r="A2" s="121" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>424</v>
-      </c>
-      <c r="C2" s="121" t="s">
-        <v>425</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="128" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I2" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J2" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K2" s="98" t="s">
+        <v>426</v>
+      </c>
+      <c r="L2" s="141" t="s">
         <v>427</v>
       </c>
-      <c r="L2" s="141" t="s">
-        <v>428</v>
-      </c>
       <c r="M2" s="141" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="72">
       <c r="A3" s="125" t="s">
+        <v>428</v>
+      </c>
+      <c r="B3" s="74" t="s">
         <v>429</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="C3" s="125" t="s">
         <v>430</v>
-      </c>
-      <c r="C3" s="125" t="s">
-        <v>431</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="85" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H3" s="127">
         <v>1</v>
       </c>
       <c r="I3" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J3" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -15908,7 +15909,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -15933,25 +15934,25 @@
     </row>
     <row r="5" spans="1:13" ht="43.2">
       <c r="A5" s="125" t="s">
+        <v>434</v>
+      </c>
+      <c r="B5" s="74" t="s">
         <v>435</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="C5" s="134" t="s">
         <v>436</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>437</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H5" s="127">
         <v>1</v>
@@ -15963,32 +15964,32 @@
         <v>29</v>
       </c>
       <c r="K5" s="98" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
     </row>
     <row r="6" spans="1:13" ht="57.6">
       <c r="A6" s="121" t="s">
+        <v>440</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>441</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="121" t="s">
         <v>442</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>443</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>81</v>
@@ -16000,36 +16001,36 @@
         <v>29</v>
       </c>
       <c r="K6" s="98" t="s">
+        <v>445</v>
+      </c>
+      <c r="L6" s="107" t="s">
         <v>446</v>
       </c>
-      <c r="L6" s="107" t="s">
-        <v>447</v>
-      </c>
       <c r="M6" s="107" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>447</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>448</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="134" t="s">
         <v>449</v>
       </c>
-      <c r="C7" s="134" t="s">
+      <c r="D7" s="185" t="s">
         <v>450</v>
       </c>
-      <c r="D7" s="185" t="s">
+      <c r="E7" s="126" t="s">
         <v>451</v>
-      </c>
-      <c r="E7" s="126" t="s">
-        <v>452</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="156" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -16041,7 +16042,7 @@
         <v>29</v>
       </c>
       <c r="K7" s="98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -16060,7 +16061,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>17</v>
@@ -16072,32 +16073,32 @@
         <v>19</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L8" s="107"/>
       <c r="M8" s="107"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="125" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B9" s="74" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D9" s="187" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="126" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>17</v>
@@ -16115,32 +16116,32 @@
         <v>29</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
     </row>
     <row r="10" spans="1:13" ht="57.6">
       <c r="A10" s="121" t="s">
+        <v>458</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="141" t="s">
         <v>460</v>
-      </c>
-      <c r="C10" s="141" t="s">
-        <v>461</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H10" s="124" t="s">
         <v>81</v>
@@ -16152,32 +16153,32 @@
         <v>37</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
     <row r="11" spans="1:13" ht="72">
       <c r="A11" s="125" t="s">
+        <v>463</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>464</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="125" t="s">
         <v>465</v>
       </c>
-      <c r="C11" s="125" t="s">
+      <c r="D11" s="154" t="s">
         <v>466</v>
       </c>
-      <c r="D11" s="154" t="s">
+      <c r="E11" s="126" t="s">
         <v>467</v>
-      </c>
-      <c r="E11" s="126" t="s">
-        <v>468</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H11" s="127">
         <v>1</v>
@@ -16189,7 +16190,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
@@ -16208,7 +16209,7 @@
         <v>85</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -16226,14 +16227,14 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
     <row r="13" spans="1:13" ht="72">
       <c r="A13" s="125" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B13" s="74" t="s">
         <v>90</v>
@@ -16245,50 +16246,50 @@
         <v>92</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H13" s="127">
         <v>1</v>
       </c>
       <c r="I13" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="72">
       <c r="A14" s="121" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B14" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="121" t="s">
         <v>177</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>178</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="124" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H14" s="124" t="s">
         <v>19</v>
@@ -16300,57 +16301,57 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
     <row r="15" spans="1:13" ht="100.8">
       <c r="A15" s="125" t="s">
+        <v>479</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>480</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>481</v>
       </c>
-      <c r="C15" s="125" t="s">
+      <c r="D15" s="185" t="s">
+        <v>450</v>
+      </c>
+      <c r="E15" s="80" t="s">
         <v>482</v>
-      </c>
-      <c r="D15" s="185" t="s">
-        <v>451</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>483</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="127" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H15" s="127" t="s">
         <v>81</v>
       </c>
       <c r="I15" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="C16" s="141" t="s">
         <v>97</v>
-      </c>
-      <c r="C16" s="141" t="s">
-        <v>98</v>
       </c>
       <c r="D16" s="189" t="s">
         <v>16</v>
@@ -16360,7 +16361,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="124" t="s">
         <v>81</v>
@@ -16372,32 +16373,32 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13" ht="57.6">
       <c r="A17" s="125" t="s">
+        <v>485</v>
+      </c>
+      <c r="B17" s="74" t="s">
         <v>486</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="C17" s="125" t="s">
         <v>487</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="D17" s="185" t="s">
+        <v>450</v>
+      </c>
+      <c r="E17" s="74" t="s">
         <v>488</v>
-      </c>
-      <c r="D17" s="185" t="s">
-        <v>451</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>489</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -16409,32 +16410,32 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>109</v>
       </c>
       <c r="D18" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" s="124" t="s">
         <v>81</v>
@@ -16446,30 +16447,30 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
     </row>
     <row r="19" spans="1:13" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="126" t="s">
         <v>310</v>
       </c>
-      <c r="B19" s="126" t="s">
-        <v>311</v>
-      </c>
       <c r="C19" s="125" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D19" s="126"/>
       <c r="E19" s="80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>81</v>
@@ -16482,33 +16483,33 @@
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="129" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="M19" s="129" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="129.6">
       <c r="A20" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>112</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>113</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="133">
         <v>1</v>
@@ -16520,32 +16521,32 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
     <row r="21" spans="1:13" ht="43.2">
       <c r="A21" s="125" t="s">
+        <v>324</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>325</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>326</v>
       </c>
-      <c r="C21" s="125" t="s">
-        <v>327</v>
-      </c>
       <c r="D21" s="154" t="s">
+        <v>496</v>
+      </c>
+      <c r="E21" s="81" t="s">
         <v>497</v>
-      </c>
-      <c r="E21" s="81" t="s">
-        <v>498</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H21" s="127" t="s">
         <v>81</v>
@@ -16557,32 +16558,32 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13" ht="57.6">
       <c r="A22" s="121" t="s">
+        <v>330</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>332</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>333</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>81</v>
@@ -16599,19 +16600,19 @@
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="125" t="s">
         <v>133</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>134</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -16623,13 +16624,13 @@
         <v>19</v>
       </c>
       <c r="I23" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17111,7 +17112,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17128,7 +17129,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17146,7 +17147,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17176,13 +17177,13 @@
         <v>52</v>
       </c>
       <c r="I3" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J3" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17202,7 +17203,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17220,31 +17221,31 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L4" s="129"/>
     </row>
     <row r="5" spans="1:12" ht="43.2">
       <c r="A5" s="121" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="C5" s="121" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="121" t="s">
+      <c r="D5" s="122" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="122" t="s">
-        <v>198</v>
-      </c>
       <c r="E5" s="135" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="124" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>81</v>
@@ -17259,156 +17260,156 @@
       <c r="L5" s="107"/>
     </row>
     <row r="6" spans="1:12" ht="28.8">
-      <c r="A6" s="245" t="s">
+      <c r="A6" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="246" t="s">
+      <c r="B6" s="244" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="245" t="s">
+      <c r="C6" s="243" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="247" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="244" t="s">
+      <c r="E6" s="245" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="244" t="s">
+      <c r="G6" s="242" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="244" t="s">
+      <c r="H6" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="242" t="s">
+      <c r="I6" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="235" t="s">
+      <c r="J6" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="243" t="s">
-        <v>510</v>
-      </c>
-      <c r="L6" s="242"/>
+      <c r="K6" s="247" t="s">
+        <v>509</v>
+      </c>
+      <c r="L6" s="246"/>
     </row>
     <row r="7" spans="1:12" ht="28.8">
-      <c r="A7" s="245"/>
-      <c r="B7" s="246"/>
-      <c r="C7" s="245"/>
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="243"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="247"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="242"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="246"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="245"/>
+      <c r="A8" s="243"/>
+      <c r="B8" s="244"/>
+      <c r="C8" s="243"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="247"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="243"/>
-      <c r="L8" s="242"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="247"/>
+      <c r="L8" s="246"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="245"/>
-      <c r="B9" s="246"/>
-      <c r="C9" s="245"/>
+      <c r="A9" s="243"/>
+      <c r="B9" s="244"/>
+      <c r="C9" s="243"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="247"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="243"/>
-      <c r="L9" s="242"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="246"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="245"/>
-      <c r="B10" s="246"/>
-      <c r="C10" s="245"/>
+      <c r="A10" s="243"/>
+      <c r="B10" s="244"/>
+      <c r="C10" s="243"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="247"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="243"/>
-      <c r="L10" s="242"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="247"/>
+      <c r="L10" s="246"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="C11" s="121" t="s">
         <v>97</v>
-      </c>
-      <c r="C11" s="121" t="s">
-        <v>98</v>
       </c>
       <c r="D11" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L11" s="107"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="126" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="126" t="s">
+      <c r="C12" s="125" t="s">
         <v>102</v>
-      </c>
-      <c r="C12" s="125" t="s">
-        <v>103</v>
       </c>
       <c r="D12" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -17420,13 +17421,13 @@
         <v>81</v>
       </c>
       <c r="I12" s="127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -17434,61 +17435,61 @@
     </row>
     <row r="13" spans="1:12" ht="28.8">
       <c r="A13" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="132" t="s">
+      <c r="C13" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="C13" s="121" t="s">
-        <v>109</v>
       </c>
       <c r="D13" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I13" s="124" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L13" s="107"/>
     </row>
     <row r="14" spans="1:12" ht="48.9" customHeight="1">
       <c r="A14" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="125" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="125" t="s">
+      <c r="C14" s="125" t="s">
         <v>123</v>
-      </c>
-      <c r="C14" s="125" t="s">
-        <v>124</v>
       </c>
       <c r="D14" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="193" t="s">
         <v>19</v>
@@ -17500,27 +17501,27 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L14" s="129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="121" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="121" t="s">
+      <c r="C15" s="121" t="s">
         <v>133</v>
-      </c>
-      <c r="C15" s="121" t="s">
-        <v>134</v>
       </c>
       <c r="D15" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -17538,7 +17539,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L15" s="107"/>
     </row>
@@ -17665,17 +17666,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
   <mergeCells count="11">
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
@@ -17819,30 +17820,30 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="92.4">
       <c r="A2" s="131" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="D2" s="143" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="143" t="s">
-        <v>153</v>
-      </c>
       <c r="E2" s="82" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H2" s="124">
         <v>1</v>
@@ -17854,7 +17855,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -17892,25 +17893,25 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B4" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="121" t="s">
         <v>177</v>
-      </c>
-      <c r="C4" s="121" t="s">
-        <v>178</v>
       </c>
       <c r="D4" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="124" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H4" s="124" t="s">
         <v>19</v>
@@ -17998,13 +17999,13 @@
     </row>
     <row r="7" spans="1:12" ht="28.8">
       <c r="A7" s="125" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>112</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>113</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>16</v>
@@ -18014,7 +18015,7 @@
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>19</v>
@@ -18042,7 +18043,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18060,101 +18061,101 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="43.2">
       <c r="A9" s="125" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" s="74" t="s">
         <v>526</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="C9" s="125" t="s">
         <v>527</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>528</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H9" s="127">
         <v>1</v>
       </c>
       <c r="I9" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J9" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
       <c r="A10" s="121" t="s">
+        <v>530</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>531</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="121" t="s">
         <v>532</v>
-      </c>
-      <c r="C10" s="121" t="s">
-        <v>533</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H10" s="133">
         <v>1</v>
       </c>
       <c r="I10" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L10" s="107"/>
     </row>
     <row r="11" spans="1:12" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>463</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>464</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="134" t="s">
         <v>465</v>
       </c>
-      <c r="C11" s="134" t="s">
+      <c r="D11" s="154" t="s">
         <v>466</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>467</v>
       </c>
       <c r="E11" s="126"/>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -18170,13 +18171,13 @@
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>535</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>536</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>537</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>538</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18186,7 +18187,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="124" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H12" s="124" t="s">
         <v>19</v>
@@ -18202,19 +18203,19 @@
     </row>
     <row r="13" spans="1:12" ht="57.6">
       <c r="A13" s="191" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="74" t="s">
         <v>213</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="C13" s="134" t="s">
         <v>214</v>
-      </c>
-      <c r="C13" s="134" t="s">
-        <v>215</v>
       </c>
       <c r="D13" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18236,13 +18237,13 @@
     </row>
     <row r="14" spans="1:12" ht="28.8">
       <c r="A14" s="121" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="121" t="s">
         <v>231</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>232</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
@@ -18268,19 +18269,19 @@
     </row>
     <row r="15" spans="1:12" ht="57.6">
       <c r="A15" s="125" t="s">
+        <v>539</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>540</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>541</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>542</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18314,7 +18315,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18348,13 +18349,13 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H17" s="127">
         <v>1</v>
@@ -18366,31 +18367,31 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L17" s="129"/>
     </row>
     <row r="18" spans="1:12" ht="57.6">
       <c r="A18" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="121" t="s">
         <v>97</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>98</v>
       </c>
       <c r="D18" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" s="124" t="s">
         <v>81</v>
@@ -18406,13 +18407,13 @@
     </row>
     <row r="19" spans="1:12" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>265</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="C19" s="134" t="s">
         <v>267</v>
-      </c>
-      <c r="C19" s="134" t="s">
-        <v>268</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
@@ -18422,7 +18423,7 @@
         <v>17</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>19</v>
@@ -18435,24 +18436,24 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="43.2">
       <c r="A20" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>102</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>103</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -18476,19 +18477,19 @@
     </row>
     <row r="21" spans="1:12" ht="57.6">
       <c r="A21" s="125" t="s">
+        <v>549</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>550</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>551</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>552</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -18506,33 +18507,33 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
+        <v>553</v>
+      </c>
+      <c r="L21" s="192" t="s">
         <v>554</v>
-      </c>
-      <c r="L21" s="192" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="43.2">
       <c r="A22" s="121" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="121" t="s">
         <v>336</v>
       </c>
-      <c r="B22" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="121" t="s">
+      <c r="D22" s="143" t="s">
         <v>337</v>
       </c>
-      <c r="D22" s="143" t="s">
-        <v>338</v>
-      </c>
       <c r="E22" s="35" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>52</v>
@@ -18548,19 +18549,19 @@
     </row>
     <row r="23" spans="1:12" ht="28.8">
       <c r="A23" s="125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="134" t="s">
         <v>133</v>
-      </c>
-      <c r="C23" s="134" t="s">
-        <v>134</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -18578,7 +18579,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L23" s="195"/>
     </row>
@@ -19061,15 +19062,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -19312,6 +19304,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19325,14 +19326,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19351,6 +19344,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
   <ds:schemaRefs>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8958F1D5-0A21-4FE0-BA8C-AACF2C87639E}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75DD3E37-514C-4AE3-A673-1E268BD8AFB0}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -1734,9 +1734,6 @@
     <t>http://publications.europa.eu/resource/authority/file-type</t>
   </si>
   <si>
-    <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL, e.g., from the File Type vocabulary. For instance, for mzML files the value of this property could be: http://edamontology.org/format_3244</t>
-  </si>
-  <si>
     <t>dct:MediaTypeOrExtent (IRI)</t>
   </si>
   <si>
@@ -2618,6 +2615,9 @@
   <si>
     <t>The licence under which the catalogue (with resource description) is made available.
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
+  </si>
+  <si>
+    <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL from the File Type vocabulary.</t>
   </si>
 </sst>
 </file>
@@ -3765,6 +3765,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3776,13 +3779,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3796,12 +3802,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7438,33 +7438,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>557</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>558</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>559</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>560</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="72">
       <c r="A2" s="196" t="s">
+        <v>561</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>562</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="76" t="s">
         <v>563</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>564</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7473,7 +7473,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7488,13 +7488,13 @@
     </row>
     <row r="3" spans="1:15" ht="28.8">
       <c r="A3" s="68" t="s">
+        <v>566</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>567</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="77" t="s">
         <v>568</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>569</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7633,36 +7633,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>569</v>
+      </c>
+      <c r="M1" s="220" t="s">
         <v>570</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="N1" s="226" t="s">
         <v>571</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="O1" s="230" t="s">
         <v>572</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="P1" s="227" t="s">
         <v>573</v>
       </c>
-      <c r="P1" s="227" t="s">
+      <c r="Q1" s="231" t="s">
         <v>574</v>
       </c>
-      <c r="Q1" s="231" t="s">
+      <c r="R1" s="233" t="s">
         <v>575</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="58" t="s">
+        <v>576</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>577</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="76" t="s">
         <v>578</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>579</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -7690,13 +7690,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="48" t="s">
+        <v>579</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>580</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>581</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>582</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8358,33 +8358,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>582</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>583</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>584</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>585</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2">
       <c r="A2" s="84" t="s">
+        <v>586</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>587</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>588</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>589</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8414,19 +8414,19 @@
     </row>
     <row r="3" spans="1:15" ht="129.6">
       <c r="A3" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>591</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>592</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="D3" s="234" t="s">
         <v>593</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="E3" s="50" t="s">
         <v>594</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>595</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -8552,33 +8552,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>595</v>
+      </c>
+      <c r="M1" s="229" t="s">
         <v>596</v>
       </c>
-      <c r="M1" s="229" t="s">
+      <c r="N1" s="228" t="s">
         <v>597</v>
       </c>
-      <c r="N1" s="228" t="s">
+      <c r="O1" s="233" t="s">
         <v>598</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="158.4">
       <c r="A2" s="84" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>591</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>592</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>600</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>592</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>593</v>
-      </c>
-      <c r="D2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>601</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>602</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
@@ -8599,19 +8599,19 @@
     </row>
     <row r="3" spans="1:15" ht="43.2">
       <c r="A3" s="48" t="s">
+        <v>602</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>603</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>604</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>605</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
@@ -8737,33 +8737,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>606</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>607</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>608</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>609</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="100.8">
       <c r="A2" s="84" t="s">
+        <v>610</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>611</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>612</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>613</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8784,19 +8784,19 @@
     </row>
     <row r="3" spans="1:15" ht="57.6">
       <c r="A3" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>615</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>616</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>617</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -8900,7 +8900,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -8923,13 +8923,13 @@
     </row>
     <row r="2" spans="1:10" ht="28.8">
       <c r="A2" s="63" t="s">
+        <v>619</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>620</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="C2" s="44" t="s">
         <v>621</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>622</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -8937,7 +8937,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -8951,13 +8951,13 @@
     </row>
     <row r="3" spans="1:10" ht="43.2">
       <c r="A3" s="67" t="s">
+        <v>623</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>624</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>625</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>626</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8965,10 +8965,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="H3" s="48" t="s">
         <v>627</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>628</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -8979,13 +8979,13 @@
     </row>
     <row r="4" spans="1:10" ht="43.2">
       <c r="A4" s="63" t="s">
+        <v>628</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>629</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="C4" s="44" t="s">
         <v>630</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>631</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -8993,10 +8993,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
+        <v>631</v>
+      </c>
+      <c r="H4" s="65" t="s">
         <v>632</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>633</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9007,26 +9007,26 @@
     </row>
     <row r="5" spans="1:10" ht="43.2">
       <c r="A5" s="67" t="s">
+        <v>633</v>
+      </c>
+      <c r="B5" s="50" t="s">
         <v>634</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>635</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>636</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
+        <v>637</v>
+      </c>
+      <c r="H5" s="48" t="s">
         <v>638</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>639</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9037,13 +9037,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8">
       <c r="A6" s="63" t="s">
+        <v>639</v>
+      </c>
+      <c r="B6" s="73" t="s">
         <v>640</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="C6" s="44" t="s">
         <v>641</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>642</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9054,7 +9054,7 @@
         <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9065,13 +9065,13 @@
     </row>
     <row r="7" spans="1:10" ht="28.8">
       <c r="A7" s="67" t="s">
+        <v>642</v>
+      </c>
+      <c r="B7" s="50" t="s">
         <v>643</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>644</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>645</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9093,23 +9093,23 @@
     </row>
     <row r="8" spans="1:10" ht="86.4">
       <c r="A8" s="63" t="s">
+        <v>645</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>646</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="C8" s="44" t="s">
         <v>647</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>648</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9123,13 +9123,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.8">
       <c r="A9" s="67" t="s">
+        <v>650</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>651</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>652</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>653</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9137,7 +9137,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9151,23 +9151,23 @@
     </row>
     <row r="10" spans="1:10" ht="28.8">
       <c r="A10" s="63" t="s">
+        <v>654</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>655</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="44" t="s">
         <v>656</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>657</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -9632,36 +9632,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>658</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>659</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="233" t="s">
         <v>660</v>
-      </c>
-      <c r="N1" s="233" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="72">
       <c r="A2" s="44" t="s">
+        <v>661</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>662</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>663</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="78" t="s">
         <v>664</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="E2" s="197" t="s">
         <v>665</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>666</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -9675,13 +9675,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1">
       <c r="A3" s="49" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>668</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="48" t="s">
         <v>669</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>670</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -9691,7 +9691,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -10605,107 +10605,107 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="236" t="s">
+      <c r="A8" s="237" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="237" t="s">
+      <c r="B8" s="238" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="236" t="s">
+      <c r="C8" s="237" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="238" t="s">
+      <c r="E8" s="239" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="235" t="s">
+      <c r="F8" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="235" t="s">
+      <c r="G8" s="236" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="235" t="s">
+      <c r="H8" s="236" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="239" t="s">
+      <c r="I8" s="235" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="239" t="s">
+      <c r="J8" s="235" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="239"/>
-      <c r="M8" s="239"/>
+      <c r="L8" s="235"/>
+      <c r="M8" s="235"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="236"/>
-      <c r="B9" s="237"/>
-      <c r="C9" s="236"/>
+      <c r="A9" s="237"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="237"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="238"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="239"/>
-      <c r="M9" s="239"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="235"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="236"/>
-      <c r="B10" s="237"/>
-      <c r="C10" s="236"/>
+      <c r="A10" s="237"/>
+      <c r="B10" s="238"/>
+      <c r="C10" s="237"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="238"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="235"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="236"/>
-      <c r="B11" s="237"/>
-      <c r="C11" s="236"/>
+      <c r="A11" s="237"/>
+      <c r="B11" s="238"/>
+      <c r="C11" s="237"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="238"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="239"/>
+      <c r="L11" s="235"/>
+      <c r="M11" s="235"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="236"/>
-      <c r="B12" s="237"/>
-      <c r="C12" s="236"/>
+      <c r="A12" s="237"/>
+      <c r="B12" s="238"/>
+      <c r="C12" s="237"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="238"/>
-      <c r="F12" s="235"/>
-      <c r="G12" s="235"/>
-      <c r="H12" s="235"/>
-      <c r="I12" s="239"/>
-      <c r="J12" s="239"/>
+      <c r="E12" s="239"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="239"/>
-      <c r="M12" s="239"/>
+      <c r="L12" s="235"/>
+      <c r="M12" s="235"/>
     </row>
     <row r="13" spans="1:13" ht="43.2">
       <c r="A13" s="125" t="s">
@@ -10830,7 +10830,7 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -11524,17 +11524,17 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <mergeCells count="11">
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="J8:J12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="F8:F12"/>
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="190" priority="16" operator="equal">
@@ -12181,102 +12181,102 @@
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="236" t="s">
+      <c r="A14" s="237" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="240" t="s">
+      <c r="B14" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="236" t="s">
+      <c r="C14" s="237" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="238" t="s">
+      <c r="E14" s="239" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="235" t="s">
+      <c r="F14" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="235" t="s">
+      <c r="G14" s="236" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="235" t="s">
+      <c r="H14" s="236" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="239" t="s">
+      <c r="I14" s="235" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="239" t="s">
+      <c r="J14" s="235" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="241"/>
-      <c r="L14" s="239"/>
+      <c r="K14" s="240"/>
+      <c r="L14" s="235"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="236"/>
-      <c r="B15" s="240"/>
-      <c r="C15" s="236"/>
+      <c r="A15" s="237"/>
+      <c r="B15" s="241"/>
+      <c r="C15" s="237"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="238"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
-      <c r="H15" s="235"/>
-      <c r="I15" s="239"/>
-      <c r="J15" s="239"/>
-      <c r="K15" s="241"/>
-      <c r="L15" s="239"/>
+      <c r="E15" s="239"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="240"/>
+      <c r="L15" s="235"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="236"/>
-      <c r="B16" s="240"/>
-      <c r="C16" s="236"/>
+      <c r="A16" s="237"/>
+      <c r="B16" s="241"/>
+      <c r="C16" s="237"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="238"/>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
-      <c r="K16" s="241"/>
-      <c r="L16" s="239"/>
+      <c r="E16" s="239"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="240"/>
+      <c r="L16" s="235"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="236"/>
-      <c r="B17" s="240"/>
-      <c r="C17" s="236"/>
+      <c r="A17" s="237"/>
+      <c r="B17" s="241"/>
+      <c r="C17" s="237"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="238"/>
-      <c r="F17" s="235"/>
-      <c r="G17" s="235"/>
-      <c r="H17" s="235"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="239"/>
+      <c r="E17" s="239"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="240"/>
+      <c r="L17" s="235"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="236"/>
-      <c r="B18" s="240"/>
-      <c r="C18" s="236"/>
+      <c r="A18" s="237"/>
+      <c r="B18" s="241"/>
+      <c r="C18" s="237"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="238"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="240"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
@@ -13604,17 +13604,17 @@
     <sortCondition ref="A2:A53"/>
   </sortState>
   <mergeCells count="11">
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="E14:E18"/>
     <mergeCell ref="L14:L18"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="J14:J18"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F14 F19:F53">
     <cfRule type="cellIs" dxfId="171" priority="8" operator="equal">
@@ -13860,7 +13860,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
@@ -14930,7 +14930,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
@@ -16158,7 +16158,7 @@
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
-    <row r="11" spans="1:13" ht="72">
+    <row r="11" spans="1:13" ht="43.2">
       <c r="A11" s="125" t="s">
         <v>463</v>
       </c>
@@ -16172,13 +16172,13 @@
         <v>466</v>
       </c>
       <c r="E11" s="126" t="s">
-        <v>467</v>
+        <v>674</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H11" s="127">
         <v>1</v>
@@ -16190,7 +16190,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
@@ -16209,7 +16209,7 @@
         <v>85</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -16227,14 +16227,14 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
     <row r="13" spans="1:13" ht="72">
       <c r="A13" s="125" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B13" s="74" t="s">
         <v>90</v>
@@ -16246,13 +16246,13 @@
         <v>92</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H13" s="127">
         <v>1</v>
@@ -16264,14 +16264,14 @@
         <v>37</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="72">
       <c r="A14" s="121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>176</v>
@@ -16283,7 +16283,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -16301,26 +16301,26 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
     <row r="15" spans="1:13" ht="100.8">
       <c r="A15" s="125" t="s">
+        <v>478</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>479</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>480</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>481</v>
       </c>
       <c r="D15" s="185" t="s">
         <v>450</v>
       </c>
       <c r="E15" s="80" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -16338,7 +16338,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
@@ -16373,26 +16373,26 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13" ht="57.6">
       <c r="A17" s="125" t="s">
+        <v>484</v>
+      </c>
+      <c r="B17" s="74" t="s">
         <v>485</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="C17" s="125" t="s">
         <v>486</v>
-      </c>
-      <c r="C17" s="125" t="s">
-        <v>487</v>
       </c>
       <c r="D17" s="185" t="s">
         <v>450</v>
       </c>
       <c r="E17" s="74" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>17</v>
@@ -16410,7 +16410,7 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
@@ -16429,7 +16429,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -16447,7 +16447,7 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
@@ -16460,7 +16460,7 @@
         <v>310</v>
       </c>
       <c r="C19" s="125" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D19" s="126"/>
       <c r="E19" s="80" t="s">
@@ -16483,10 +16483,10 @@
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="129" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M19" s="129" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="129.6">
@@ -16503,7 +16503,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
@@ -16521,7 +16521,7 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
@@ -16537,10 +16537,10 @@
         <v>326</v>
       </c>
       <c r="D21" s="154" t="s">
+        <v>495</v>
+      </c>
+      <c r="E21" s="81" t="s">
         <v>496</v>
-      </c>
-      <c r="E21" s="81" t="s">
-        <v>497</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -16558,7 +16558,7 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
@@ -16577,7 +16577,7 @@
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
@@ -16612,7 +16612,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -16630,7 +16630,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17112,7 +17112,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17129,7 +17129,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17147,7 +17147,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17183,7 +17183,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17203,7 +17203,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17221,7 +17221,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L4" s="129"/>
     </row>
@@ -17239,7 +17239,7 @@
         <v>197</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
@@ -17260,104 +17260,104 @@
       <c r="L5" s="107"/>
     </row>
     <row r="6" spans="1:12" ht="28.8">
-      <c r="A6" s="243" t="s">
+      <c r="A6" s="245" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="244" t="s">
+      <c r="B6" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="243" t="s">
+      <c r="C6" s="245" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="245" t="s">
+      <c r="E6" s="247" t="s">
         <v>200</v>
       </c>
-      <c r="F6" s="242" t="s">
+      <c r="F6" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="242" t="s">
+      <c r="G6" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="242" t="s">
+      <c r="H6" s="244" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="246" t="s">
+      <c r="I6" s="242" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="239" t="s">
+      <c r="J6" s="235" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="247" t="s">
-        <v>509</v>
-      </c>
-      <c r="L6" s="246"/>
+      <c r="K6" s="243" t="s">
+        <v>508</v>
+      </c>
+      <c r="L6" s="242"/>
     </row>
     <row r="7" spans="1:12" ht="28.8">
-      <c r="A7" s="243"/>
-      <c r="B7" s="244"/>
-      <c r="C7" s="243"/>
+      <c r="A7" s="245"/>
+      <c r="B7" s="246"/>
+      <c r="C7" s="245"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="245"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="242"/>
-      <c r="I7" s="246"/>
-      <c r="J7" s="239"/>
-      <c r="K7" s="247"/>
-      <c r="L7" s="246"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="244"/>
+      <c r="I7" s="242"/>
+      <c r="J7" s="235"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="242"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="243"/>
-      <c r="B8" s="244"/>
-      <c r="C8" s="243"/>
+      <c r="A8" s="245"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="245"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="245"/>
-      <c r="F8" s="242"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="242"/>
-      <c r="I8" s="246"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="247"/>
-      <c r="L8" s="246"/>
+      <c r="E8" s="247"/>
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="244"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="243"/>
+      <c r="L8" s="242"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="243"/>
-      <c r="B9" s="244"/>
-      <c r="C9" s="243"/>
+      <c r="A9" s="245"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="245"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="246"/>
+      <c r="E9" s="247"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="242"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="243"/>
-      <c r="B10" s="244"/>
-      <c r="C10" s="243"/>
+      <c r="A10" s="245"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="245"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="246"/>
+      <c r="E10" s="247"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="244"/>
+      <c r="H10" s="244"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="242"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="121" t="s">
@@ -17373,7 +17373,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -17391,7 +17391,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L11" s="107"/>
     </row>
@@ -17409,7 +17409,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -17427,7 +17427,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -17447,7 +17447,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
@@ -17465,7 +17465,7 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L13" s="107"/>
     </row>
@@ -17483,7 +17483,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -17501,7 +17501,7 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L14" s="129" t="s">
         <v>313</v>
@@ -17521,7 +17521,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -17666,17 +17666,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
   <mergeCells count="11">
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="J6:J10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
@@ -17820,7 +17820,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="92.4">
@@ -17837,7 +17837,7 @@
         <v>152</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
@@ -17855,7 +17855,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -17893,7 +17893,7 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>176</v>
@@ -17905,7 +17905,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -18043,7 +18043,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18061,25 +18061,25 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="43.2">
       <c r="A9" s="125" t="s">
+        <v>524</v>
+      </c>
+      <c r="B9" s="74" t="s">
         <v>525</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="C9" s="125" t="s">
         <v>526</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>527</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
@@ -18097,25 +18097,25 @@
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
       <c r="A10" s="121" t="s">
+        <v>529</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>530</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="121" t="s">
         <v>531</v>
-      </c>
-      <c r="C10" s="121" t="s">
-        <v>532</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
@@ -18133,7 +18133,7 @@
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L10" s="107"/>
     </row>
@@ -18155,7 +18155,7 @@
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -18171,13 +18171,13 @@
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>534</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>535</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>536</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>537</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18215,7 +18215,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18269,19 +18269,19 @@
     </row>
     <row r="15" spans="1:12" ht="57.6">
       <c r="A15" s="125" t="s">
+        <v>538</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>539</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>540</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>541</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18315,7 +18315,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18349,7 +18349,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
@@ -18367,7 +18367,7 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L17" s="129"/>
     </row>
@@ -18385,7 +18385,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="43.2">
@@ -18453,7 +18453,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -18477,19 +18477,19 @@
     </row>
     <row r="21" spans="1:12" ht="57.6">
       <c r="A21" s="125" t="s">
+        <v>548</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>549</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>550</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>551</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -18507,10 +18507,10 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
+        <v>552</v>
+      </c>
+      <c r="L21" s="192" t="s">
         <v>553</v>
-      </c>
-      <c r="L21" s="192" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="43.2">
@@ -18527,7 +18527,7 @@
         <v>337</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
@@ -18561,7 +18561,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -18579,7 +18579,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L23" s="195"/>
     </row>
@@ -19062,6 +19062,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -19304,15 +19313,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19326,6 +19326,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19344,14 +19352,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
   <ds:schemaRefs>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75DD3E37-514C-4AE3-A673-1E268BD8AFB0}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A5D35E6-B235-466B-BAC2-6DE286A26D1D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-12765" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -583,12 +583,6 @@
     <t>If available, add URI to analytics distribution here</t>
   </si>
   <si>
-    <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
-For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
-As multiple legislations may apply to the resource the maximum cardinality is not limited.
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
-  </si>
-  <si>
     <t>code values</t>
   </si>
   <si>
@@ -841,11 +835,6 @@
     <t>https://w3c.github.io/dpv/2.0/dpv/modules/legal_basis.html#vocab-legal-basis</t>
   </si>
   <si>
-    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
-Example value for this property could be: dpv:Consent</t>
-  </si>
-  <si>
     <t>dpv:LegalBasis</t>
   </si>
   <si>
@@ -989,10 +978,6 @@
   </si>
   <si>
     <t>https://w3c.github.io/dpv/2.1/dpv/#vocab-purposes</t>
-  </si>
-  <si>
-    <t>One (or many) category or sub-category of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column).
-Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
   <si>
     <t>dpv:Purpose</t>
@@ -2618,6 +2603,22 @@
   </si>
   <si>
     <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL from the File Type vocabulary.</t>
+  </si>
+  <si>
+    <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
+For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
+As multiple legislations may apply to the resource the maximum cardinality is not limited. Note that the relation with other legislations is complex and is being looked into by legal experts.
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
+  </si>
+  <si>
+    <t>One (or many) category or sub-category of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
+Example value could be: dpv:ResearchAndDevelopment.</t>
+  </si>
+  <si>
+    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
+This property should always be filled if the data contains personal data and the applicable legislation is GDPR.
+Example value for this property could be: dpv:Consent</t>
   </si>
 </sst>
 </file>
@@ -3765,9 +3766,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3779,10 +3777,25 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3790,18 +3803,6 @@
     </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7438,33 +7439,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>554</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>555</v>
+      </c>
+      <c r="N1" s="227" t="s">
+        <v>556</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>557</v>
-      </c>
-      <c r="M1" s="226" t="s">
-        <v>558</v>
-      </c>
-      <c r="N1" s="227" t="s">
-        <v>559</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="72">
       <c r="A2" s="196" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7473,7 +7474,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7488,13 +7489,13 @@
     </row>
     <row r="3" spans="1:15" ht="28.8">
       <c r="A3" s="68" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7633,36 +7634,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>566</v>
+      </c>
+      <c r="M1" s="220" t="s">
+        <v>567</v>
+      </c>
+      <c r="N1" s="226" t="s">
+        <v>568</v>
+      </c>
+      <c r="O1" s="230" t="s">
         <v>569</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="P1" s="227" t="s">
         <v>570</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="Q1" s="231" t="s">
         <v>571</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="R1" s="233" t="s">
         <v>572</v>
-      </c>
-      <c r="P1" s="227" t="s">
-        <v>573</v>
-      </c>
-      <c r="Q1" s="231" t="s">
-        <v>574</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="58" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -7690,13 +7691,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="48" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8358,33 +8359,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>579</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>580</v>
+      </c>
+      <c r="N1" s="227" t="s">
+        <v>581</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>582</v>
-      </c>
-      <c r="M1" s="226" t="s">
-        <v>583</v>
-      </c>
-      <c r="N1" s="227" t="s">
-        <v>584</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2">
       <c r="A2" s="84" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8414,25 +8415,25 @@
     </row>
     <row r="3" spans="1:15" ht="129.6">
       <c r="A3" s="48" t="s">
+        <v>587</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>588</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>589</v>
+      </c>
+      <c r="D3" s="234" t="s">
         <v>590</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>591</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>592</v>
-      </c>
-      <c r="D3" s="234" t="s">
-        <v>593</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>594</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8552,39 +8553,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>592</v>
+      </c>
+      <c r="M1" s="229" t="s">
+        <v>593</v>
+      </c>
+      <c r="N1" s="228" t="s">
+        <v>594</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>595</v>
-      </c>
-      <c r="M1" s="229" t="s">
-        <v>596</v>
-      </c>
-      <c r="N1" s="228" t="s">
-        <v>597</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="158.4">
       <c r="A2" s="84" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="115" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>52</v>
@@ -8599,25 +8600,25 @@
     </row>
     <row r="3" spans="1:15" ht="43.2">
       <c r="A3" s="48" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>52</v>
@@ -8737,39 +8738,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>603</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>604</v>
+      </c>
+      <c r="N1" s="227" t="s">
+        <v>605</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>606</v>
-      </c>
-      <c r="M1" s="226" t="s">
-        <v>607</v>
-      </c>
-      <c r="N1" s="227" t="s">
-        <v>608</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="100.8">
       <c r="A2" s="84" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>81</v>
@@ -8784,25 +8785,25 @@
     </row>
     <row r="3" spans="1:15" ht="57.6">
       <c r="A3" s="48" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8900,7 +8901,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -8923,13 +8924,13 @@
     </row>
     <row r="2" spans="1:10" ht="28.8">
       <c r="A2" s="63" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -8937,7 +8938,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -8951,13 +8952,13 @@
     </row>
     <row r="3" spans="1:10" ht="43.2">
       <c r="A3" s="67" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8965,10 +8966,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -8979,13 +8980,13 @@
     </row>
     <row r="4" spans="1:10" ht="43.2">
       <c r="A4" s="63" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -8993,10 +8994,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H4" s="65" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9007,26 +9008,26 @@
     </row>
     <row r="5" spans="1:10" ht="43.2">
       <c r="A5" s="67" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9037,13 +9038,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8">
       <c r="A6" s="63" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9054,7 +9055,7 @@
         <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9065,13 +9066,13 @@
     </row>
     <row r="7" spans="1:10" ht="28.8">
       <c r="A7" s="67" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9093,23 +9094,23 @@
     </row>
     <row r="8" spans="1:10" ht="86.4">
       <c r="A8" s="63" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9123,13 +9124,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.8">
       <c r="A9" s="67" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9137,7 +9138,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9151,23 +9152,23 @@
     </row>
     <row r="10" spans="1:10" ht="28.8">
       <c r="A10" s="63" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -9632,36 +9633,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="N1" s="233" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="72">
       <c r="A2" s="44" t="s">
+        <v>658</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>659</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>660</v>
+      </c>
+      <c r="D2" s="78" t="s">
         <v>661</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="E2" s="197" t="s">
         <v>662</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>663</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>664</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>665</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -9675,13 +9676,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1">
       <c r="A3" s="49" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -9691,7 +9692,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -10605,107 +10606,107 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="237" t="s">
+      <c r="A8" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="C8" s="236" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="239" t="s">
+      <c r="E8" s="238" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="236" t="s">
+      <c r="F8" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="236" t="s">
+      <c r="G8" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="236" t="s">
+      <c r="H8" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="235" t="s">
+      <c r="I8" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="235" t="s">
+      <c r="J8" s="239" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="237"/>
-      <c r="B9" s="238"/>
-      <c r="C9" s="237"/>
+      <c r="A9" s="236"/>
+      <c r="B9" s="237"/>
+      <c r="C9" s="236"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="237"/>
-      <c r="B10" s="238"/>
-      <c r="C10" s="237"/>
+      <c r="A10" s="236"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="236"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="239"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="237"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="237"/>
+      <c r="A11" s="236"/>
+      <c r="B11" s="237"/>
+      <c r="C11" s="236"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="239"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
+      <c r="E11" s="238"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="235"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="237"/>
-      <c r="B12" s="238"/>
-      <c r="C12" s="237"/>
+      <c r="A12" s="236"/>
+      <c r="B12" s="237"/>
+      <c r="C12" s="236"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="239"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="239"/>
+      <c r="J12" s="239"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="235"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
     </row>
     <row r="13" spans="1:13" ht="43.2">
       <c r="A13" s="125" t="s">
@@ -10830,7 +10831,7 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -11524,17 +11525,17 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <mergeCells count="11">
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="J8:J12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="F8:F12"/>
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="190" priority="16" operator="equal">
@@ -11792,7 +11793,7 @@
       <c r="M3" s="129"/>
       <c r="N3" s="129"/>
     </row>
-    <row r="4" spans="1:14" s="117" customFormat="1" ht="144">
+    <row r="4" spans="1:14" s="117" customFormat="1" ht="158.4">
       <c r="A4" s="131" t="s">
         <v>13</v>
       </c>
@@ -11806,7 +11807,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>162</v>
+        <v>672</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>35</v>
@@ -11830,25 +11831,25 @@
     </row>
     <row r="5" spans="1:14" ht="57.6">
       <c r="A5" s="125" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="C5" s="134" t="s">
         <v>164</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>165</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H5" s="127" t="s">
         <v>19</v>
@@ -11860,7 +11861,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="130" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -11868,25 +11869,25 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="121" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="121" t="s">
         <v>170</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>171</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>19</v>
@@ -11898,31 +11899,31 @@
         <v>66</v>
       </c>
       <c r="K6" s="106" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L6" s="107"/>
     </row>
     <row r="7" spans="1:14" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>177</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>19</v>
@@ -11934,7 +11935,7 @@
         <v>66</v>
       </c>
       <c r="K7" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -11972,7 +11973,7 @@
         <v>37</v>
       </c>
       <c r="K8" s="106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L8" s="107" t="s">
         <v>39</v>
@@ -11998,7 +11999,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
@@ -12016,7 +12017,7 @@
         <v>37</v>
       </c>
       <c r="K9" s="130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L9" s="129" t="s">
         <v>46</v>
@@ -12042,7 +12043,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
@@ -12066,19 +12067,19 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="125" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="125" t="s">
         <v>185</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>186</v>
       </c>
       <c r="D11" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="140" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>17</v>
@@ -12097,30 +12098,30 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M11" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N11" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>190</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>191</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -12138,31 +12139,31 @@
         <v>66</v>
       </c>
       <c r="K12" s="106" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L12" s="107"/>
     </row>
     <row r="13" spans="1:14" ht="69.75" customHeight="1">
       <c r="A13" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="74" t="s">
         <v>194</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="C13" s="125" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="D13" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="142" t="s">
+      <c r="E13" s="80" t="s">
         <v>197</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>198</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H13" s="127" t="s">
         <v>81</v>
@@ -12174,125 +12175,125 @@
         <v>66</v>
       </c>
       <c r="K13" s="130" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="237" t="s">
+      <c r="A14" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="240" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="237" t="s">
+      <c r="C14" s="236" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="239" t="s">
-        <v>200</v>
-      </c>
-      <c r="F14" s="236" t="s">
+      <c r="E14" s="238" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="236" t="s">
+      <c r="G14" s="235" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="236" t="s">
+      <c r="H14" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="235" t="s">
+      <c r="I14" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="235" t="s">
+      <c r="J14" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="240"/>
-      <c r="L14" s="235"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="239"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="237"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="237"/>
+      <c r="A15" s="236"/>
+      <c r="B15" s="240"/>
+      <c r="C15" s="236"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="239"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="240"/>
-      <c r="L15" s="235"/>
+      <c r="E15" s="238"/>
+      <c r="F15" s="235"/>
+      <c r="G15" s="235"/>
+      <c r="H15" s="235"/>
+      <c r="I15" s="239"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="239"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="237"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="237"/>
+      <c r="A16" s="236"/>
+      <c r="B16" s="240"/>
+      <c r="C16" s="236"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="239"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="235"/>
+      <c r="E16" s="238"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="239"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="237"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="237"/>
+      <c r="A17" s="236"/>
+      <c r="B17" s="240"/>
+      <c r="C17" s="236"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="239"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="235"/>
+      <c r="E17" s="238"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="239"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="237"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="237"/>
+      <c r="A18" s="236"/>
+      <c r="B18" s="240"/>
+      <c r="C18" s="236"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="239"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="235"/>
+      <c r="E18" s="238"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="C19" s="125" t="s">
         <v>202</v>
-      </c>
-      <c r="C19" s="125" t="s">
-        <v>203</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -12310,35 +12311,35 @@
         <v>29</v>
       </c>
       <c r="K19" s="207" t="s">
+        <v>204</v>
+      </c>
+      <c r="L19" s="134" t="s">
         <v>205</v>
-      </c>
-      <c r="L19" s="134" t="s">
-        <v>206</v>
       </c>
       <c r="M19" s="129"/>
       <c r="N19" s="129"/>
     </row>
     <row r="20" spans="1:14" ht="86.4">
       <c r="A20" s="121" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>208</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>209</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H20" s="124" t="s">
         <v>19</v>
@@ -12350,25 +12351,25 @@
         <v>66</v>
       </c>
       <c r="K20" s="106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L20" s="107"/>
     </row>
     <row r="21" spans="1:14" ht="100.8">
       <c r="A21" s="125" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>212</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>213</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>214</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="208" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>35</v>
@@ -12386,7 +12387,7 @@
         <v>37</v>
       </c>
       <c r="K21" s="130" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
@@ -12394,25 +12395,25 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="121" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>218</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>219</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>19</v>
@@ -12425,30 +12426,30 @@
       </c>
       <c r="K22" s="106"/>
       <c r="L22" s="141" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="43.2">
       <c r="A23" s="125" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="125" t="s">
         <v>224</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>225</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="127" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H23" s="127" t="s">
         <v>19</v>
@@ -12460,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="207" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -12468,19 +12469,19 @@
     </row>
     <row r="24" spans="1:14" ht="43.2">
       <c r="A24" s="121" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="C24" s="141" t="s">
         <v>230</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>231</v>
       </c>
       <c r="D24" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>35</v>
@@ -12498,7 +12499,7 @@
         <v>29</v>
       </c>
       <c r="K24" s="106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L24" s="107"/>
     </row>
@@ -12516,7 +12517,7 @@
         <v>85</v>
       </c>
       <c r="E25" s="126" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F25" s="127" t="s">
         <v>17</v>
@@ -12540,27 +12541,27 @@
       <c r="M25" s="129"/>
       <c r="N25" s="129"/>
     </row>
-    <row r="26" spans="1:14" ht="115.2">
+    <row r="26" spans="1:14" ht="144">
       <c r="A26" s="121" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="C26" s="141" t="s">
         <v>236</v>
       </c>
-      <c r="C26" s="141" t="s">
+      <c r="D26" s="122" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="122" t="s">
-        <v>238</v>
-      </c>
       <c r="E26" s="132" t="s">
-        <v>239</v>
+        <v>674</v>
       </c>
       <c r="F26" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H26" s="124" t="s">
         <v>19</v>
@@ -12572,31 +12573,31 @@
         <v>66</v>
       </c>
       <c r="K26" s="106" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L26" s="107"/>
     </row>
     <row r="27" spans="1:14" ht="43.2">
       <c r="A27" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" s="125" t="s">
         <v>242</v>
-      </c>
-      <c r="B27" s="74" t="s">
-        <v>243</v>
-      </c>
-      <c r="C27" s="125" t="s">
-        <v>244</v>
       </c>
       <c r="D27" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="126" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F27" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="127" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H27" s="127" t="s">
         <v>81</v>
@@ -12608,7 +12609,7 @@
         <v>66</v>
       </c>
       <c r="K27" s="130" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L27" s="129"/>
       <c r="M27" s="129"/>
@@ -12616,25 +12617,25 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="121" t="s">
+        <v>246</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="141" t="s">
         <v>248</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="141" t="s">
-        <v>250</v>
       </c>
       <c r="D28" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="132" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F28" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="124" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H28" s="124" t="s">
         <v>81</v>
@@ -12646,7 +12647,7 @@
         <v>66</v>
       </c>
       <c r="K28" s="106" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L28" s="107"/>
     </row>
@@ -12664,7 +12665,7 @@
         <v>16</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F29" s="127" t="s">
         <v>17</v>
@@ -12690,25 +12691,25 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C30" s="121" t="s">
         <v>254</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" s="121" t="s">
-        <v>256</v>
       </c>
       <c r="D30" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="132" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F30" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H30" s="124" t="s">
         <v>81</v>
@@ -12720,31 +12721,31 @@
         <v>66</v>
       </c>
       <c r="K30" s="106" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L30" s="107"/>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="125" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="125" t="s">
         <v>260</v>
-      </c>
-      <c r="B31" s="74" t="s">
-        <v>261</v>
-      </c>
-      <c r="C31" s="125" t="s">
-        <v>262</v>
       </c>
       <c r="D31" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F31" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="127" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H31" s="127" t="s">
         <v>81</v>
@@ -12756,7 +12757,7 @@
         <v>66</v>
       </c>
       <c r="K31" s="130" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L31" s="129"/>
       <c r="M31" s="129"/>
@@ -12764,25 +12765,25 @@
     </row>
     <row r="32" spans="1:14" ht="57.6">
       <c r="A32" s="121" t="s">
+        <v>263</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="C32" s="121" t="s">
         <v>265</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="C32" s="121" t="s">
-        <v>267</v>
       </c>
       <c r="D32" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F32" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="124" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H32" s="124" t="s">
         <v>19</v>
@@ -12794,31 +12795,31 @@
         <v>29</v>
       </c>
       <c r="K32" s="106" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L32" s="107"/>
     </row>
     <row r="33" spans="1:14" ht="57.6">
       <c r="A33" s="125" t="s">
+        <v>269</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="125" t="s">
         <v>271</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="D33" s="142" t="s">
         <v>272</v>
       </c>
-      <c r="C33" s="125" t="s">
+      <c r="E33" s="80" t="s">
         <v>273</v>
-      </c>
-      <c r="D33" s="142" t="s">
-        <v>274</v>
-      </c>
-      <c r="E33" s="80" t="s">
-        <v>275</v>
       </c>
       <c r="F33" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="127" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H33" s="127" t="s">
         <v>19</v>
@@ -12830,7 +12831,7 @@
         <v>66</v>
       </c>
       <c r="K33" s="130" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L33" s="129"/>
       <c r="M33" s="129"/>
@@ -12838,19 +12839,19 @@
     </row>
     <row r="34" spans="1:14" ht="43.2">
       <c r="A34" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="C34" s="121" t="s">
         <v>278</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="C34" s="121" t="s">
-        <v>280</v>
       </c>
       <c r="D34" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="132" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F34" s="124" t="s">
         <v>17</v>
@@ -12868,7 +12869,7 @@
         <v>66</v>
       </c>
       <c r="K34" s="106" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L34" s="107"/>
     </row>
@@ -12886,7 +12887,7 @@
         <v>16</v>
       </c>
       <c r="E35" s="205" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F35" s="127" t="s">
         <v>35</v>
@@ -12916,27 +12917,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="43.2">
+    <row r="36" spans="1:14" ht="57.6">
       <c r="A36" s="121" t="s">
+        <v>282</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C36" s="121" t="s">
         <v>284</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="D36" s="122" t="s">
         <v>285</v>
       </c>
-      <c r="C36" s="121" t="s">
-        <v>286</v>
-      </c>
-      <c r="D36" s="122" t="s">
-        <v>287</v>
-      </c>
       <c r="E36" s="138" t="s">
-        <v>288</v>
+        <v>673</v>
       </c>
       <c r="F36" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="124" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H36" s="124" t="s">
         <v>19</v>
@@ -12954,25 +12955,25 @@
     </row>
     <row r="37" spans="1:14" ht="228" customHeight="1">
       <c r="A37" s="125" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B37" s="74" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C37" s="134" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D37" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="126" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F37" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="128" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H37" s="127" t="s">
         <v>19</v>
@@ -12985,36 +12986,36 @@
       </c>
       <c r="K37" s="130"/>
       <c r="L37" s="129" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M37" s="129" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N37" s="129" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="57.6">
       <c r="A38" s="121" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C38" s="121" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D38" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E38" s="132" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F38" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="128" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H38" s="124" t="s">
         <v>19</v>
@@ -13029,36 +13030,36 @@
         <v>136</v>
       </c>
       <c r="L38" s="107" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M38" s="107" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N38" s="107" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2">
       <c r="A39" s="125" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B39" s="74" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C39" s="125" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D39" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="126" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F39" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="128" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H39" s="127" t="s">
         <v>19</v>
@@ -13071,13 +13072,13 @@
       </c>
       <c r="K39" s="130"/>
       <c r="L39" s="129" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="M39" s="129" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N39" s="129" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
@@ -13094,7 +13095,7 @@
         <v>16</v>
       </c>
       <c r="E40" s="132" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F40" s="124" t="s">
         <v>17</v>
@@ -13118,19 +13119,19 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="125" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B41" s="74" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C41" s="125" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D41" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="74" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F41" s="127" t="s">
         <v>17</v>
@@ -13151,30 +13152,30 @@
         <v>137</v>
       </c>
       <c r="L41" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M41" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N41" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
       <c r="A42" s="121" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C42" s="121" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D42" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="132" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F42" s="124" t="s">
         <v>17</v>
@@ -13195,26 +13196,26 @@
         <v>138</v>
       </c>
       <c r="L42" s="141" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M42" s="107"/>
       <c r="N42" s="107"/>
     </row>
     <row r="43" spans="1:14" ht="28.8">
       <c r="A43" s="125" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B43" s="74" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C43" s="125" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D43" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="205" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F43" s="127" t="s">
         <v>17</v>
@@ -13235,32 +13236,32 @@
         <v>139</v>
       </c>
       <c r="L43" s="134" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M43" s="129"/>
       <c r="N43" s="129"/>
     </row>
     <row r="44" spans="1:14" ht="57.6">
       <c r="A44" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="C44" s="121" t="s">
+        <v>323</v>
+      </c>
+      <c r="D44" s="143" t="s">
         <v>324</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="E44" s="132" t="s">
         <v>325</v>
-      </c>
-      <c r="C44" s="121" t="s">
-        <v>326</v>
-      </c>
-      <c r="D44" s="143" t="s">
-        <v>327</v>
-      </c>
-      <c r="E44" s="132" t="s">
-        <v>328</v>
       </c>
       <c r="F44" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H44" s="124" t="s">
         <v>81</v>
@@ -13292,7 +13293,7 @@
         <v>16</v>
       </c>
       <c r="E45" s="74" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F45" s="127" t="s">
         <v>17</v>
@@ -13313,36 +13314,36 @@
         <v>125</v>
       </c>
       <c r="L45" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M45" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N45" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="57.6">
       <c r="A46" s="121" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C46" s="141" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D46" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="132" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F46" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="124" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H46" s="124" t="s">
         <v>81</v>
@@ -13362,25 +13363,25 @@
     </row>
     <row r="47" spans="1:14" ht="74.25" customHeight="1">
       <c r="A47" s="125" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B47" s="74" t="s">
         <v>127</v>
       </c>
       <c r="C47" s="125" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D47" s="142" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E47" s="74" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F47" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H47" s="127" t="s">
         <v>52</v>
@@ -13412,7 +13413,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="132" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F48" s="124" t="s">
         <v>35</v>
@@ -13438,25 +13439,25 @@
     </row>
     <row r="49" spans="1:14" ht="57.6">
       <c r="A49" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="C49" s="125" t="s">
+        <v>339</v>
+      </c>
+      <c r="D49" s="217" t="s">
         <v>340</v>
       </c>
-      <c r="B49" s="74" t="s">
+      <c r="E49" s="83" t="s">
         <v>341</v>
-      </c>
-      <c r="C49" s="125" t="s">
-        <v>342</v>
-      </c>
-      <c r="D49" s="217" t="s">
-        <v>343</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>344</v>
       </c>
       <c r="F49" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H49" s="127" t="s">
         <v>19</v>
@@ -13476,19 +13477,19 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="121" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C50" s="121" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D50" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="132" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F50" s="124" t="s">
         <v>17</v>
@@ -13514,19 +13515,19 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="125" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B51" s="74" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C51" s="125" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D51" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F51" s="127" t="s">
         <v>17</v>
@@ -13552,13 +13553,13 @@
     </row>
     <row r="52" spans="1:14" ht="84.75" customHeight="1">
       <c r="A52" s="121" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B52" s="35" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C52" s="121" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D52" s="132" t="s">
         <v>16</v>
@@ -13568,7 +13569,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="124" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H52" s="124" t="s">
         <v>19</v>
@@ -13604,17 +13605,17 @@
     <sortCondition ref="A2:A53"/>
   </sortState>
   <mergeCells count="11">
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
     <mergeCell ref="L14:L18"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="J14:J18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F14 F19:F53">
     <cfRule type="cellIs" dxfId="171" priority="8" operator="equal">
@@ -13781,42 +13782,42 @@
         <v>10</v>
       </c>
       <c r="L1" s="223" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="223" t="s">
+        <v>355</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>356</v>
+      </c>
+      <c r="O1" s="108" t="s">
         <v>357</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="P1" s="223" t="s">
         <v>358</v>
       </c>
-      <c r="N1" s="108" t="s">
+      <c r="Q1" s="223" t="s">
         <v>359</v>
       </c>
-      <c r="O1" s="108" t="s">
+      <c r="R1" s="224" t="s">
         <v>360</v>
       </c>
-      <c r="P1" s="223" t="s">
+      <c r="S1" s="224" t="s">
         <v>361</v>
       </c>
-      <c r="Q1" s="223" t="s">
+      <c r="T1" s="224" t="s">
         <v>362</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="U1" s="224" t="s">
         <v>363</v>
       </c>
-      <c r="S1" s="224" t="s">
+      <c r="V1" s="233" t="s">
         <v>364</v>
-      </c>
-      <c r="T1" s="224" t="s">
-        <v>365</v>
-      </c>
-      <c r="U1" s="224" t="s">
-        <v>366</v>
-      </c>
-      <c r="V1" s="233" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="28.8">
       <c r="A2" s="64" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B2" s="157" t="s">
         <v>61</v>
@@ -13825,10 +13826,10 @@
         <v>62</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E2" s="158" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
@@ -13848,25 +13849,25 @@
     </row>
     <row r="3" spans="1:22" ht="115.2">
       <c r="A3" s="68" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D3" s="162" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -13878,7 +13879,7 @@
         <v>66</v>
       </c>
       <c r="K3" s="136" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -13893,19 +13894,19 @@
     </row>
     <row r="4" spans="1:22" ht="129.6">
       <c r="A4" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="157" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="C4" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="64" t="s">
-        <v>214</v>
-      </c>
       <c r="D4" s="71" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E4" s="158" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
@@ -13920,28 +13921,28 @@
         <v>28</v>
       </c>
       <c r="J4" s="160" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K4" s="136" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L4" s="107"/>
     </row>
     <row r="5" spans="1:22" ht="43.2">
       <c r="A5" s="165" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C5" s="165" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F5" s="166" t="s">
         <v>35</v>
@@ -13959,7 +13960,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="136" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -13974,19 +13975,19 @@
     </row>
     <row r="6" spans="1:22" ht="72">
       <c r="A6" s="168" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B6" s="151" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C6" s="168" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F6" s="133" t="s">
         <v>17</v>
@@ -14008,25 +14009,25 @@
     </row>
     <row r="7" spans="1:22" ht="115.2">
       <c r="A7" s="125" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="125" t="s">
+        <v>388</v>
+      </c>
+      <c r="D7" s="171" t="s">
         <v>389</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="E7" s="81" t="s">
         <v>390</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="171" t="s">
-        <v>392</v>
-      </c>
-      <c r="E7" s="81" t="s">
-        <v>393</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -14051,25 +14052,25 @@
     </row>
     <row r="8" spans="1:22" ht="28.8">
       <c r="A8" s="64" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B8" s="157" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C8" s="172" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D8" s="143" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E8" s="135" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F8" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="159" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H8" s="159" t="s">
         <v>81</v>
@@ -14081,13 +14082,13 @@
         <v>29</v>
       </c>
       <c r="K8" s="136" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:22" ht="43.2">
       <c r="A9" s="165" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>77</v>
@@ -14099,13 +14100,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="173" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F9" s="166" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="166" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H9" s="166">
         <v>1</v>
@@ -14117,7 +14118,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="136" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
@@ -14862,45 +14863,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="225" t="s">
+        <v>396</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>397</v>
+      </c>
+      <c r="N1" s="223" t="s">
+        <v>398</v>
+      </c>
+      <c r="O1" s="224" t="s">
         <v>399</v>
       </c>
-      <c r="M1" s="108" t="s">
+      <c r="P1" s="232" t="s">
         <v>400</v>
       </c>
-      <c r="N1" s="223" t="s">
+      <c r="Q1" s="233" t="s">
         <v>401</v>
-      </c>
-      <c r="O1" s="224" t="s">
-        <v>402</v>
-      </c>
-      <c r="P1" s="232" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q1" s="233" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="64.349999999999994" customHeight="1">
       <c r="A2" s="64" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C2" s="172" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>19</v>
@@ -14912,31 +14913,31 @@
         <v>29</v>
       </c>
       <c r="K2" s="156" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L2" s="136"/>
     </row>
     <row r="3" spans="1:17" ht="129.6">
       <c r="A3" s="68" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -14948,7 +14949,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L3" s="75"/>
       <c r="M3" s="61"/>
@@ -14958,25 +14959,25 @@
     </row>
     <row r="4" spans="1:17" ht="28.8">
       <c r="A4" s="64" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H4" s="159">
         <v>1</v>
@@ -14988,7 +14989,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="156" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="L4" s="136"/>
     </row>
@@ -15811,27 +15812,27 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="M1" s="223" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8">
       <c r="A2" s="121" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -15849,36 +15850,36 @@
         <v>37</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L2" s="141" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M2" s="141" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="72">
       <c r="A3" s="125" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C3" s="125" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="85" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="127" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="127">
         <v>1</v>
@@ -15890,7 +15891,7 @@
         <v>37</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -15909,7 +15910,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -15934,25 +15935,25 @@
     </row>
     <row r="5" spans="1:13" ht="43.2">
       <c r="A5" s="125" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H5" s="127">
         <v>1</v>
@@ -15964,32 +15965,32 @@
         <v>29</v>
       </c>
       <c r="K5" s="98" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
     </row>
     <row r="6" spans="1:13" ht="57.6">
       <c r="A6" s="121" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>81</v>
@@ -16001,36 +16002,36 @@
         <v>29</v>
       </c>
       <c r="K6" s="98" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="L6" s="107" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M6" s="107" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="134" t="s">
+        <v>446</v>
+      </c>
+      <c r="D7" s="185" t="s">
         <v>447</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="E7" s="126" t="s">
         <v>448</v>
-      </c>
-      <c r="C7" s="134" t="s">
-        <v>449</v>
-      </c>
-      <c r="D7" s="185" t="s">
-        <v>450</v>
-      </c>
-      <c r="E7" s="126" t="s">
-        <v>451</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="156" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -16042,7 +16043,7 @@
         <v>29</v>
       </c>
       <c r="K7" s="98" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -16061,7 +16062,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>17</v>
@@ -16079,26 +16080,26 @@
         <v>29</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="L8" s="107"/>
       <c r="M8" s="107"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="125" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="74" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" s="187" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="126" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>17</v>
@@ -16116,32 +16117,32 @@
         <v>29</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
     </row>
     <row r="10" spans="1:13" ht="57.6">
       <c r="A10" s="121" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C10" s="141" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H10" s="124" t="s">
         <v>81</v>
@@ -16153,32 +16154,32 @@
         <v>37</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
     <row r="11" spans="1:13" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" s="125" t="s">
+        <v>462</v>
+      </c>
+      <c r="D11" s="154" t="s">
         <v>463</v>
       </c>
-      <c r="B11" s="74" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>466</v>
-      </c>
       <c r="E11" s="126" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H11" s="127">
         <v>1</v>
@@ -16190,7 +16191,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
@@ -16209,7 +16210,7 @@
         <v>85</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -16227,14 +16228,14 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
     <row r="13" spans="1:13" ht="72">
       <c r="A13" s="125" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B13" s="74" t="s">
         <v>90</v>
@@ -16246,13 +16247,13 @@
         <v>92</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H13" s="127">
         <v>1</v>
@@ -16264,32 +16265,32 @@
         <v>37</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="72">
       <c r="A14" s="121" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B14" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="121" t="s">
         <v>176</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>177</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H14" s="124" t="s">
         <v>19</v>
@@ -16301,32 +16302,32 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
     <row r="15" spans="1:13" ht="100.8">
       <c r="A15" s="125" t="s">
+        <v>475</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>476</v>
+      </c>
+      <c r="C15" s="125" t="s">
+        <v>477</v>
+      </c>
+      <c r="D15" s="185" t="s">
+        <v>447</v>
+      </c>
+      <c r="E15" s="80" t="s">
         <v>478</v>
-      </c>
-      <c r="B15" s="74" t="s">
-        <v>479</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>480</v>
-      </c>
-      <c r="D15" s="185" t="s">
-        <v>450</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>481</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="127" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H15" s="127" t="s">
         <v>81</v>
@@ -16338,7 +16339,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
@@ -16373,32 +16374,32 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13" ht="57.6">
       <c r="A17" s="125" t="s">
+        <v>481</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="125" t="s">
+        <v>483</v>
+      </c>
+      <c r="D17" s="185" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="74" t="s">
         <v>484</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>485</v>
-      </c>
-      <c r="C17" s="125" t="s">
-        <v>486</v>
-      </c>
-      <c r="D17" s="185" t="s">
-        <v>450</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>487</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -16410,7 +16411,7 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
@@ -16429,7 +16430,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -16447,24 +16448,24 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
     </row>
     <row r="19" spans="1:13" ht="28.8">
       <c r="A19" s="125" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B19" s="126" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C19" s="125" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D19" s="126"/>
       <c r="E19" s="80" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -16483,10 +16484,10 @@
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="129" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M19" s="129" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="129.6">
@@ -16503,7 +16504,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
@@ -16521,32 +16522,32 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
     <row r="21" spans="1:13" ht="43.2">
       <c r="A21" s="125" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E21" s="81" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H21" s="127" t="s">
         <v>81</v>
@@ -16558,32 +16559,32 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13" ht="57.6">
       <c r="A22" s="121" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>81</v>
@@ -16612,7 +16613,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -16630,7 +16631,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17112,7 +17113,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17129,7 +17130,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17147,7 +17148,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17183,7 +17184,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17203,7 +17204,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17221,31 +17222,31 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L4" s="129"/>
     </row>
     <row r="5" spans="1:12" ht="43.2">
       <c r="A5" s="121" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="C5" s="121" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="121" t="s">
+      <c r="D5" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="122" t="s">
-        <v>197</v>
-      </c>
       <c r="E5" s="135" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>81</v>
@@ -17260,104 +17261,104 @@
       <c r="L5" s="107"/>
     </row>
     <row r="6" spans="1:12" ht="28.8">
-      <c r="A6" s="245" t="s">
+      <c r="A6" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="246" t="s">
+      <c r="B6" s="244" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="245" t="s">
+      <c r="C6" s="243" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="247" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" s="244" t="s">
+      <c r="E6" s="245" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="244" t="s">
+      <c r="G6" s="242" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="244" t="s">
+      <c r="H6" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="242" t="s">
+      <c r="I6" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="235" t="s">
+      <c r="J6" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="243" t="s">
-        <v>508</v>
-      </c>
-      <c r="L6" s="242"/>
+      <c r="K6" s="247" t="s">
+        <v>505</v>
+      </c>
+      <c r="L6" s="246"/>
     </row>
     <row r="7" spans="1:12" ht="28.8">
-      <c r="A7" s="245"/>
-      <c r="B7" s="246"/>
-      <c r="C7" s="245"/>
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="243"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="247"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="242"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="246"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="245"/>
+      <c r="A8" s="243"/>
+      <c r="B8" s="244"/>
+      <c r="C8" s="243"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="247"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="243"/>
-      <c r="L8" s="242"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="247"/>
+      <c r="L8" s="246"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="245"/>
-      <c r="B9" s="246"/>
-      <c r="C9" s="245"/>
+      <c r="A9" s="243"/>
+      <c r="B9" s="244"/>
+      <c r="C9" s="243"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="247"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="243"/>
-      <c r="L9" s="242"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="246"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="245"/>
-      <c r="B10" s="246"/>
-      <c r="C10" s="245"/>
+      <c r="A10" s="243"/>
+      <c r="B10" s="244"/>
+      <c r="C10" s="243"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="247"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="243"/>
-      <c r="L10" s="242"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="247"/>
+      <c r="L10" s="246"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="121" t="s">
@@ -17373,7 +17374,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -17391,7 +17392,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L11" s="107"/>
     </row>
@@ -17409,7 +17410,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -17427,7 +17428,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -17447,7 +17448,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
@@ -17465,7 +17466,7 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L13" s="107"/>
     </row>
@@ -17483,7 +17484,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -17501,10 +17502,10 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L14" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -17521,7 +17522,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -17666,17 +17667,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
   <mergeCells count="11">
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
@@ -17820,7 +17821,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="92.4">
@@ -17837,7 +17838,7 @@
         <v>152</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
@@ -17855,7 +17856,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -17893,25 +17894,25 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B4" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="121" t="s">
         <v>176</v>
-      </c>
-      <c r="C4" s="121" t="s">
-        <v>177</v>
       </c>
       <c r="D4" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H4" s="124" t="s">
         <v>19</v>
@@ -18043,7 +18044,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18061,31 +18062,31 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="43.2">
       <c r="A9" s="125" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H9" s="127">
         <v>1</v>
@@ -18097,31 +18098,31 @@
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
       <c r="A10" s="121" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C10" s="121" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H10" s="133">
         <v>1</v>
@@ -18133,29 +18134,29 @@
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L10" s="107"/>
     </row>
     <row r="11" spans="1:12" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" s="134" t="s">
+        <v>462</v>
+      </c>
+      <c r="D11" s="154" t="s">
         <v>463</v>
-      </c>
-      <c r="B11" s="74" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="134" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>466</v>
       </c>
       <c r="E11" s="126"/>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -18171,13 +18172,13 @@
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="121" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C12" s="121" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18187,7 +18188,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H12" s="124" t="s">
         <v>19</v>
@@ -18203,19 +18204,19 @@
     </row>
     <row r="13" spans="1:12" ht="57.6">
       <c r="A13" s="191" t="s">
+        <v>211</v>
+      </c>
+      <c r="B13" s="74" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="C13" s="134" t="s">
         <v>213</v>
-      </c>
-      <c r="C13" s="134" t="s">
-        <v>214</v>
       </c>
       <c r="D13" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18237,13 +18238,13 @@
     </row>
     <row r="14" spans="1:12" ht="28.8">
       <c r="A14" s="121" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="121" t="s">
         <v>230</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>231</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
@@ -18269,19 +18270,19 @@
     </row>
     <row r="15" spans="1:12" ht="57.6">
       <c r="A15" s="125" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B15" s="74" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C15" s="125" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18315,7 +18316,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18349,7 +18350,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
@@ -18367,7 +18368,7 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L17" s="129"/>
     </row>
@@ -18385,7 +18386,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -18407,13 +18408,13 @@
     </row>
     <row r="19" spans="1:12" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="134" t="s">
         <v>265</v>
-      </c>
-      <c r="B19" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="C19" s="134" t="s">
-        <v>267</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
@@ -18423,7 +18424,7 @@
         <v>17</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>19</v>
@@ -18436,7 +18437,7 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="43.2">
@@ -18453,7 +18454,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -18477,19 +18478,19 @@
     </row>
     <row r="21" spans="1:12" ht="57.6">
       <c r="A21" s="125" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -18507,33 +18508,33 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L21" s="192" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="43.2">
       <c r="A22" s="121" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B22" s="35" t="s">
         <v>127</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D22" s="143" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>52</v>
@@ -18561,7 +18562,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -18579,7 +18580,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L23" s="195"/>
     </row>
@@ -19062,15 +19063,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -19313,6 +19305,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19326,14 +19327,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19352,6 +19345,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
   <ds:schemaRefs>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A5D35E6-B235-466B-BAC2-6DE286A26D1D}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB2FDFB2-6BD5-4989-9906-EC23F51E3B08}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-12765" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2611,14 +2611,14 @@
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
   </si>
   <si>
-    <t>One (or many) category or sub-category of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
-Example value could be: dpv:ResearchAndDevelopment.</t>
-  </si>
-  <si>
     <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
-This property should always be filled if the data contains personal data and the applicable legislation is GDPR.
+This property should always be filled if the dataset contains personal data and the applicable legislation is GDPR.
 Example value for this property could be: dpv:Consent</t>
+  </si>
+  <si>
+    <t>One (or many) categoiesy or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
+Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
 </sst>
 </file>
@@ -3766,24 +3766,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3797,12 +3803,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10606,107 +10606,107 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="236" t="s">
+      <c r="A8" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="237" t="s">
+      <c r="B8" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="236" t="s">
+      <c r="C8" s="238" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="238" t="s">
+      <c r="E8" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="235" t="s">
+      <c r="F8" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="235" t="s">
+      <c r="G8" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="235" t="s">
+      <c r="H8" s="237" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="239" t="s">
+      <c r="I8" s="235" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="239" t="s">
+      <c r="J8" s="235" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="239"/>
-      <c r="M8" s="239"/>
+      <c r="L8" s="235"/>
+      <c r="M8" s="235"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="236"/>
-      <c r="B9" s="237"/>
-      <c r="C9" s="236"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="238"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="238"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="239"/>
-      <c r="M9" s="239"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="235"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="236"/>
-      <c r="B10" s="237"/>
-      <c r="C10" s="236"/>
+      <c r="A10" s="238"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="238"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="238"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="235"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="236"/>
-      <c r="B11" s="237"/>
-      <c r="C11" s="236"/>
+      <c r="A11" s="238"/>
+      <c r="B11" s="241"/>
+      <c r="C11" s="238"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="238"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="237"/>
+      <c r="G11" s="237"/>
+      <c r="H11" s="237"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="239"/>
+      <c r="L11" s="235"/>
+      <c r="M11" s="235"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="236"/>
-      <c r="B12" s="237"/>
-      <c r="C12" s="236"/>
+      <c r="A12" s="238"/>
+      <c r="B12" s="241"/>
+      <c r="C12" s="238"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="238"/>
-      <c r="F12" s="235"/>
-      <c r="G12" s="235"/>
-      <c r="H12" s="235"/>
-      <c r="I12" s="239"/>
-      <c r="J12" s="239"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="237"/>
+      <c r="H12" s="237"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="239"/>
-      <c r="M12" s="239"/>
+      <c r="L12" s="235"/>
+      <c r="M12" s="235"/>
     </row>
     <row r="13" spans="1:13" ht="43.2">
       <c r="A13" s="125" t="s">
@@ -11525,17 +11525,17 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <mergeCells count="11">
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="J8:J12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="F8:F12"/>
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="190" priority="16" operator="equal">
@@ -12182,102 +12182,102 @@
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="236" t="s">
+      <c r="A14" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="240" t="s">
+      <c r="B14" s="239" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="236" t="s">
+      <c r="C14" s="238" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="238" t="s">
+      <c r="E14" s="240" t="s">
         <v>199</v>
       </c>
-      <c r="F14" s="235" t="s">
+      <c r="F14" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="235" t="s">
+      <c r="G14" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="235" t="s">
+      <c r="H14" s="237" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="239" t="s">
+      <c r="I14" s="235" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="239" t="s">
+      <c r="J14" s="235" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="241"/>
-      <c r="L14" s="239"/>
+      <c r="K14" s="236"/>
+      <c r="L14" s="235"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="236"/>
-      <c r="B15" s="240"/>
-      <c r="C15" s="236"/>
+      <c r="A15" s="238"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="238"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="238"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
-      <c r="H15" s="235"/>
-      <c r="I15" s="239"/>
-      <c r="J15" s="239"/>
-      <c r="K15" s="241"/>
-      <c r="L15" s="239"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="237"/>
+      <c r="G15" s="237"/>
+      <c r="H15" s="237"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="235"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="236"/>
-      <c r="B16" s="240"/>
-      <c r="C16" s="236"/>
+      <c r="A16" s="238"/>
+      <c r="B16" s="239"/>
+      <c r="C16" s="238"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="238"/>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
-      <c r="K16" s="241"/>
-      <c r="L16" s="239"/>
+      <c r="E16" s="240"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="235"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="236"/>
-      <c r="B17" s="240"/>
-      <c r="C17" s="236"/>
+      <c r="A17" s="238"/>
+      <c r="B17" s="239"/>
+      <c r="C17" s="238"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="238"/>
-      <c r="F17" s="235"/>
-      <c r="G17" s="235"/>
-      <c r="H17" s="235"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="239"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="237"/>
+      <c r="G17" s="237"/>
+      <c r="H17" s="237"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="235"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="236"/>
-      <c r="B18" s="240"/>
-      <c r="C18" s="236"/>
+      <c r="A18" s="238"/>
+      <c r="B18" s="239"/>
+      <c r="C18" s="238"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="238"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="239"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="237"/>
+      <c r="G18" s="237"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
@@ -12555,7 +12555,7 @@
         <v>237</v>
       </c>
       <c r="E26" s="132" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F26" s="124" t="s">
         <v>17</v>
@@ -12931,7 +12931,7 @@
         <v>285</v>
       </c>
       <c r="E36" s="138" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F36" s="124" t="s">
         <v>17</v>
@@ -13605,17 +13605,17 @@
     <sortCondition ref="A2:A53"/>
   </sortState>
   <mergeCells count="11">
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="E14:E18"/>
     <mergeCell ref="L14:L18"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="J14:J18"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F14 F19:F53">
     <cfRule type="cellIs" dxfId="171" priority="8" operator="equal">
@@ -17261,104 +17261,104 @@
       <c r="L5" s="107"/>
     </row>
     <row r="6" spans="1:12" ht="28.8">
-      <c r="A6" s="243" t="s">
+      <c r="A6" s="245" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="244" t="s">
+      <c r="B6" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="243" t="s">
+      <c r="C6" s="245" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="245" t="s">
+      <c r="E6" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="242" t="s">
+      <c r="F6" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="242" t="s">
+      <c r="G6" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="242" t="s">
+      <c r="H6" s="244" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="246" t="s">
+      <c r="I6" s="242" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="239" t="s">
+      <c r="J6" s="235" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="247" t="s">
+      <c r="K6" s="243" t="s">
         <v>505</v>
       </c>
-      <c r="L6" s="246"/>
+      <c r="L6" s="242"/>
     </row>
     <row r="7" spans="1:12" ht="28.8">
-      <c r="A7" s="243"/>
-      <c r="B7" s="244"/>
-      <c r="C7" s="243"/>
+      <c r="A7" s="245"/>
+      <c r="B7" s="246"/>
+      <c r="C7" s="245"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="245"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="242"/>
-      <c r="I7" s="246"/>
-      <c r="J7" s="239"/>
-      <c r="K7" s="247"/>
-      <c r="L7" s="246"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="244"/>
+      <c r="I7" s="242"/>
+      <c r="J7" s="235"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="242"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="243"/>
-      <c r="B8" s="244"/>
-      <c r="C8" s="243"/>
+      <c r="A8" s="245"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="245"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="245"/>
-      <c r="F8" s="242"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="242"/>
-      <c r="I8" s="246"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="247"/>
-      <c r="L8" s="246"/>
+      <c r="E8" s="247"/>
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="244"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="243"/>
+      <c r="L8" s="242"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="243"/>
-      <c r="B9" s="244"/>
-      <c r="C9" s="243"/>
+      <c r="A9" s="245"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="245"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="246"/>
+      <c r="E9" s="247"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="242"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="243"/>
-      <c r="B10" s="244"/>
-      <c r="C10" s="243"/>
+      <c r="A10" s="245"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="245"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="246"/>
+      <c r="E10" s="247"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="244"/>
+      <c r="H10" s="244"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="242"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="121" t="s">
@@ -17667,17 +17667,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
   <mergeCells count="11">
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="J6:J10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
@@ -19063,6 +19063,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -19305,15 +19314,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19327,6 +19327,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19345,14 +19353,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
   <ds:schemaRefs>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75DD3E37-514C-4AE3-A673-1E268BD8AFB0}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB2FDFB2-6BD5-4989-9906-EC23F51E3B08}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-12765" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -583,12 +583,6 @@
     <t>If available, add URI to analytics distribution here</t>
   </si>
   <si>
-    <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
-For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
-As multiple legislations may apply to the resource the maximum cardinality is not limited.
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
-  </si>
-  <si>
     <t>code values</t>
   </si>
   <si>
@@ -841,11 +835,6 @@
     <t>https://w3c.github.io/dpv/2.0/dpv/modules/legal_basis.html#vocab-legal-basis</t>
   </si>
   <si>
-    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
-Example value for this property could be: dpv:Consent</t>
-  </si>
-  <si>
     <t>dpv:LegalBasis</t>
   </si>
   <si>
@@ -989,10 +978,6 @@
   </si>
   <si>
     <t>https://w3c.github.io/dpv/2.1/dpv/#vocab-purposes</t>
-  </si>
-  <si>
-    <t>One (or many) category or sub-category of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column).
-Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
   <si>
     <t>dpv:Purpose</t>
@@ -2618,6 +2603,22 @@
   </si>
   <si>
     <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL from the File Type vocabulary.</t>
+  </si>
+  <si>
+    <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
+For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
+As multiple legislations may apply to the resource the maximum cardinality is not limited. Note that the relation with other legislations is complex and is being looked into by legal experts.
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
+  </si>
+  <si>
+    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
+This property should always be filled if the dataset contains personal data and the applicable legislation is GDPR.
+Example value for this property could be: dpv:Consent</t>
+  </si>
+  <si>
+    <t>One (or many) categoiesy or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
+Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
 </sst>
 </file>
@@ -3767,22 +3768,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7438,33 +7439,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>554</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>555</v>
+      </c>
+      <c r="N1" s="227" t="s">
+        <v>556</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>557</v>
-      </c>
-      <c r="M1" s="226" t="s">
-        <v>558</v>
-      </c>
-      <c r="N1" s="227" t="s">
-        <v>559</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="72">
       <c r="A2" s="196" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7473,7 +7474,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7488,13 +7489,13 @@
     </row>
     <row r="3" spans="1:15" ht="28.8">
       <c r="A3" s="68" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7633,36 +7634,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>566</v>
+      </c>
+      <c r="M1" s="220" t="s">
+        <v>567</v>
+      </c>
+      <c r="N1" s="226" t="s">
+        <v>568</v>
+      </c>
+      <c r="O1" s="230" t="s">
         <v>569</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="P1" s="227" t="s">
         <v>570</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="Q1" s="231" t="s">
         <v>571</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="R1" s="233" t="s">
         <v>572</v>
-      </c>
-      <c r="P1" s="227" t="s">
-        <v>573</v>
-      </c>
-      <c r="Q1" s="231" t="s">
-        <v>574</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="58" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -7690,13 +7691,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="48" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8358,33 +8359,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>579</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>580</v>
+      </c>
+      <c r="N1" s="227" t="s">
+        <v>581</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>582</v>
-      </c>
-      <c r="M1" s="226" t="s">
-        <v>583</v>
-      </c>
-      <c r="N1" s="227" t="s">
-        <v>584</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2">
       <c r="A2" s="84" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8414,25 +8415,25 @@
     </row>
     <row r="3" spans="1:15" ht="129.6">
       <c r="A3" s="48" t="s">
+        <v>587</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>588</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>589</v>
+      </c>
+      <c r="D3" s="234" t="s">
         <v>590</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>591</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>592</v>
-      </c>
-      <c r="D3" s="234" t="s">
-        <v>593</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>594</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8552,39 +8553,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>592</v>
+      </c>
+      <c r="M1" s="229" t="s">
+        <v>593</v>
+      </c>
+      <c r="N1" s="228" t="s">
+        <v>594</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>595</v>
-      </c>
-      <c r="M1" s="229" t="s">
-        <v>596</v>
-      </c>
-      <c r="N1" s="228" t="s">
-        <v>597</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="158.4">
       <c r="A2" s="84" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="115" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>52</v>
@@ -8599,25 +8600,25 @@
     </row>
     <row r="3" spans="1:15" ht="43.2">
       <c r="A3" s="48" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>52</v>
@@ -8737,39 +8738,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>603</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>604</v>
+      </c>
+      <c r="N1" s="227" t="s">
+        <v>605</v>
+      </c>
+      <c r="O1" s="233" t="s">
         <v>606</v>
-      </c>
-      <c r="M1" s="226" t="s">
-        <v>607</v>
-      </c>
-      <c r="N1" s="227" t="s">
-        <v>608</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="100.8">
       <c r="A2" s="84" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>81</v>
@@ -8784,25 +8785,25 @@
     </row>
     <row r="3" spans="1:15" ht="57.6">
       <c r="A3" s="48" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8900,7 +8901,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -8923,13 +8924,13 @@
     </row>
     <row r="2" spans="1:10" ht="28.8">
       <c r="A2" s="63" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -8937,7 +8938,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -8951,13 +8952,13 @@
     </row>
     <row r="3" spans="1:10" ht="43.2">
       <c r="A3" s="67" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8965,10 +8966,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -8979,13 +8980,13 @@
     </row>
     <row r="4" spans="1:10" ht="43.2">
       <c r="A4" s="63" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -8993,10 +8994,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H4" s="65" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9007,26 +9008,26 @@
     </row>
     <row r="5" spans="1:10" ht="43.2">
       <c r="A5" s="67" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9037,13 +9038,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8">
       <c r="A6" s="63" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9054,7 +9055,7 @@
         <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9065,13 +9066,13 @@
     </row>
     <row r="7" spans="1:10" ht="28.8">
       <c r="A7" s="67" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9093,23 +9094,23 @@
     </row>
     <row r="8" spans="1:10" ht="86.4">
       <c r="A8" s="63" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9123,13 +9124,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.8">
       <c r="A9" s="67" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9137,7 +9138,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9151,23 +9152,23 @@
     </row>
     <row r="10" spans="1:10" ht="28.8">
       <c r="A10" s="63" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -9632,36 +9633,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="N1" s="233" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="72">
       <c r="A2" s="44" t="s">
+        <v>658</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>659</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>660</v>
+      </c>
+      <c r="D2" s="78" t="s">
         <v>661</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="E2" s="197" t="s">
         <v>662</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>663</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>664</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>665</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -9675,13 +9676,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1">
       <c r="A3" s="49" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -9691,7 +9692,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -10605,28 +10606,28 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="237" t="s">
+      <c r="A8" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="C8" s="238" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="239" t="s">
+      <c r="E8" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="236" t="s">
+      <c r="F8" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="236" t="s">
+      <c r="G8" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="236" t="s">
+      <c r="H8" s="237" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="235" t="s">
@@ -10640,16 +10641,16 @@
       <c r="M8" s="235"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="237"/>
-      <c r="B9" s="238"/>
-      <c r="C9" s="237"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="238"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
       <c r="I9" s="235"/>
       <c r="J9" s="235"/>
       <c r="K9" s="137"/>
@@ -10657,16 +10658,16 @@
       <c r="M9" s="235"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="237"/>
-      <c r="B10" s="238"/>
-      <c r="C10" s="237"/>
+      <c r="A10" s="238"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="238"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="239"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
       <c r="I10" s="235"/>
       <c r="J10" s="235"/>
       <c r="K10" s="137"/>
@@ -10674,16 +10675,16 @@
       <c r="M10" s="235"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="237"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="237"/>
+      <c r="A11" s="238"/>
+      <c r="B11" s="241"/>
+      <c r="C11" s="238"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="239"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="237"/>
+      <c r="G11" s="237"/>
+      <c r="H11" s="237"/>
       <c r="I11" s="235"/>
       <c r="J11" s="235"/>
       <c r="K11" s="153"/>
@@ -10691,16 +10692,16 @@
       <c r="M11" s="235"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="237"/>
-      <c r="B12" s="238"/>
-      <c r="C12" s="237"/>
+      <c r="A12" s="238"/>
+      <c r="B12" s="241"/>
+      <c r="C12" s="238"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="239"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="237"/>
+      <c r="H12" s="237"/>
       <c r="I12" s="235"/>
       <c r="J12" s="235"/>
       <c r="K12" s="137"/>
@@ -10830,7 +10831,7 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -11792,7 +11793,7 @@
       <c r="M3" s="129"/>
       <c r="N3" s="129"/>
     </row>
-    <row r="4" spans="1:14" s="117" customFormat="1" ht="144">
+    <row r="4" spans="1:14" s="117" customFormat="1" ht="158.4">
       <c r="A4" s="131" t="s">
         <v>13</v>
       </c>
@@ -11806,7 +11807,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>162</v>
+        <v>672</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>35</v>
@@ -11830,25 +11831,25 @@
     </row>
     <row r="5" spans="1:14" ht="57.6">
       <c r="A5" s="125" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="C5" s="134" t="s">
         <v>164</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>165</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H5" s="127" t="s">
         <v>19</v>
@@ -11860,7 +11861,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="130" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -11868,25 +11869,25 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="121" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="121" t="s">
         <v>170</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>171</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>19</v>
@@ -11898,31 +11899,31 @@
         <v>66</v>
       </c>
       <c r="K6" s="106" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L6" s="107"/>
     </row>
     <row r="7" spans="1:14" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>177</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>19</v>
@@ -11934,7 +11935,7 @@
         <v>66</v>
       </c>
       <c r="K7" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -11972,7 +11973,7 @@
         <v>37</v>
       </c>
       <c r="K8" s="106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L8" s="107" t="s">
         <v>39</v>
@@ -11998,7 +11999,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
@@ -12016,7 +12017,7 @@
         <v>37</v>
       </c>
       <c r="K9" s="130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L9" s="129" t="s">
         <v>46</v>
@@ -12042,7 +12043,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
@@ -12066,19 +12067,19 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="125" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="125" t="s">
         <v>185</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>186</v>
       </c>
       <c r="D11" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="140" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>17</v>
@@ -12097,30 +12098,30 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M11" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N11" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>190</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>191</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -12138,31 +12139,31 @@
         <v>66</v>
       </c>
       <c r="K12" s="106" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L12" s="107"/>
     </row>
     <row r="13" spans="1:14" ht="69.75" customHeight="1">
       <c r="A13" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="74" t="s">
         <v>194</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="C13" s="125" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="D13" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="142" t="s">
+      <c r="E13" s="80" t="s">
         <v>197</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>198</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H13" s="127" t="s">
         <v>81</v>
@@ -12174,35 +12175,35 @@
         <v>66</v>
       </c>
       <c r="K13" s="130" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="237" t="s">
+      <c r="A14" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="239" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="237" t="s">
+      <c r="C14" s="238" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="239" t="s">
-        <v>200</v>
-      </c>
-      <c r="F14" s="236" t="s">
+      <c r="E14" s="240" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="236" t="s">
+      <c r="G14" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="236" t="s">
+      <c r="H14" s="237" t="s">
         <v>19</v>
       </c>
       <c r="I14" s="235" t="s">
@@ -12211,88 +12212,88 @@
       <c r="J14" s="235" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="240"/>
+      <c r="K14" s="236"/>
       <c r="L14" s="235"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="237"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="237"/>
+      <c r="A15" s="238"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="238"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="239"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="237"/>
+      <c r="G15" s="237"/>
+      <c r="H15" s="237"/>
       <c r="I15" s="235"/>
       <c r="J15" s="235"/>
-      <c r="K15" s="240"/>
+      <c r="K15" s="236"/>
       <c r="L15" s="235"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="237"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="237"/>
+      <c r="A16" s="238"/>
+      <c r="B16" s="239"/>
+      <c r="C16" s="238"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="239"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
+      <c r="E16" s="240"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
       <c r="I16" s="235"/>
       <c r="J16" s="235"/>
-      <c r="K16" s="240"/>
+      <c r="K16" s="236"/>
       <c r="L16" s="235"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="237"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="237"/>
+      <c r="A17" s="238"/>
+      <c r="B17" s="239"/>
+      <c r="C17" s="238"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="239"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="237"/>
+      <c r="G17" s="237"/>
+      <c r="H17" s="237"/>
       <c r="I17" s="235"/>
       <c r="J17" s="235"/>
-      <c r="K17" s="240"/>
+      <c r="K17" s="236"/>
       <c r="L17" s="235"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="237"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="237"/>
+      <c r="A18" s="238"/>
+      <c r="B18" s="239"/>
+      <c r="C18" s="238"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="239"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="237"/>
+      <c r="G18" s="237"/>
+      <c r="H18" s="237"/>
       <c r="I18" s="235"/>
       <c r="J18" s="235"/>
-      <c r="K18" s="240"/>
+      <c r="K18" s="236"/>
       <c r="L18" s="235"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="C19" s="125" t="s">
         <v>202</v>
-      </c>
-      <c r="C19" s="125" t="s">
-        <v>203</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -12310,35 +12311,35 @@
         <v>29</v>
       </c>
       <c r="K19" s="207" t="s">
+        <v>204</v>
+      </c>
+      <c r="L19" s="134" t="s">
         <v>205</v>
-      </c>
-      <c r="L19" s="134" t="s">
-        <v>206</v>
       </c>
       <c r="M19" s="129"/>
       <c r="N19" s="129"/>
     </row>
     <row r="20" spans="1:14" ht="86.4">
       <c r="A20" s="121" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>208</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>209</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H20" s="124" t="s">
         <v>19</v>
@@ -12350,25 +12351,25 @@
         <v>66</v>
       </c>
       <c r="K20" s="106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L20" s="107"/>
     </row>
     <row r="21" spans="1:14" ht="100.8">
       <c r="A21" s="125" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>212</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>213</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>214</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="208" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>35</v>
@@ -12386,7 +12387,7 @@
         <v>37</v>
       </c>
       <c r="K21" s="130" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
@@ -12394,25 +12395,25 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="121" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>218</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>219</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>19</v>
@@ -12425,30 +12426,30 @@
       </c>
       <c r="K22" s="106"/>
       <c r="L22" s="141" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="43.2">
       <c r="A23" s="125" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="125" t="s">
         <v>224</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>225</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="127" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H23" s="127" t="s">
         <v>19</v>
@@ -12460,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="207" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -12468,19 +12469,19 @@
     </row>
     <row r="24" spans="1:14" ht="43.2">
       <c r="A24" s="121" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="C24" s="141" t="s">
         <v>230</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>231</v>
       </c>
       <c r="D24" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>35</v>
@@ -12498,7 +12499,7 @@
         <v>29</v>
       </c>
       <c r="K24" s="106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L24" s="107"/>
     </row>
@@ -12516,7 +12517,7 @@
         <v>85</v>
       </c>
       <c r="E25" s="126" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F25" s="127" t="s">
         <v>17</v>
@@ -12540,27 +12541,27 @@
       <c r="M25" s="129"/>
       <c r="N25" s="129"/>
     </row>
-    <row r="26" spans="1:14" ht="115.2">
+    <row r="26" spans="1:14" ht="144">
       <c r="A26" s="121" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="C26" s="141" t="s">
         <v>236</v>
       </c>
-      <c r="C26" s="141" t="s">
+      <c r="D26" s="122" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="122" t="s">
-        <v>238</v>
-      </c>
       <c r="E26" s="132" t="s">
-        <v>239</v>
+        <v>673</v>
       </c>
       <c r="F26" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H26" s="124" t="s">
         <v>19</v>
@@ -12572,31 +12573,31 @@
         <v>66</v>
       </c>
       <c r="K26" s="106" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L26" s="107"/>
     </row>
     <row r="27" spans="1:14" ht="43.2">
       <c r="A27" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" s="125" t="s">
         <v>242</v>
-      </c>
-      <c r="B27" s="74" t="s">
-        <v>243</v>
-      </c>
-      <c r="C27" s="125" t="s">
-        <v>244</v>
       </c>
       <c r="D27" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="126" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F27" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="127" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H27" s="127" t="s">
         <v>81</v>
@@ -12608,7 +12609,7 @@
         <v>66</v>
       </c>
       <c r="K27" s="130" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L27" s="129"/>
       <c r="M27" s="129"/>
@@ -12616,25 +12617,25 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="121" t="s">
+        <v>246</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="141" t="s">
         <v>248</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="141" t="s">
-        <v>250</v>
       </c>
       <c r="D28" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="132" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F28" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="124" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H28" s="124" t="s">
         <v>81</v>
@@ -12646,7 +12647,7 @@
         <v>66</v>
       </c>
       <c r="K28" s="106" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L28" s="107"/>
     </row>
@@ -12664,7 +12665,7 @@
         <v>16</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F29" s="127" t="s">
         <v>17</v>
@@ -12690,25 +12691,25 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C30" s="121" t="s">
         <v>254</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" s="121" t="s">
-        <v>256</v>
       </c>
       <c r="D30" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="132" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F30" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H30" s="124" t="s">
         <v>81</v>
@@ -12720,31 +12721,31 @@
         <v>66</v>
       </c>
       <c r="K30" s="106" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L30" s="107"/>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="125" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="125" t="s">
         <v>260</v>
-      </c>
-      <c r="B31" s="74" t="s">
-        <v>261</v>
-      </c>
-      <c r="C31" s="125" t="s">
-        <v>262</v>
       </c>
       <c r="D31" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F31" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="127" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H31" s="127" t="s">
         <v>81</v>
@@ -12756,7 +12757,7 @@
         <v>66</v>
       </c>
       <c r="K31" s="130" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L31" s="129"/>
       <c r="M31" s="129"/>
@@ -12764,25 +12765,25 @@
     </row>
     <row r="32" spans="1:14" ht="57.6">
       <c r="A32" s="121" t="s">
+        <v>263</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="C32" s="121" t="s">
         <v>265</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="C32" s="121" t="s">
-        <v>267</v>
       </c>
       <c r="D32" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F32" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="124" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H32" s="124" t="s">
         <v>19</v>
@@ -12794,31 +12795,31 @@
         <v>29</v>
       </c>
       <c r="K32" s="106" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L32" s="107"/>
     </row>
     <row r="33" spans="1:14" ht="57.6">
       <c r="A33" s="125" t="s">
+        <v>269</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="125" t="s">
         <v>271</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="D33" s="142" t="s">
         <v>272</v>
       </c>
-      <c r="C33" s="125" t="s">
+      <c r="E33" s="80" t="s">
         <v>273</v>
-      </c>
-      <c r="D33" s="142" t="s">
-        <v>274</v>
-      </c>
-      <c r="E33" s="80" t="s">
-        <v>275</v>
       </c>
       <c r="F33" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="127" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H33" s="127" t="s">
         <v>19</v>
@@ -12830,7 +12831,7 @@
         <v>66</v>
       </c>
       <c r="K33" s="130" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L33" s="129"/>
       <c r="M33" s="129"/>
@@ -12838,19 +12839,19 @@
     </row>
     <row r="34" spans="1:14" ht="43.2">
       <c r="A34" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="C34" s="121" t="s">
         <v>278</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="C34" s="121" t="s">
-        <v>280</v>
       </c>
       <c r="D34" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="132" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F34" s="124" t="s">
         <v>17</v>
@@ -12868,7 +12869,7 @@
         <v>66</v>
       </c>
       <c r="K34" s="106" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L34" s="107"/>
     </row>
@@ -12886,7 +12887,7 @@
         <v>16</v>
       </c>
       <c r="E35" s="205" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F35" s="127" t="s">
         <v>35</v>
@@ -12916,27 +12917,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="43.2">
+    <row r="36" spans="1:14" ht="57.6">
       <c r="A36" s="121" t="s">
+        <v>282</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C36" s="121" t="s">
         <v>284</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="D36" s="122" t="s">
         <v>285</v>
       </c>
-      <c r="C36" s="121" t="s">
-        <v>286</v>
-      </c>
-      <c r="D36" s="122" t="s">
-        <v>287</v>
-      </c>
       <c r="E36" s="138" t="s">
-        <v>288</v>
+        <v>674</v>
       </c>
       <c r="F36" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="124" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H36" s="124" t="s">
         <v>19</v>
@@ -12954,25 +12955,25 @@
     </row>
     <row r="37" spans="1:14" ht="228" customHeight="1">
       <c r="A37" s="125" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B37" s="74" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C37" s="134" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D37" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="126" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F37" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="128" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H37" s="127" t="s">
         <v>19</v>
@@ -12985,36 +12986,36 @@
       </c>
       <c r="K37" s="130"/>
       <c r="L37" s="129" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M37" s="129" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N37" s="129" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="57.6">
       <c r="A38" s="121" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C38" s="121" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D38" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E38" s="132" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F38" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="128" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H38" s="124" t="s">
         <v>19</v>
@@ -13029,36 +13030,36 @@
         <v>136</v>
       </c>
       <c r="L38" s="107" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M38" s="107" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N38" s="107" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2">
       <c r="A39" s="125" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B39" s="74" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C39" s="125" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D39" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="126" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F39" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="128" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H39" s="127" t="s">
         <v>19</v>
@@ -13071,13 +13072,13 @@
       </c>
       <c r="K39" s="130"/>
       <c r="L39" s="129" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="M39" s="129" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N39" s="129" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
@@ -13094,7 +13095,7 @@
         <v>16</v>
       </c>
       <c r="E40" s="132" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F40" s="124" t="s">
         <v>17</v>
@@ -13118,19 +13119,19 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="125" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B41" s="74" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C41" s="125" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D41" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="74" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F41" s="127" t="s">
         <v>17</v>
@@ -13151,30 +13152,30 @@
         <v>137</v>
       </c>
       <c r="L41" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M41" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N41" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
       <c r="A42" s="121" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C42" s="121" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D42" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="132" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F42" s="124" t="s">
         <v>17</v>
@@ -13195,26 +13196,26 @@
         <v>138</v>
       </c>
       <c r="L42" s="141" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M42" s="107"/>
       <c r="N42" s="107"/>
     </row>
     <row r="43" spans="1:14" ht="28.8">
       <c r="A43" s="125" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B43" s="74" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C43" s="125" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D43" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="205" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F43" s="127" t="s">
         <v>17</v>
@@ -13235,32 +13236,32 @@
         <v>139</v>
       </c>
       <c r="L43" s="134" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M43" s="129"/>
       <c r="N43" s="129"/>
     </row>
     <row r="44" spans="1:14" ht="57.6">
       <c r="A44" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="C44" s="121" t="s">
+        <v>323</v>
+      </c>
+      <c r="D44" s="143" t="s">
         <v>324</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="E44" s="132" t="s">
         <v>325</v>
-      </c>
-      <c r="C44" s="121" t="s">
-        <v>326</v>
-      </c>
-      <c r="D44" s="143" t="s">
-        <v>327</v>
-      </c>
-      <c r="E44" s="132" t="s">
-        <v>328</v>
       </c>
       <c r="F44" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H44" s="124" t="s">
         <v>81</v>
@@ -13292,7 +13293,7 @@
         <v>16</v>
       </c>
       <c r="E45" s="74" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F45" s="127" t="s">
         <v>17</v>
@@ -13313,36 +13314,36 @@
         <v>125</v>
       </c>
       <c r="L45" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M45" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N45" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="57.6">
       <c r="A46" s="121" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C46" s="141" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D46" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="132" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F46" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="124" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H46" s="124" t="s">
         <v>81</v>
@@ -13362,25 +13363,25 @@
     </row>
     <row r="47" spans="1:14" ht="74.25" customHeight="1">
       <c r="A47" s="125" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B47" s="74" t="s">
         <v>127</v>
       </c>
       <c r="C47" s="125" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D47" s="142" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E47" s="74" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F47" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H47" s="127" t="s">
         <v>52</v>
@@ -13412,7 +13413,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="132" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F48" s="124" t="s">
         <v>35</v>
@@ -13438,25 +13439,25 @@
     </row>
     <row r="49" spans="1:14" ht="57.6">
       <c r="A49" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="C49" s="125" t="s">
+        <v>339</v>
+      </c>
+      <c r="D49" s="217" t="s">
         <v>340</v>
       </c>
-      <c r="B49" s="74" t="s">
+      <c r="E49" s="83" t="s">
         <v>341</v>
-      </c>
-      <c r="C49" s="125" t="s">
-        <v>342</v>
-      </c>
-      <c r="D49" s="217" t="s">
-        <v>343</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>344</v>
       </c>
       <c r="F49" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H49" s="127" t="s">
         <v>19</v>
@@ -13476,19 +13477,19 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="121" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C50" s="121" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D50" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="132" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F50" s="124" t="s">
         <v>17</v>
@@ -13514,19 +13515,19 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="125" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B51" s="74" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C51" s="125" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D51" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F51" s="127" t="s">
         <v>17</v>
@@ -13552,13 +13553,13 @@
     </row>
     <row r="52" spans="1:14" ht="84.75" customHeight="1">
       <c r="A52" s="121" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B52" s="35" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C52" s="121" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D52" s="132" t="s">
         <v>16</v>
@@ -13568,7 +13569,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="124" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H52" s="124" t="s">
         <v>19</v>
@@ -13781,42 +13782,42 @@
         <v>10</v>
       </c>
       <c r="L1" s="223" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="223" t="s">
+        <v>355</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>356</v>
+      </c>
+      <c r="O1" s="108" t="s">
         <v>357</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="P1" s="223" t="s">
         <v>358</v>
       </c>
-      <c r="N1" s="108" t="s">
+      <c r="Q1" s="223" t="s">
         <v>359</v>
       </c>
-      <c r="O1" s="108" t="s">
+      <c r="R1" s="224" t="s">
         <v>360</v>
       </c>
-      <c r="P1" s="223" t="s">
+      <c r="S1" s="224" t="s">
         <v>361</v>
       </c>
-      <c r="Q1" s="223" t="s">
+      <c r="T1" s="224" t="s">
         <v>362</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="U1" s="224" t="s">
         <v>363</v>
       </c>
-      <c r="S1" s="224" t="s">
+      <c r="V1" s="233" t="s">
         <v>364</v>
-      </c>
-      <c r="T1" s="224" t="s">
-        <v>365</v>
-      </c>
-      <c r="U1" s="224" t="s">
-        <v>366</v>
-      </c>
-      <c r="V1" s="233" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="28.8">
       <c r="A2" s="64" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B2" s="157" t="s">
         <v>61</v>
@@ -13825,10 +13826,10 @@
         <v>62</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E2" s="158" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
@@ -13848,25 +13849,25 @@
     </row>
     <row r="3" spans="1:22" ht="115.2">
       <c r="A3" s="68" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D3" s="162" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -13878,7 +13879,7 @@
         <v>66</v>
       </c>
       <c r="K3" s="136" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -13893,19 +13894,19 @@
     </row>
     <row r="4" spans="1:22" ht="129.6">
       <c r="A4" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="157" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="157" t="s">
+      <c r="C4" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="64" t="s">
-        <v>214</v>
-      </c>
       <c r="D4" s="71" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E4" s="158" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
@@ -13920,28 +13921,28 @@
         <v>28</v>
       </c>
       <c r="J4" s="160" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K4" s="136" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L4" s="107"/>
     </row>
     <row r="5" spans="1:22" ht="43.2">
       <c r="A5" s="165" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C5" s="165" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F5" s="166" t="s">
         <v>35</v>
@@ -13959,7 +13960,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="136" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -13974,19 +13975,19 @@
     </row>
     <row r="6" spans="1:22" ht="72">
       <c r="A6" s="168" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B6" s="151" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C6" s="168" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F6" s="133" t="s">
         <v>17</v>
@@ -14008,25 +14009,25 @@
     </row>
     <row r="7" spans="1:22" ht="115.2">
       <c r="A7" s="125" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="125" t="s">
+        <v>388</v>
+      </c>
+      <c r="D7" s="171" t="s">
         <v>389</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="E7" s="81" t="s">
         <v>390</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="171" t="s">
-        <v>392</v>
-      </c>
-      <c r="E7" s="81" t="s">
-        <v>393</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -14051,25 +14052,25 @@
     </row>
     <row r="8" spans="1:22" ht="28.8">
       <c r="A8" s="64" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B8" s="157" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C8" s="172" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D8" s="143" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E8" s="135" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F8" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="159" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H8" s="159" t="s">
         <v>81</v>
@@ -14081,13 +14082,13 @@
         <v>29</v>
       </c>
       <c r="K8" s="136" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:22" ht="43.2">
       <c r="A9" s="165" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>77</v>
@@ -14099,13 +14100,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="173" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F9" s="166" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="166" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H9" s="166">
         <v>1</v>
@@ -14117,7 +14118,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="136" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
@@ -14862,45 +14863,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="225" t="s">
+        <v>396</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>397</v>
+      </c>
+      <c r="N1" s="223" t="s">
+        <v>398</v>
+      </c>
+      <c r="O1" s="224" t="s">
         <v>399</v>
       </c>
-      <c r="M1" s="108" t="s">
+      <c r="P1" s="232" t="s">
         <v>400</v>
       </c>
-      <c r="N1" s="223" t="s">
+      <c r="Q1" s="233" t="s">
         <v>401</v>
-      </c>
-      <c r="O1" s="224" t="s">
-        <v>402</v>
-      </c>
-      <c r="P1" s="232" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q1" s="233" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="64.349999999999994" customHeight="1">
       <c r="A2" s="64" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C2" s="172" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>19</v>
@@ -14912,31 +14913,31 @@
         <v>29</v>
       </c>
       <c r="K2" s="156" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L2" s="136"/>
     </row>
     <row r="3" spans="1:17" ht="129.6">
       <c r="A3" s="68" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -14948,7 +14949,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L3" s="75"/>
       <c r="M3" s="61"/>
@@ -14958,25 +14959,25 @@
     </row>
     <row r="4" spans="1:17" ht="28.8">
       <c r="A4" s="64" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H4" s="159">
         <v>1</v>
@@ -14988,7 +14989,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="156" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="L4" s="136"/>
     </row>
@@ -15811,27 +15812,27 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="M1" s="223" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8">
       <c r="A2" s="121" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -15849,36 +15850,36 @@
         <v>37</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L2" s="141" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M2" s="141" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="72">
       <c r="A3" s="125" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C3" s="125" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="85" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="127" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="127">
         <v>1</v>
@@ -15890,7 +15891,7 @@
         <v>37</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -15909,7 +15910,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -15934,25 +15935,25 @@
     </row>
     <row r="5" spans="1:13" ht="43.2">
       <c r="A5" s="125" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H5" s="127">
         <v>1</v>
@@ -15964,32 +15965,32 @@
         <v>29</v>
       </c>
       <c r="K5" s="98" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
     </row>
     <row r="6" spans="1:13" ht="57.6">
       <c r="A6" s="121" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>81</v>
@@ -16001,36 +16002,36 @@
         <v>29</v>
       </c>
       <c r="K6" s="98" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="L6" s="107" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M6" s="107" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="134" t="s">
+        <v>446</v>
+      </c>
+      <c r="D7" s="185" t="s">
         <v>447</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="E7" s="126" t="s">
         <v>448</v>
-      </c>
-      <c r="C7" s="134" t="s">
-        <v>449</v>
-      </c>
-      <c r="D7" s="185" t="s">
-        <v>450</v>
-      </c>
-      <c r="E7" s="126" t="s">
-        <v>451</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="156" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -16042,7 +16043,7 @@
         <v>29</v>
       </c>
       <c r="K7" s="98" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -16061,7 +16062,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>17</v>
@@ -16079,26 +16080,26 @@
         <v>29</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="L8" s="107"/>
       <c r="M8" s="107"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="125" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="74" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" s="187" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="126" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>17</v>
@@ -16116,32 +16117,32 @@
         <v>29</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
     </row>
     <row r="10" spans="1:13" ht="57.6">
       <c r="A10" s="121" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C10" s="141" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H10" s="124" t="s">
         <v>81</v>
@@ -16153,32 +16154,32 @@
         <v>37</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
     <row r="11" spans="1:13" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" s="125" t="s">
+        <v>462</v>
+      </c>
+      <c r="D11" s="154" t="s">
         <v>463</v>
       </c>
-      <c r="B11" s="74" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>466</v>
-      </c>
       <c r="E11" s="126" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H11" s="127">
         <v>1</v>
@@ -16190,7 +16191,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
@@ -16209,7 +16210,7 @@
         <v>85</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -16227,14 +16228,14 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
     <row r="13" spans="1:13" ht="72">
       <c r="A13" s="125" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B13" s="74" t="s">
         <v>90</v>
@@ -16246,13 +16247,13 @@
         <v>92</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H13" s="127">
         <v>1</v>
@@ -16264,32 +16265,32 @@
         <v>37</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="72">
       <c r="A14" s="121" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B14" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="121" t="s">
         <v>176</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>177</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H14" s="124" t="s">
         <v>19</v>
@@ -16301,32 +16302,32 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
     <row r="15" spans="1:13" ht="100.8">
       <c r="A15" s="125" t="s">
+        <v>475</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>476</v>
+      </c>
+      <c r="C15" s="125" t="s">
+        <v>477</v>
+      </c>
+      <c r="D15" s="185" t="s">
+        <v>447</v>
+      </c>
+      <c r="E15" s="80" t="s">
         <v>478</v>
-      </c>
-      <c r="B15" s="74" t="s">
-        <v>479</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>480</v>
-      </c>
-      <c r="D15" s="185" t="s">
-        <v>450</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>481</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="127" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H15" s="127" t="s">
         <v>81</v>
@@ -16338,7 +16339,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
@@ -16373,32 +16374,32 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13" ht="57.6">
       <c r="A17" s="125" t="s">
+        <v>481</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="125" t="s">
+        <v>483</v>
+      </c>
+      <c r="D17" s="185" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="74" t="s">
         <v>484</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>485</v>
-      </c>
-      <c r="C17" s="125" t="s">
-        <v>486</v>
-      </c>
-      <c r="D17" s="185" t="s">
-        <v>450</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>487</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -16410,7 +16411,7 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
@@ -16429,7 +16430,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -16447,24 +16448,24 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
     </row>
     <row r="19" spans="1:13" ht="28.8">
       <c r="A19" s="125" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B19" s="126" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C19" s="125" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D19" s="126"/>
       <c r="E19" s="80" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -16483,10 +16484,10 @@
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="129" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M19" s="129" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="129.6">
@@ -16503,7 +16504,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
@@ -16521,32 +16522,32 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
     <row r="21" spans="1:13" ht="43.2">
       <c r="A21" s="125" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E21" s="81" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H21" s="127" t="s">
         <v>81</v>
@@ -16558,32 +16559,32 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13" ht="57.6">
       <c r="A22" s="121" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>81</v>
@@ -16612,7 +16613,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -16630,7 +16631,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17112,7 +17113,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17129,7 +17130,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17147,7 +17148,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17183,7 +17184,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17203,7 +17204,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17221,31 +17222,31 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L4" s="129"/>
     </row>
     <row r="5" spans="1:12" ht="43.2">
       <c r="A5" s="121" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="C5" s="121" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="121" t="s">
+      <c r="D5" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="122" t="s">
-        <v>197</v>
-      </c>
       <c r="E5" s="135" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>81</v>
@@ -17273,7 +17274,7 @@
         <v>63</v>
       </c>
       <c r="E6" s="247" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F6" s="244" t="s">
         <v>17</v>
@@ -17291,7 +17292,7 @@
         <v>66</v>
       </c>
       <c r="K6" s="243" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="L6" s="242"/>
     </row>
@@ -17373,7 +17374,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -17391,7 +17392,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L11" s="107"/>
     </row>
@@ -17409,7 +17410,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -17427,7 +17428,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -17447,7 +17448,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
@@ -17465,7 +17466,7 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L13" s="107"/>
     </row>
@@ -17483,7 +17484,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -17501,10 +17502,10 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L14" s="129" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -17521,7 +17522,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -17820,7 +17821,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="92.4">
@@ -17837,7 +17838,7 @@
         <v>152</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
@@ -17855,7 +17856,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -17893,25 +17894,25 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B4" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="121" t="s">
         <v>176</v>
-      </c>
-      <c r="C4" s="121" t="s">
-        <v>177</v>
       </c>
       <c r="D4" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H4" s="124" t="s">
         <v>19</v>
@@ -18043,7 +18044,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18061,31 +18062,31 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="43.2">
       <c r="A9" s="125" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H9" s="127">
         <v>1</v>
@@ -18097,31 +18098,31 @@
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
       <c r="A10" s="121" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C10" s="121" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H10" s="133">
         <v>1</v>
@@ -18133,29 +18134,29 @@
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L10" s="107"/>
     </row>
     <row r="11" spans="1:12" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" s="134" t="s">
+        <v>462</v>
+      </c>
+      <c r="D11" s="154" t="s">
         <v>463</v>
-      </c>
-      <c r="B11" s="74" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="134" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>466</v>
       </c>
       <c r="E11" s="126"/>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -18171,13 +18172,13 @@
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="121" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C12" s="121" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18187,7 +18188,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H12" s="124" t="s">
         <v>19</v>
@@ -18203,19 +18204,19 @@
     </row>
     <row r="13" spans="1:12" ht="57.6">
       <c r="A13" s="191" t="s">
+        <v>211</v>
+      </c>
+      <c r="B13" s="74" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="C13" s="134" t="s">
         <v>213</v>
-      </c>
-      <c r="C13" s="134" t="s">
-        <v>214</v>
       </c>
       <c r="D13" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18237,13 +18238,13 @@
     </row>
     <row r="14" spans="1:12" ht="28.8">
       <c r="A14" s="121" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="121" t="s">
         <v>230</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>231</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
@@ -18269,19 +18270,19 @@
     </row>
     <row r="15" spans="1:12" ht="57.6">
       <c r="A15" s="125" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B15" s="74" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C15" s="125" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18315,7 +18316,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18349,7 +18350,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
@@ -18367,7 +18368,7 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L17" s="129"/>
     </row>
@@ -18385,7 +18386,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -18407,13 +18408,13 @@
     </row>
     <row r="19" spans="1:12" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="134" t="s">
         <v>265</v>
-      </c>
-      <c r="B19" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="C19" s="134" t="s">
-        <v>267</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
@@ -18423,7 +18424,7 @@
         <v>17</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>19</v>
@@ -18436,7 +18437,7 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="43.2">
@@ -18453,7 +18454,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -18477,19 +18478,19 @@
     </row>
     <row r="21" spans="1:12" ht="57.6">
       <c r="A21" s="125" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -18507,33 +18508,33 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L21" s="192" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="43.2">
       <c r="A22" s="121" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B22" s="35" t="s">
         <v>127</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D22" s="143" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>52</v>
@@ -18561,7 +18562,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -18579,7 +18580,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L23" s="195"/>
     </row>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E62AF80-5461-4F05-88C6-9AD4988BAB39}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB2FDFB2-6BD5-4989-9906-EC23F51E3B08}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-17388" windowWidth="30936" windowHeight="16776" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-12765" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -372,9 +372,6 @@
     <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
   </si>
   <si>
-    <t>The licence under which the catalogue (with resource description) is made available. In the description of distributions and data services the licences of that resources are taken up.</t>
-  </si>
-  <si>
     <t>dct:LicenseDocument (IRI)</t>
   </si>
   <si>
@@ -584,12 +581,6 @@
   </si>
   <si>
     <t>If available, add URI to analytics distribution here</t>
-  </si>
-  <si>
-    <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
-For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
-As multiple legislations may apply to the resource the maximum cardinality is not limited.
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
   </si>
   <si>
     <t>code values</t>
@@ -844,11 +835,6 @@
     <t>https://w3c.github.io/dpv/2.0/dpv/modules/legal_basis.html#vocab-legal-basis</t>
   </si>
   <si>
-    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
-Example value for this property could be: dpv:Consent</t>
-  </si>
-  <si>
     <t>dpv:LegalBasis</t>
   </si>
   <si>
@@ -992,10 +978,6 @@
   </si>
   <si>
     <t>https://w3c.github.io/dpv/2.1/dpv/#vocab-purposes</t>
-  </si>
-  <si>
-    <t>One (or many) category or sub-category of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column).
-Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
   <si>
     <t>dpv:Purpose</t>
@@ -1737,9 +1719,6 @@
     <t>http://publications.europa.eu/resource/authority/file-type</t>
   </si>
   <si>
-    <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL, e.g., from the File Type vocabulary. For instance, for mzML files the value of this property could be: http://edamontology.org/format_3244</t>
-  </si>
-  <si>
     <t>dct:MediaTypeOrExtent (IRI)</t>
   </si>
   <si>
@@ -2617,6 +2596,29 @@
 This protects their privacy and enables contact about the resource even after the individual has left the institution.
 The email address has to be provided starting with mailto: prefix.
 For example: mailto:info@example.com</t>
+  </si>
+  <si>
+    <t>The licence under which the catalogue (with resource description) is made available.
+The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
+  </si>
+  <si>
+    <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL from the File Type vocabulary.</t>
+  </si>
+  <si>
+    <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
+For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
+As multiple legislations may apply to the resource the maximum cardinality is not limited. Note that the relation with other legislations is complex and is being looked into by legal experts.
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
+  </si>
+  <si>
+    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
+This property should always be filled if the dataset contains personal data and the applicable legislation is GDPR.
+Example value for this property could be: dpv:Consent</t>
+  </si>
+  <si>
+    <t>One (or many) categoiesy or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
+Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
 </sst>
 </file>
@@ -3766,22 +3768,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7437,33 +7439,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N1" s="227" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="O1" s="233" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="72">
       <c r="A2" s="196" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7472,7 +7474,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7487,13 +7489,13 @@
     </row>
     <row r="3" spans="1:15" ht="28.8">
       <c r="A3" s="68" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7632,36 +7634,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>566</v>
+      </c>
+      <c r="M1" s="220" t="s">
+        <v>567</v>
+      </c>
+      <c r="N1" s="226" t="s">
+        <v>568</v>
+      </c>
+      <c r="O1" s="230" t="s">
+        <v>569</v>
+      </c>
+      <c r="P1" s="227" t="s">
+        <v>570</v>
+      </c>
+      <c r="Q1" s="231" t="s">
         <v>571</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="R1" s="233" t="s">
         <v>572</v>
-      </c>
-      <c r="N1" s="226" t="s">
-        <v>573</v>
-      </c>
-      <c r="O1" s="230" t="s">
-        <v>574</v>
-      </c>
-      <c r="P1" s="227" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q1" s="231" t="s">
-        <v>576</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="58" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -7671,7 +7673,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>81</v>
@@ -7689,13 +7691,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="48" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -7705,7 +7707,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8357,33 +8359,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="N1" s="227" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="O1" s="233" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2">
       <c r="A2" s="84" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8413,25 +8415,25 @@
     </row>
     <row r="3" spans="1:15" ht="129.6">
       <c r="A3" s="48" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D3" s="234" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8551,39 +8553,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="M1" s="229" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="N1" s="228" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="O1" s="233" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="158.4">
       <c r="A2" s="84" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="115" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>52</v>
@@ -8598,25 +8600,25 @@
     </row>
     <row r="3" spans="1:15" ht="43.2">
       <c r="A3" s="48" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>52</v>
@@ -8736,39 +8738,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="N1" s="227" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="O1" s="233" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="100.8">
       <c r="A2" s="84" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>81</v>
@@ -8783,25 +8785,25 @@
     </row>
     <row r="3" spans="1:15" ht="57.6">
       <c r="A3" s="48" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>81</v>
@@ -8899,7 +8901,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -8922,13 +8924,13 @@
     </row>
     <row r="2" spans="1:10" ht="28.8">
       <c r="A2" s="63" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -8936,7 +8938,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -8950,13 +8952,13 @@
     </row>
     <row r="3" spans="1:10" ht="43.2">
       <c r="A3" s="67" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8964,10 +8966,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -8978,13 +8980,13 @@
     </row>
     <row r="4" spans="1:10" ht="43.2">
       <c r="A4" s="63" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -8992,10 +8994,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="H4" s="65" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9006,26 +9008,26 @@
     </row>
     <row r="5" spans="1:10" ht="43.2">
       <c r="A5" s="67" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9036,13 +9038,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8">
       <c r="A6" s="63" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9050,10 +9052,10 @@
       <c r="E6" s="53"/>
       <c r="F6" s="64"/>
       <c r="G6" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9064,13 +9066,13 @@
     </row>
     <row r="7" spans="1:10" ht="28.8">
       <c r="A7" s="67" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9078,7 +9080,7 @@
       <c r="E7" s="54"/>
       <c r="F7" s="68"/>
       <c r="G7" s="67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="48">
         <v>1</v>
@@ -9092,23 +9094,23 @@
     </row>
     <row r="8" spans="1:10" ht="86.4">
       <c r="A8" s="63" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9122,13 +9124,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.8">
       <c r="A9" s="67" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9136,7 +9138,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9150,23 +9152,23 @@
     </row>
     <row r="10" spans="1:10" ht="28.8">
       <c r="A10" s="63" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -9631,36 +9633,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="N1" s="233" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="72">
       <c r="A2" s="44" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="D2" s="78" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -9674,13 +9676,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1">
       <c r="A3" s="49" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -9690,7 +9692,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -10604,28 +10606,28 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="237" t="s">
+      <c r="A8" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="C8" s="238" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="239" t="s">
+      <c r="E8" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="236" t="s">
+      <c r="F8" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="236" t="s">
+      <c r="G8" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="236" t="s">
+      <c r="H8" s="237" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="235" t="s">
@@ -10639,16 +10641,16 @@
       <c r="M8" s="235"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="237"/>
-      <c r="B9" s="238"/>
-      <c r="C9" s="237"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="238"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
       <c r="I9" s="235"/>
       <c r="J9" s="235"/>
       <c r="K9" s="137"/>
@@ -10656,16 +10658,16 @@
       <c r="M9" s="235"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="237"/>
-      <c r="B10" s="238"/>
-      <c r="C10" s="237"/>
+      <c r="A10" s="238"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="238"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="239"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
       <c r="I10" s="235"/>
       <c r="J10" s="235"/>
       <c r="K10" s="137"/>
@@ -10673,16 +10675,16 @@
       <c r="M10" s="235"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="237"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="237"/>
+      <c r="A11" s="238"/>
+      <c r="B11" s="241"/>
+      <c r="C11" s="238"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="239"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="237"/>
+      <c r="G11" s="237"/>
+      <c r="H11" s="237"/>
       <c r="I11" s="235"/>
       <c r="J11" s="235"/>
       <c r="K11" s="153"/>
@@ -10690,16 +10692,16 @@
       <c r="M11" s="235"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="237"/>
-      <c r="B12" s="238"/>
-      <c r="C12" s="237"/>
+      <c r="A12" s="238"/>
+      <c r="B12" s="241"/>
+      <c r="C12" s="238"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="239"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="237"/>
+      <c r="H12" s="237"/>
       <c r="I12" s="235"/>
       <c r="J12" s="235"/>
       <c r="K12" s="137"/>
@@ -10815,7 +10817,7 @@
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
     </row>
-    <row r="16" spans="1:13" ht="43.2">
+    <row r="16" spans="1:13" ht="85.2" customHeight="1">
       <c r="A16" s="121" t="s">
         <v>89</v>
       </c>
@@ -10829,13 +10831,13 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>93</v>
+        <v>670</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="124" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H16" s="124" t="s">
         <v>81</v>
@@ -10847,20 +10849,20 @@
         <v>29</v>
       </c>
       <c r="K16" s="155" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="C17" s="125" t="s">
         <v>97</v>
-      </c>
-      <c r="C17" s="125" t="s">
-        <v>98</v>
       </c>
       <c r="D17" s="126" t="s">
         <v>16</v>
@@ -10870,7 +10872,7 @@
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -10882,26 +10884,26 @@
         <v>29</v>
       </c>
       <c r="K17" s="155" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
     </row>
     <row r="18" spans="1:13" ht="43.2">
       <c r="A18" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="141" t="s">
         <v>102</v>
-      </c>
-      <c r="C18" s="141" t="s">
-        <v>103</v>
       </c>
       <c r="D18" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>35</v>
@@ -10913,13 +10915,13 @@
         <v>1</v>
       </c>
       <c r="I18" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K18" s="155" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L18" s="107" t="s">
         <v>46</v>
@@ -10930,13 +10932,13 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="125" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="C19" s="125" t="s">
         <v>108</v>
-      </c>
-      <c r="C19" s="125" t="s">
-        <v>109</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
@@ -10946,7 +10948,7 @@
         <v>17</v>
       </c>
       <c r="G19" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>81</v>
@@ -10958,32 +10960,32 @@
         <v>29</v>
       </c>
       <c r="K19" s="207" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L19" s="129"/>
       <c r="M19" s="129"/>
     </row>
     <row r="20" spans="1:13" ht="43.2">
       <c r="A20" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>112</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>113</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="124" t="s">
         <v>81</v>
@@ -11000,25 +11002,25 @@
     </row>
     <row r="21" spans="1:13" ht="72">
       <c r="A21" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>117</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>118</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="127" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H21" s="127" t="s">
         <v>19</v>
@@ -11031,19 +11033,19 @@
       </c>
       <c r="K21" s="130"/>
       <c r="L21" s="134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>123</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>124</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
@@ -11053,7 +11055,7 @@
         <v>17</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>19</v>
@@ -11065,32 +11067,32 @@
         <v>29</v>
       </c>
       <c r="K22" s="106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L22" s="107"/>
       <c r="M22" s="107"/>
     </row>
     <row r="23" spans="1:13" ht="57.6">
       <c r="A23" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="134" t="s">
         <v>128</v>
-      </c>
-      <c r="C23" s="134" t="s">
-        <v>129</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H23" s="127" t="s">
         <v>19</v>
@@ -11107,19 +11109,19 @@
     </row>
     <row r="24" spans="1:13" ht="28.8">
       <c r="A24" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="C24" s="121" t="s">
         <v>133</v>
-      </c>
-      <c r="C24" s="121" t="s">
-        <v>134</v>
       </c>
       <c r="D24" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="211" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>35</v>
@@ -11137,7 +11139,7 @@
         <v>29</v>
       </c>
       <c r="K24" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L24" s="107"/>
       <c r="M24" s="107"/>
@@ -11293,7 +11295,7 @@
       <c r="G38" s="36"/>
       <c r="H38" s="37"/>
       <c r="K38" s="94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -11317,7 +11319,7 @@
       <c r="G40" s="36"/>
       <c r="H40" s="37"/>
       <c r="K40" s="94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -11341,7 +11343,7 @@
       <c r="G42" s="36"/>
       <c r="H42" s="37"/>
       <c r="K42" s="94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -11354,7 +11356,7 @@
       <c r="G43" s="36"/>
       <c r="H43" s="37"/>
       <c r="K43" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -11367,7 +11369,7 @@
       <c r="G44" s="36"/>
       <c r="H44" s="37"/>
       <c r="K44" s="94" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -11380,7 +11382,7 @@
       <c r="G45" s="36"/>
       <c r="H45" s="37"/>
       <c r="K45" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -11392,7 +11394,7 @@
       <c r="G46" s="36"/>
       <c r="H46" s="37"/>
       <c r="K46" s="94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -11405,7 +11407,7 @@
       <c r="G47" s="36"/>
       <c r="H47" s="37"/>
       <c r="K47" s="93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -11418,7 +11420,7 @@
       <c r="G48" s="36"/>
       <c r="H48" s="37"/>
       <c r="K48" s="94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -11431,7 +11433,7 @@
       <c r="G49" s="36"/>
       <c r="H49" s="37"/>
       <c r="K49" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -11444,7 +11446,7 @@
       <c r="G50" s="36"/>
       <c r="H50" s="37"/>
       <c r="K50" s="94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -11457,7 +11459,7 @@
       <c r="G51" s="36"/>
       <c r="H51" s="37"/>
       <c r="K51" s="93" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -11470,7 +11472,7 @@
       <c r="G52" s="36"/>
       <c r="H52" s="37"/>
       <c r="K52" s="94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -11483,7 +11485,7 @@
       <c r="G53" s="36"/>
       <c r="H53" s="37"/>
       <c r="K53" s="93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -11706,36 +11708,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>147</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="N1" s="224" t="s">
         <v>148</v>
-      </c>
-      <c r="N1" s="224" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="209.25" customHeight="1">
       <c r="A2" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="D2" s="122" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="E2" s="123" t="s">
         <v>153</v>
-      </c>
-      <c r="E2" s="123" t="s">
-        <v>154</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H2" s="124">
         <v>1</v>
@@ -11747,31 +11749,31 @@
         <v>21</v>
       </c>
       <c r="K2" s="106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L2" s="107"/>
     </row>
     <row r="3" spans="1:14" ht="72">
       <c r="A3" s="125" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="C3" s="125" t="s">
         <v>157</v>
-      </c>
-      <c r="C3" s="125" t="s">
-        <v>158</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H3" s="127" t="s">
         <v>19</v>
@@ -11783,15 +11785,15 @@
         <v>66</v>
       </c>
       <c r="K3" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="134" t="s">
         <v>161</v>
-      </c>
-      <c r="L3" s="134" t="s">
-        <v>162</v>
       </c>
       <c r="M3" s="129"/>
       <c r="N3" s="129"/>
     </row>
-    <row r="4" spans="1:14" s="117" customFormat="1" ht="144">
+    <row r="4" spans="1:14" s="117" customFormat="1" ht="158.4">
       <c r="A4" s="131" t="s">
         <v>13</v>
       </c>
@@ -11805,7 +11807,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>163</v>
+        <v>672</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>35</v>
@@ -11829,25 +11831,25 @@
     </row>
     <row r="5" spans="1:14" ht="57.6">
       <c r="A5" s="125" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="134" t="s">
         <v>164</v>
-      </c>
-      <c r="B5" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>166</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H5" s="127" t="s">
         <v>19</v>
@@ -11859,7 +11861,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="130" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -11867,25 +11869,25 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="121" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="121" t="s">
         <v>170</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>172</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="132" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="124" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>19</v>
@@ -11897,31 +11899,31 @@
         <v>66</v>
       </c>
       <c r="K6" s="106" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L6" s="107"/>
     </row>
     <row r="7" spans="1:14" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="125" t="s">
         <v>176</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>178</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="74" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>19</v>
@@ -11933,7 +11935,7 @@
         <v>66</v>
       </c>
       <c r="K7" s="130" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -11965,13 +11967,13 @@
         <v>1</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K8" s="106" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L8" s="107" t="s">
         <v>39</v>
@@ -11997,7 +11999,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="74" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
@@ -12015,7 +12017,7 @@
         <v>37</v>
       </c>
       <c r="K9" s="130" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L9" s="129" t="s">
         <v>46</v>
@@ -12041,7 +12043,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
@@ -12065,25 +12067,25 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="125" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="125" t="s">
         <v>185</v>
-      </c>
-      <c r="B11" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>187</v>
       </c>
       <c r="D11" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="140" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -12096,30 +12098,30 @@
       </c>
       <c r="K11" s="130"/>
       <c r="L11" s="129" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M11" s="129" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N11" s="129" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="121" t="s">
         <v>190</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>192</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="132" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -12137,31 +12139,31 @@
         <v>66</v>
       </c>
       <c r="K12" s="106" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L12" s="107"/>
     </row>
     <row r="13" spans="1:14" ht="69.75" customHeight="1">
       <c r="A13" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="125" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="D13" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="E13" s="80" t="s">
         <v>197</v>
-      </c>
-      <c r="D13" s="142" t="s">
-        <v>198</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>199</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H13" s="127" t="s">
         <v>81</v>
@@ -12173,35 +12175,35 @@
         <v>66</v>
       </c>
       <c r="K13" s="130" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="237" t="s">
+      <c r="A14" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="239" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="237" t="s">
+      <c r="C14" s="238" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="239" t="s">
-        <v>201</v>
-      </c>
-      <c r="F14" s="236" t="s">
+      <c r="E14" s="240" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="236" t="s">
+      <c r="G14" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="236" t="s">
+      <c r="H14" s="237" t="s">
         <v>19</v>
       </c>
       <c r="I14" s="235" t="s">
@@ -12210,88 +12212,88 @@
       <c r="J14" s="235" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="240"/>
+      <c r="K14" s="236"/>
       <c r="L14" s="235"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="237"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="237"/>
+      <c r="A15" s="238"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="238"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="239"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="237"/>
+      <c r="G15" s="237"/>
+      <c r="H15" s="237"/>
       <c r="I15" s="235"/>
       <c r="J15" s="235"/>
-      <c r="K15" s="240"/>
+      <c r="K15" s="236"/>
       <c r="L15" s="235"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="237"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="237"/>
+      <c r="A16" s="238"/>
+      <c r="B16" s="239"/>
+      <c r="C16" s="238"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="239"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
+      <c r="E16" s="240"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
       <c r="I16" s="235"/>
       <c r="J16" s="235"/>
-      <c r="K16" s="240"/>
+      <c r="K16" s="236"/>
       <c r="L16" s="235"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="237"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="237"/>
+      <c r="A17" s="238"/>
+      <c r="B17" s="239"/>
+      <c r="C17" s="238"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="239"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="237"/>
+      <c r="G17" s="237"/>
+      <c r="H17" s="237"/>
       <c r="I17" s="235"/>
       <c r="J17" s="235"/>
-      <c r="K17" s="240"/>
+      <c r="K17" s="236"/>
       <c r="L17" s="235"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="237"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="237"/>
+      <c r="A18" s="238"/>
+      <c r="B18" s="239"/>
+      <c r="C18" s="238"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="239"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="237"/>
+      <c r="G18" s="237"/>
+      <c r="H18" s="237"/>
       <c r="I18" s="235"/>
       <c r="J18" s="235"/>
-      <c r="K18" s="240"/>
+      <c r="K18" s="236"/>
       <c r="L18" s="235"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="125" t="s">
         <v>202</v>
-      </c>
-      <c r="B19" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="125" t="s">
-        <v>204</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="80" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -12309,35 +12311,35 @@
         <v>29</v>
       </c>
       <c r="K19" s="207" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L19" s="134" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M19" s="129"/>
       <c r="N19" s="129"/>
     </row>
     <row r="20" spans="1:14" ht="86.4">
       <c r="A20" s="121" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="121" t="s">
         <v>208</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>210</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H20" s="124" t="s">
         <v>19</v>
@@ -12349,25 +12351,25 @@
         <v>66</v>
       </c>
       <c r="K20" s="106" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L20" s="107"/>
     </row>
     <row r="21" spans="1:14" ht="100.8">
       <c r="A21" s="125" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="125" t="s">
         <v>213</v>
-      </c>
-      <c r="B21" s="74" t="s">
-        <v>214</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>215</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="208" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>35</v>
@@ -12385,7 +12387,7 @@
         <v>37</v>
       </c>
       <c r="K21" s="130" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
@@ -12393,25 +12395,25 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="121" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="121" t="s">
         <v>218</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>220</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>19</v>
@@ -12424,30 +12426,30 @@
       </c>
       <c r="K22" s="106"/>
       <c r="L22" s="141" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="43.2">
       <c r="A23" s="125" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" s="125" t="s">
         <v>224</v>
-      </c>
-      <c r="B23" s="74" t="s">
-        <v>225</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>226</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="127" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H23" s="127" t="s">
         <v>19</v>
@@ -12459,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="207" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -12467,19 +12469,19 @@
     </row>
     <row r="24" spans="1:14" ht="43.2">
       <c r="A24" s="121" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" s="141" t="s">
         <v>230</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>232</v>
       </c>
       <c r="D24" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>35</v>
@@ -12491,13 +12493,13 @@
         <v>52</v>
       </c>
       <c r="I24" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="106" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L24" s="107"/>
     </row>
@@ -12515,7 +12517,7 @@
         <v>85</v>
       </c>
       <c r="E25" s="126" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F25" s="127" t="s">
         <v>17</v>
@@ -12539,27 +12541,27 @@
       <c r="M25" s="129"/>
       <c r="N25" s="129"/>
     </row>
-    <row r="26" spans="1:14" ht="115.2">
+    <row r="26" spans="1:14" ht="144">
       <c r="A26" s="121" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" s="141" t="s">
         <v>236</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="D26" s="122" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="141" t="s">
-        <v>238</v>
-      </c>
-      <c r="D26" s="122" t="s">
-        <v>239</v>
-      </c>
       <c r="E26" s="132" t="s">
-        <v>240</v>
+        <v>673</v>
       </c>
       <c r="F26" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="124" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H26" s="124" t="s">
         <v>19</v>
@@ -12571,31 +12573,31 @@
         <v>66</v>
       </c>
       <c r="K26" s="106" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L26" s="107"/>
     </row>
     <row r="27" spans="1:14" ht="43.2">
       <c r="A27" s="125" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B27" s="74" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C27" s="125" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D27" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="126" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F27" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="127" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H27" s="127" t="s">
         <v>81</v>
@@ -12607,7 +12609,7 @@
         <v>66</v>
       </c>
       <c r="K27" s="130" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L27" s="129"/>
       <c r="M27" s="129"/>
@@ -12615,25 +12617,25 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="121" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C28" s="141" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D28" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="132" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F28" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="124" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H28" s="124" t="s">
         <v>81</v>
@@ -12645,43 +12647,43 @@
         <v>66</v>
       </c>
       <c r="K28" s="106" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L28" s="107"/>
     </row>
     <row r="29" spans="1:14" ht="43.2">
       <c r="A29" s="125" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="C29" s="125" t="s">
         <v>97</v>
-      </c>
-      <c r="C29" s="125" t="s">
-        <v>98</v>
       </c>
       <c r="D29" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F29" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H29" s="127" t="s">
         <v>81</v>
       </c>
       <c r="I29" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J29" s="129" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L29" s="129"/>
       <c r="M29" s="129"/>
@@ -12689,25 +12691,25 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="121" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C30" s="121" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D30" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="132" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F30" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H30" s="124" t="s">
         <v>81</v>
@@ -12719,31 +12721,31 @@
         <v>66</v>
       </c>
       <c r="K30" s="106" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L30" s="107"/>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="125" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B31" s="74" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C31" s="125" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D31" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F31" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="127" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H31" s="127" t="s">
         <v>81</v>
@@ -12755,7 +12757,7 @@
         <v>66</v>
       </c>
       <c r="K31" s="130" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L31" s="129"/>
       <c r="M31" s="129"/>
@@ -12763,25 +12765,25 @@
     </row>
     <row r="32" spans="1:14" ht="57.6">
       <c r="A32" s="121" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C32" s="121" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D32" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F32" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="124" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H32" s="124" t="s">
         <v>19</v>
@@ -12793,31 +12795,31 @@
         <v>29</v>
       </c>
       <c r="K32" s="106" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L32" s="107"/>
     </row>
     <row r="33" spans="1:14" ht="57.6">
       <c r="A33" s="125" t="s">
+        <v>269</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="125" t="s">
+        <v>271</v>
+      </c>
+      <c r="D33" s="142" t="s">
         <v>272</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="E33" s="80" t="s">
         <v>273</v>
-      </c>
-      <c r="C33" s="125" t="s">
-        <v>274</v>
-      </c>
-      <c r="D33" s="142" t="s">
-        <v>275</v>
-      </c>
-      <c r="E33" s="80" t="s">
-        <v>276</v>
       </c>
       <c r="F33" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="127" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H33" s="127" t="s">
         <v>19</v>
@@ -12829,7 +12831,7 @@
         <v>66</v>
       </c>
       <c r="K33" s="130" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L33" s="129"/>
       <c r="M33" s="129"/>
@@ -12837,19 +12839,19 @@
     </row>
     <row r="34" spans="1:14" ht="43.2">
       <c r="A34" s="121" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C34" s="121" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D34" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="132" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F34" s="124" t="s">
         <v>17</v>
@@ -12867,25 +12869,25 @@
         <v>66</v>
       </c>
       <c r="K34" s="106" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L34" s="107"/>
     </row>
     <row r="35" spans="1:14" ht="115.2">
       <c r="A35" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="74" t="s">
+      <c r="C35" s="125" t="s">
         <v>102</v>
-      </c>
-      <c r="C35" s="125" t="s">
-        <v>103</v>
       </c>
       <c r="D35" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="205" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F35" s="127" t="s">
         <v>35</v>
@@ -12897,13 +12899,13 @@
         <v>1</v>
       </c>
       <c r="I35" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J35" s="129" t="s">
         <v>21</v>
       </c>
       <c r="K35" s="130" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L35" s="129" t="s">
         <v>46</v>
@@ -12915,27 +12917,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="43.2">
+    <row r="36" spans="1:14" ht="57.6">
       <c r="A36" s="121" t="s">
+        <v>282</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C36" s="121" t="s">
+        <v>284</v>
+      </c>
+      <c r="D36" s="122" t="s">
         <v>285</v>
       </c>
-      <c r="B36" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="C36" s="121" t="s">
-        <v>287</v>
-      </c>
-      <c r="D36" s="122" t="s">
-        <v>288</v>
-      </c>
       <c r="E36" s="138" t="s">
-        <v>289</v>
+        <v>674</v>
       </c>
       <c r="F36" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="124" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H36" s="124" t="s">
         <v>19</v>
@@ -12947,31 +12949,31 @@
         <v>66</v>
       </c>
       <c r="K36" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L36" s="107"/>
     </row>
     <row r="37" spans="1:14" ht="228" customHeight="1">
       <c r="A37" s="125" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B37" s="74" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C37" s="134" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D37" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="126" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F37" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="128" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H37" s="127" t="s">
         <v>19</v>
@@ -12984,36 +12986,36 @@
       </c>
       <c r="K37" s="130"/>
       <c r="L37" s="129" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="M37" s="129" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N37" s="129" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="57.6">
       <c r="A38" s="121" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C38" s="121" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D38" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E38" s="132" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F38" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="128" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H38" s="124" t="s">
         <v>19</v>
@@ -13025,39 +13027,39 @@
         <v>29</v>
       </c>
       <c r="K38" s="106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L38" s="107" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="M38" s="107" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="N38" s="107" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2">
       <c r="A39" s="125" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B39" s="74" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C39" s="125" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D39" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="126" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F39" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="128" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H39" s="127" t="s">
         <v>19</v>
@@ -13070,72 +13072,72 @@
       </c>
       <c r="K39" s="130"/>
       <c r="L39" s="129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M39" s="129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="N39" s="129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="C40" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="C40" s="121" t="s">
-        <v>109</v>
       </c>
       <c r="D40" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="132" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F40" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I40" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J40" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K40" s="106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L40" s="107"/>
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="125" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B41" s="74" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C41" s="125" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D41" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="74" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F41" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" s="127" t="s">
         <v>81</v>
@@ -13147,39 +13149,39 @@
         <v>66</v>
       </c>
       <c r="K41" s="130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L41" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M41" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N41" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
       <c r="A42" s="121" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C42" s="121" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D42" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="132" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F42" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H42" s="124" t="s">
         <v>19</v>
@@ -13191,29 +13193,29 @@
         <v>66</v>
       </c>
       <c r="K42" s="106" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L42" s="141" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M42" s="107"/>
       <c r="N42" s="107"/>
     </row>
     <row r="43" spans="1:14" ht="28.8">
       <c r="A43" s="125" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B43" s="74" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C43" s="125" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D43" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="205" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F43" s="127" t="s">
         <v>17</v>
@@ -13231,35 +13233,35 @@
         <v>29</v>
       </c>
       <c r="K43" s="130" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L43" s="134" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M43" s="129"/>
       <c r="N43" s="129"/>
     </row>
     <row r="44" spans="1:14" ht="57.6">
       <c r="A44" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="C44" s="121" t="s">
+        <v>323</v>
+      </c>
+      <c r="D44" s="143" t="s">
+        <v>324</v>
+      </c>
+      <c r="E44" s="132" t="s">
         <v>325</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="C44" s="121" t="s">
-        <v>327</v>
-      </c>
-      <c r="D44" s="143" t="s">
-        <v>328</v>
-      </c>
-      <c r="E44" s="132" t="s">
-        <v>329</v>
       </c>
       <c r="F44" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H44" s="124" t="s">
         <v>81</v>
@@ -13271,7 +13273,7 @@
         <v>37</v>
       </c>
       <c r="K44" s="106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L44" s="107"/>
       <c r="M44" s="107"/>
@@ -13279,25 +13281,25 @@
     </row>
     <row r="45" spans="1:14" ht="28.8">
       <c r="A45" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="74" t="s">
+      <c r="C45" s="125" t="s">
         <v>123</v>
-      </c>
-      <c r="C45" s="125" t="s">
-        <v>124</v>
       </c>
       <c r="D45" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E45" s="74" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F45" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G45" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H45" s="127" t="s">
         <v>19</v>
@@ -13309,39 +13311,39 @@
         <v>29</v>
       </c>
       <c r="K45" s="130" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L45" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M45" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N45" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="57.6">
       <c r="A46" s="121" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C46" s="141" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D46" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="132" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F46" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="124" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H46" s="124" t="s">
         <v>81</v>
@@ -13353,7 +13355,7 @@
         <v>37</v>
       </c>
       <c r="K46" s="106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L46" s="107"/>
       <c r="M46" s="107"/>
@@ -13361,25 +13363,25 @@
     </row>
     <row r="47" spans="1:14" ht="74.25" customHeight="1">
       <c r="A47" s="125" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B47" s="74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C47" s="125" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D47" s="142" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E47" s="74" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F47" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H47" s="127" t="s">
         <v>52</v>
@@ -13391,7 +13393,7 @@
         <v>66</v>
       </c>
       <c r="K47" s="130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L47" s="129"/>
       <c r="M47" s="129"/>
@@ -13399,19 +13401,19 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="C48" s="121" t="s">
         <v>133</v>
-      </c>
-      <c r="C48" s="121" t="s">
-        <v>134</v>
       </c>
       <c r="D48" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E48" s="132" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F48" s="124" t="s">
         <v>35</v>
@@ -13429,7 +13431,7 @@
         <v>29</v>
       </c>
       <c r="K48" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L48" s="107"/>
       <c r="M48" s="107"/>
@@ -13437,37 +13439,37 @@
     </row>
     <row r="49" spans="1:14" ht="57.6">
       <c r="A49" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="C49" s="125" t="s">
+        <v>339</v>
+      </c>
+      <c r="D49" s="217" t="s">
+        <v>340</v>
+      </c>
+      <c r="E49" s="83" t="s">
         <v>341</v>
-      </c>
-      <c r="B49" s="74" t="s">
-        <v>342</v>
-      </c>
-      <c r="C49" s="125" t="s">
-        <v>343</v>
-      </c>
-      <c r="D49" s="217" t="s">
-        <v>344</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>345</v>
       </c>
       <c r="F49" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H49" s="127" t="s">
         <v>19</v>
       </c>
       <c r="I49" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J49" s="129" t="s">
         <v>66</v>
       </c>
       <c r="K49" s="130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L49" s="129"/>
       <c r="M49" s="129"/>
@@ -13475,19 +13477,19 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="121" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C50" s="121" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D50" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="132" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F50" s="124" t="s">
         <v>17</v>
@@ -13499,13 +13501,13 @@
         <v>81</v>
       </c>
       <c r="I50" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J50" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K50" s="106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L50" s="107"/>
       <c r="M50" s="107"/>
@@ -13513,19 +13515,19 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="125" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B51" s="74" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C51" s="125" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D51" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F51" s="127" t="s">
         <v>17</v>
@@ -13543,7 +13545,7 @@
         <v>29</v>
       </c>
       <c r="K51" s="130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L51" s="129"/>
       <c r="M51" s="129"/>
@@ -13551,13 +13553,13 @@
     </row>
     <row r="52" spans="1:14" ht="84.75" customHeight="1">
       <c r="A52" s="121" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B52" s="35" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C52" s="121" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D52" s="132" t="s">
         <v>16</v>
@@ -13567,7 +13569,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="124" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H52" s="124" t="s">
         <v>19</v>
@@ -13780,42 +13782,42 @@
         <v>10</v>
       </c>
       <c r="L1" s="223" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="223" t="s">
+        <v>355</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>356</v>
+      </c>
+      <c r="O1" s="108" t="s">
+        <v>357</v>
+      </c>
+      <c r="P1" s="223" t="s">
         <v>358</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="Q1" s="223" t="s">
         <v>359</v>
       </c>
-      <c r="N1" s="108" t="s">
+      <c r="R1" s="224" t="s">
         <v>360</v>
       </c>
-      <c r="O1" s="108" t="s">
+      <c r="S1" s="224" t="s">
         <v>361</v>
       </c>
-      <c r="P1" s="223" t="s">
+      <c r="T1" s="224" t="s">
         <v>362</v>
       </c>
-      <c r="Q1" s="223" t="s">
+      <c r="U1" s="224" t="s">
         <v>363</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="V1" s="233" t="s">
         <v>364</v>
-      </c>
-      <c r="S1" s="224" t="s">
-        <v>365</v>
-      </c>
-      <c r="T1" s="224" t="s">
-        <v>366</v>
-      </c>
-      <c r="U1" s="224" t="s">
-        <v>367</v>
-      </c>
-      <c r="V1" s="233" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="28.8">
       <c r="A2" s="64" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B2" s="157" t="s">
         <v>61</v>
@@ -13824,10 +13826,10 @@
         <v>62</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E2" s="158" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
@@ -13847,25 +13849,25 @@
     </row>
     <row r="3" spans="1:22" ht="115.2">
       <c r="A3" s="68" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D3" s="162" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -13877,7 +13879,7 @@
         <v>66</v>
       </c>
       <c r="K3" s="136" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -13892,19 +13894,19 @@
     </row>
     <row r="4" spans="1:22" ht="129.6">
       <c r="A4" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="157" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="157" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>215</v>
-      </c>
       <c r="D4" s="71" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E4" s="158" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
@@ -13919,28 +13921,28 @@
         <v>28</v>
       </c>
       <c r="J4" s="160" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K4" s="136" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="L4" s="107"/>
     </row>
     <row r="5" spans="1:22" ht="43.2">
       <c r="A5" s="165" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C5" s="165" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F5" s="166" t="s">
         <v>35</v>
@@ -13958,7 +13960,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="136" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -13973,19 +13975,19 @@
     </row>
     <row r="6" spans="1:22" ht="72">
       <c r="A6" s="168" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B6" s="151" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C6" s="168" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F6" s="133" t="s">
         <v>17</v>
@@ -14007,25 +14009,25 @@
     </row>
     <row r="7" spans="1:22" ht="115.2">
       <c r="A7" s="125" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="125" t="s">
+        <v>388</v>
+      </c>
+      <c r="D7" s="171" t="s">
+        <v>389</v>
+      </c>
+      <c r="E7" s="81" t="s">
         <v>390</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>391</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>392</v>
-      </c>
-      <c r="D7" s="171" t="s">
-        <v>393</v>
-      </c>
-      <c r="E7" s="81" t="s">
-        <v>394</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -14050,25 +14052,25 @@
     </row>
     <row r="8" spans="1:22" ht="28.8">
       <c r="A8" s="64" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B8" s="157" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C8" s="172" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D8" s="143" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E8" s="135" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F8" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="159" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H8" s="159" t="s">
         <v>81</v>
@@ -14080,13 +14082,13 @@
         <v>29</v>
       </c>
       <c r="K8" s="136" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:22" ht="43.2">
       <c r="A9" s="165" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>77</v>
@@ -14098,13 +14100,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="173" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F9" s="166" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="166" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H9" s="166">
         <v>1</v>
@@ -14116,7 +14118,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="136" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
@@ -14861,45 +14863,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="225" t="s">
+        <v>396</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>397</v>
+      </c>
+      <c r="N1" s="223" t="s">
+        <v>398</v>
+      </c>
+      <c r="O1" s="224" t="s">
+        <v>399</v>
+      </c>
+      <c r="P1" s="232" t="s">
         <v>400</v>
       </c>
-      <c r="M1" s="108" t="s">
+      <c r="Q1" s="233" t="s">
         <v>401</v>
-      </c>
-      <c r="N1" s="223" t="s">
-        <v>402</v>
-      </c>
-      <c r="O1" s="224" t="s">
-        <v>403</v>
-      </c>
-      <c r="P1" s="232" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q1" s="233" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="64.349999999999994" customHeight="1">
       <c r="A2" s="64" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C2" s="172" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>19</v>
@@ -14911,31 +14913,31 @@
         <v>29</v>
       </c>
       <c r="K2" s="156" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L2" s="136"/>
     </row>
     <row r="3" spans="1:17" ht="129.6">
       <c r="A3" s="68" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -14947,7 +14949,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="L3" s="75"/>
       <c r="M3" s="61"/>
@@ -14957,25 +14959,25 @@
     </row>
     <row r="4" spans="1:17" ht="28.8">
       <c r="A4" s="64" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H4" s="159">
         <v>1</v>
@@ -14987,7 +14989,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="156" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L4" s="136"/>
     </row>
@@ -15810,86 +15812,86 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M1" s="223" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8">
       <c r="A2" s="121" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="128" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I2" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J2" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L2" s="141" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="M2" s="141" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="72">
       <c r="A3" s="125" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C3" s="125" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="85" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="127" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H3" s="127">
         <v>1</v>
       </c>
       <c r="I3" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J3" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -15908,7 +15910,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -15933,25 +15935,25 @@
     </row>
     <row r="5" spans="1:13" ht="43.2">
       <c r="A5" s="125" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H5" s="127">
         <v>1</v>
@@ -15963,32 +15965,32 @@
         <v>29</v>
       </c>
       <c r="K5" s="98" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
     </row>
     <row r="6" spans="1:13" ht="57.6">
       <c r="A6" s="121" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>81</v>
@@ -16000,36 +16002,36 @@
         <v>29</v>
       </c>
       <c r="K6" s="98" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L6" s="107" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M6" s="107" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="134" t="s">
+        <v>446</v>
+      </c>
+      <c r="D7" s="185" t="s">
+        <v>447</v>
+      </c>
+      <c r="E7" s="126" t="s">
         <v>448</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>449</v>
-      </c>
-      <c r="C7" s="134" t="s">
-        <v>450</v>
-      </c>
-      <c r="D7" s="185" t="s">
-        <v>451</v>
-      </c>
-      <c r="E7" s="126" t="s">
-        <v>452</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="156" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -16041,7 +16043,7 @@
         <v>29</v>
       </c>
       <c r="K7" s="98" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -16060,7 +16062,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>17</v>
@@ -16072,32 +16074,32 @@
         <v>19</v>
       </c>
       <c r="I8" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="L8" s="107"/>
       <c r="M8" s="107"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="125" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" s="74" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D9" s="187" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="126" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>17</v>
@@ -16115,32 +16117,32 @@
         <v>29</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
     </row>
     <row r="10" spans="1:13" ht="57.6">
       <c r="A10" s="121" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C10" s="141" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H10" s="124" t="s">
         <v>81</v>
@@ -16152,32 +16154,32 @@
         <v>37</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
-    <row r="11" spans="1:13" ht="72">
+    <row r="11" spans="1:13" ht="43.2">
       <c r="A11" s="125" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B11" s="74" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C11" s="125" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D11" s="154" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E11" s="126" t="s">
-        <v>468</v>
+        <v>671</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="H11" s="127">
         <v>1</v>
@@ -16189,7 +16191,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
@@ -16208,7 +16210,7 @@
         <v>85</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -16226,14 +16228,14 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
     <row r="13" spans="1:13" ht="72">
       <c r="A13" s="125" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B13" s="74" t="s">
         <v>90</v>
@@ -16245,50 +16247,50 @@
         <v>92</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="H13" s="127">
         <v>1</v>
       </c>
       <c r="I13" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="72">
       <c r="A14" s="121" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C14" s="121" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="124" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H14" s="124" t="s">
         <v>19</v>
@@ -16300,57 +16302,57 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
     <row r="15" spans="1:13" ht="100.8">
       <c r="A15" s="125" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B15" s="74" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C15" s="125" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D15" s="185" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E15" s="80" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="127" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H15" s="127" t="s">
         <v>81</v>
       </c>
       <c r="I15" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="C16" s="141" t="s">
         <v>97</v>
-      </c>
-      <c r="C16" s="141" t="s">
-        <v>98</v>
       </c>
       <c r="D16" s="189" t="s">
         <v>16</v>
@@ -16360,7 +16362,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="124" t="s">
         <v>81</v>
@@ -16372,32 +16374,32 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13" ht="57.6">
       <c r="A17" s="125" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B17" s="74" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C17" s="125" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D17" s="185" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E17" s="74" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -16409,32 +16411,32 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>109</v>
       </c>
       <c r="D18" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" s="124" t="s">
         <v>81</v>
@@ -16446,30 +16448,30 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
     </row>
     <row r="19" spans="1:13" ht="28.8">
       <c r="A19" s="125" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B19" s="126" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C19" s="125" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D19" s="126"/>
       <c r="E19" s="80" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>81</v>
@@ -16482,33 +16484,33 @@
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="129" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="M19" s="129" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="129.6">
       <c r="A20" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>112</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>113</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="133">
         <v>1</v>
@@ -16520,32 +16522,32 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
     <row r="21" spans="1:13" ht="43.2">
       <c r="A21" s="125" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E21" s="81" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H21" s="127" t="s">
         <v>81</v>
@@ -16557,32 +16559,32 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13" ht="57.6">
       <c r="A22" s="121" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>81</v>
@@ -16599,19 +16601,19 @@
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="125" t="s">
         <v>133</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>134</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -16623,13 +16625,13 @@
         <v>19</v>
       </c>
       <c r="I23" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17111,7 +17113,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17128,7 +17130,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17146,7 +17148,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17176,13 +17178,13 @@
         <v>52</v>
       </c>
       <c r="I3" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J3" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17202,7 +17204,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17220,31 +17222,31 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="L4" s="129"/>
     </row>
     <row r="5" spans="1:12" ht="43.2">
       <c r="A5" s="121" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="121" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="D5" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="121" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="122" t="s">
-        <v>198</v>
-      </c>
       <c r="E5" s="135" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H5" s="124" t="s">
         <v>81</v>
@@ -17272,7 +17274,7 @@
         <v>63</v>
       </c>
       <c r="E6" s="247" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F6" s="244" t="s">
         <v>17</v>
@@ -17290,7 +17292,7 @@
         <v>66</v>
       </c>
       <c r="K6" s="243" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="L6" s="242"/>
     </row>
@@ -17360,55 +17362,55 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="C11" s="121" t="s">
         <v>97</v>
-      </c>
-      <c r="C11" s="121" t="s">
-        <v>98</v>
       </c>
       <c r="D11" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="L11" s="107"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="126" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="126" t="s">
+      <c r="C12" s="125" t="s">
         <v>102</v>
-      </c>
-      <c r="C12" s="125" t="s">
-        <v>103</v>
       </c>
       <c r="D12" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -17420,13 +17422,13 @@
         <v>81</v>
       </c>
       <c r="I12" s="127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -17434,61 +17436,61 @@
     </row>
     <row r="13" spans="1:12" ht="28.8">
       <c r="A13" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="132" t="s">
+      <c r="C13" s="121" t="s">
         <v>108</v>
-      </c>
-      <c r="C13" s="121" t="s">
-        <v>109</v>
       </c>
       <c r="D13" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="124" t="s">
         <v>81</v>
       </c>
       <c r="I13" s="124" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="107" t="s">
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="L13" s="107"/>
     </row>
     <row r="14" spans="1:12" ht="48.9" customHeight="1">
       <c r="A14" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="125" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="125" t="s">
+      <c r="C14" s="125" t="s">
         <v>123</v>
-      </c>
-      <c r="C14" s="125" t="s">
-        <v>124</v>
       </c>
       <c r="D14" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="193" t="s">
         <v>19</v>
@@ -17500,27 +17502,27 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="L14" s="129" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="121" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="121" t="s">
+      <c r="C15" s="121" t="s">
         <v>133</v>
-      </c>
-      <c r="C15" s="121" t="s">
-        <v>134</v>
       </c>
       <c r="D15" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -17538,7 +17540,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L15" s="107"/>
     </row>
@@ -17819,30 +17821,30 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="92.4">
       <c r="A2" s="131" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="D2" s="143" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="143" t="s">
-        <v>153</v>
-      </c>
       <c r="E2" s="82" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H2" s="124">
         <v>1</v>
@@ -17854,7 +17856,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -17892,25 +17894,25 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C4" s="121" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D4" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="124" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H4" s="124" t="s">
         <v>19</v>
@@ -17998,13 +18000,13 @@
     </row>
     <row r="7" spans="1:12" ht="28.8">
       <c r="A7" s="125" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>112</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>113</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>16</v>
@@ -18014,7 +18016,7 @@
         <v>17</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>19</v>
@@ -18042,7 +18044,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18060,101 +18062,101 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="43.2">
       <c r="A9" s="125" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H9" s="127">
         <v>1</v>
       </c>
       <c r="I9" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J9" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
       <c r="A10" s="121" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C10" s="121" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H10" s="133">
         <v>1</v>
       </c>
       <c r="I10" s="107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="107" t="s">
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="L10" s="107"/>
     </row>
     <row r="11" spans="1:12" ht="43.2">
       <c r="A11" s="125" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B11" s="74" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D11" s="154" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E11" s="126"/>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -18170,13 +18172,13 @@
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="121" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C12" s="121" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18186,7 +18188,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H12" s="124" t="s">
         <v>19</v>
@@ -18202,19 +18204,19 @@
     </row>
     <row r="13" spans="1:12" ht="57.6">
       <c r="A13" s="191" t="s">
+        <v>211</v>
+      </c>
+      <c r="B13" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="134" t="s">
         <v>213</v>
-      </c>
-      <c r="B13" s="74" t="s">
-        <v>214</v>
-      </c>
-      <c r="C13" s="134" t="s">
-        <v>215</v>
       </c>
       <c r="D13" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18236,13 +18238,13 @@
     </row>
     <row r="14" spans="1:12" ht="28.8">
       <c r="A14" s="121" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" s="121" t="s">
         <v>230</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>232</v>
       </c>
       <c r="D14" s="132" t="s">
         <v>16</v>
@@ -18268,19 +18270,19 @@
     </row>
     <row r="15" spans="1:12" ht="57.6">
       <c r="A15" s="125" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B15" s="74" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C15" s="125" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18314,7 +18316,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18348,13 +18350,13 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H17" s="127">
         <v>1</v>
@@ -18366,31 +18368,31 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="L17" s="129"/>
     </row>
     <row r="18" spans="1:12" ht="57.6">
       <c r="A18" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="121" t="s">
         <v>97</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>98</v>
       </c>
       <c r="D18" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" s="124" t="s">
         <v>81</v>
@@ -18406,13 +18408,13 @@
     </row>
     <row r="19" spans="1:12" ht="28.8">
       <c r="A19" s="125" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B19" s="74" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D19" s="126" t="s">
         <v>16</v>
@@ -18422,7 +18424,7 @@
         <v>17</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H19" s="127" t="s">
         <v>19</v>
@@ -18435,24 +18437,24 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="43.2">
       <c r="A20" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="C20" s="121" t="s">
         <v>102</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>103</v>
       </c>
       <c r="D20" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -18476,19 +18478,19 @@
     </row>
     <row r="21" spans="1:12" ht="57.6">
       <c r="A21" s="125" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -18506,33 +18508,33 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="L21" s="192" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="43.2">
       <c r="A22" s="121" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D22" s="143" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>52</v>
@@ -18548,19 +18550,19 @@
     </row>
     <row r="23" spans="1:12" ht="28.8">
       <c r="A23" s="125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="C23" s="134" t="s">
         <v>133</v>
-      </c>
-      <c r="C23" s="134" t="s">
-        <v>134</v>
       </c>
       <c r="D23" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -18578,7 +18580,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="L23" s="195"/>
     </row>

--- a/Documents/Metadata_CoreGenericHealth_v2.xlsx
+++ b/Documents/Metadata_CoreGenericHealth_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB2FDFB2-6BD5-4989-9906-EC23F51E3B08}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{B604F9AE-9787-411E-AB68-6C0D2821F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56501FCB-3D8B-4B1A-811D-B69BAEFCE65B}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-12765" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="676">
   <si>
     <t>Property label</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>healthdcatap:retentionPeriod</t>
   </si>
   <si>
-    <t>This property makes use of the class dct:PeriodOfTime, in which a start and end date should be provided.</t>
-  </si>
-  <si>
     <t>fill in in 'Period of Time' tab</t>
   </si>
   <si>
@@ -2619,6 +2616,20 @@
   <si>
     <t>One (or many) categoiesy or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
 Example value could be: dpv:ResearchAndDevelopment.</t>
+  </si>
+  <si>
+    <t>Indicate with this property in case the Dataset is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
+This property makes use of the class dct:PeriodOfTime, in which a start and end date can be provided.
+If the Dataset is available indefinitely, leave the property empty (cardinality is 0..1; it is only meaningful when a retention limit applies).
+If only a start is known, provide dcat:startDate only (open-ended interval, as allowed by dct:PeriodOfTime).
+If a limit is known, provide both dcat:startDate and dcat:endDate.</t>
+  </si>
+  <si>
+    <t>Indicate with this property in case the Distribution is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
+This property makes use of the class dct:PeriodOfTime, in which a start and end date can be provided.
+If the Distribution is available indefinitely, leave the property empty (cardinality is 0..1; it is only meaningful when a retention limit applies).
+If only a start is known, provide dcat:startDate only (open-ended interval, as allowed by dct:PeriodOfTime).
+If a limit is known, provide both dcat:startDate and dcat:endDate.</t>
   </si>
 </sst>
 </file>
@@ -3766,43 +3777,43 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7439,33 +7450,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>553</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>554</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>555</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>556</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="72">
       <c r="A2" s="196" t="s">
+        <v>557</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>558</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="76" t="s">
         <v>559</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>560</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -7474,7 +7485,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -7489,13 +7500,13 @@
     </row>
     <row r="3" spans="1:15" ht="28.8">
       <c r="A3" s="68" t="s">
+        <v>562</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>563</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="77" t="s">
         <v>564</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>565</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -7634,36 +7645,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>565</v>
+      </c>
+      <c r="M1" s="220" t="s">
         <v>566</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="N1" s="226" t="s">
         <v>567</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="O1" s="230" t="s">
         <v>568</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="P1" s="227" t="s">
         <v>569</v>
       </c>
-      <c r="P1" s="227" t="s">
+      <c r="Q1" s="231" t="s">
         <v>570</v>
       </c>
-      <c r="Q1" s="231" t="s">
+      <c r="R1" s="233" t="s">
         <v>571</v>
-      </c>
-      <c r="R1" s="233" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="58" t="s">
+        <v>572</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>573</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="76" t="s">
         <v>574</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>575</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -7691,13 +7702,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="48" t="s">
+        <v>575</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>576</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>577</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>578</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8359,33 +8370,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>578</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>579</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>580</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>581</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="43.2">
       <c r="A2" s="84" t="s">
+        <v>582</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>583</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>584</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>585</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8415,19 +8426,19 @@
     </row>
     <row r="3" spans="1:15" ht="129.6">
       <c r="A3" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>587</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>588</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="D3" s="234" t="s">
         <v>589</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="E3" s="50" t="s">
         <v>590</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>591</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -8553,33 +8564,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>591</v>
+      </c>
+      <c r="M1" s="229" t="s">
         <v>592</v>
       </c>
-      <c r="M1" s="229" t="s">
+      <c r="N1" s="228" t="s">
         <v>593</v>
       </c>
-      <c r="N1" s="228" t="s">
+      <c r="O1" s="233" t="s">
         <v>594</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="158.4">
       <c r="A2" s="84" t="s">
+        <v>595</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>587</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>588</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>596</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>588</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>589</v>
-      </c>
-      <c r="D2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>597</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>598</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
@@ -8600,19 +8611,19 @@
     </row>
     <row r="3" spans="1:15" ht="43.2">
       <c r="A3" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>599</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>600</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>601</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
@@ -8738,33 +8749,33 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>602</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>603</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>604</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>605</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="100.8">
       <c r="A2" s="84" t="s">
+        <v>606</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>607</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>608</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>609</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -8785,19 +8796,19 @@
     </row>
     <row r="3" spans="1:15" ht="57.6">
       <c r="A3" s="48" t="s">
+        <v>610</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>611</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>612</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>613</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -8901,7 +8912,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -8924,13 +8935,13 @@
     </row>
     <row r="2" spans="1:10" ht="28.8">
       <c r="A2" s="63" t="s">
+        <v>615</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>616</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="C2" s="44" t="s">
         <v>617</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>618</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -8938,7 +8949,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -8952,13 +8963,13 @@
     </row>
     <row r="3" spans="1:10" ht="43.2">
       <c r="A3" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>620</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>621</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>622</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -8966,10 +8977,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
+        <v>622</v>
+      </c>
+      <c r="H3" s="48" t="s">
         <v>623</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>624</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -8980,13 +8991,13 @@
     </row>
     <row r="4" spans="1:10" ht="43.2">
       <c r="A4" s="63" t="s">
+        <v>624</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>625</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="C4" s="44" t="s">
         <v>626</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>627</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -8994,10 +9005,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="H4" s="65" t="s">
         <v>628</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>629</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -9008,26 +9019,26 @@
     </row>
     <row r="5" spans="1:10" ht="43.2">
       <c r="A5" s="67" t="s">
+        <v>629</v>
+      </c>
+      <c r="B5" s="50" t="s">
         <v>630</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>631</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>632</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
+        <v>633</v>
+      </c>
+      <c r="H5" s="48" t="s">
         <v>634</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>635</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -9038,13 +9049,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8">
       <c r="A6" s="63" t="s">
+        <v>635</v>
+      </c>
+      <c r="B6" s="73" t="s">
         <v>636</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="C6" s="44" t="s">
         <v>637</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>638</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -9055,7 +9066,7 @@
         <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -9066,13 +9077,13 @@
     </row>
     <row r="7" spans="1:10" ht="28.8">
       <c r="A7" s="67" t="s">
+        <v>638</v>
+      </c>
+      <c r="B7" s="50" t="s">
         <v>639</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>640</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>641</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -9094,23 +9105,23 @@
     </row>
     <row r="8" spans="1:10" ht="86.4">
       <c r="A8" s="63" t="s">
+        <v>641</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>642</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="C8" s="44" t="s">
         <v>643</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>644</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -9124,13 +9135,13 @@
     </row>
     <row r="9" spans="1:10" ht="28.8">
       <c r="A9" s="67" t="s">
+        <v>646</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>647</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>648</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>649</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -9138,7 +9149,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -9152,23 +9163,23 @@
     </row>
     <row r="10" spans="1:10" ht="28.8">
       <c r="A10" s="63" t="s">
+        <v>650</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>651</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="44" t="s">
         <v>652</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>653</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -9633,36 +9644,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>654</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>655</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="233" t="s">
         <v>656</v>
-      </c>
-      <c r="N1" s="233" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="72">
       <c r="A2" s="44" t="s">
+        <v>657</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>658</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>659</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="78" t="s">
         <v>660</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="E2" s="197" t="s">
         <v>661</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>662</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -9676,13 +9687,13 @@
     </row>
     <row r="3" spans="1:14" ht="71.25" customHeight="1">
       <c r="A3" s="49" t="s">
+        <v>663</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>664</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="48" t="s">
         <v>665</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>666</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -9692,7 +9703,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -10606,19 +10617,19 @@
       <c r="M7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="238" t="s">
+      <c r="A8" s="235" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="238" t="s">
+      <c r="C8" s="235" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="240" t="s">
+      <c r="E8" s="238" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="237" t="s">
@@ -10630,83 +10641,83 @@
       <c r="H8" s="237" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="235" t="s">
+      <c r="I8" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="235" t="s">
+      <c r="J8" s="239" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A9" s="238"/>
+      <c r="A9" s="235"/>
       <c r="B9" s="241"/>
-      <c r="C9" s="238"/>
+      <c r="C9" s="235"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="240"/>
+      <c r="E9" s="238"/>
       <c r="F9" s="237"/>
       <c r="G9" s="237"/>
       <c r="H9" s="237"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
     </row>
     <row r="10" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A10" s="238"/>
+      <c r="A10" s="235"/>
       <c r="B10" s="241"/>
-      <c r="C10" s="238"/>
+      <c r="C10" s="235"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="240"/>
+      <c r="E10" s="238"/>
       <c r="F10" s="237"/>
       <c r="G10" s="237"/>
       <c r="H10" s="237"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
     </row>
     <row r="11" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A11" s="238"/>
+      <c r="A11" s="235"/>
       <c r="B11" s="241"/>
-      <c r="C11" s="238"/>
+      <c r="C11" s="235"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="240"/>
+      <c r="E11" s="238"/>
       <c r="F11" s="237"/>
       <c r="G11" s="237"/>
       <c r="H11" s="237"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="235"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
     </row>
     <row r="12" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A12" s="238"/>
+      <c r="A12" s="235"/>
       <c r="B12" s="241"/>
-      <c r="C12" s="238"/>
+      <c r="C12" s="235"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="240"/>
+      <c r="E12" s="238"/>
       <c r="F12" s="237"/>
       <c r="G12" s="237"/>
       <c r="H12" s="237"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
+      <c r="I12" s="239"/>
+      <c r="J12" s="239"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="235"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
     </row>
     <row r="13" spans="1:13" ht="43.2">
       <c r="A13" s="125" t="s">
@@ -10831,7 +10842,7 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -11525,17 +11536,17 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <mergeCells count="11">
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="J8:J12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="F8:F12"/>
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="190" priority="16" operator="equal">
@@ -11807,7 +11818,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>35</v>
@@ -12182,19 +12193,19 @@
       <c r="N13" s="129"/>
     </row>
     <row r="14" spans="1:14" ht="43.2">
-      <c r="A14" s="238" t="s">
+      <c r="A14" s="235" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="239" t="s">
+      <c r="B14" s="236" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="238" t="s">
+      <c r="C14" s="235" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="240" t="s">
+      <c r="E14" s="238" t="s">
         <v>199</v>
       </c>
       <c r="F14" s="237" t="s">
@@ -12206,78 +12217,78 @@
       <c r="H14" s="237" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="235" t="s">
+      <c r="I14" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="235" t="s">
+      <c r="J14" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="236"/>
-      <c r="L14" s="235"/>
+      <c r="K14" s="240"/>
+      <c r="L14" s="239"/>
     </row>
     <row r="15" spans="1:14" ht="43.2">
-      <c r="A15" s="238"/>
-      <c r="B15" s="239"/>
-      <c r="C15" s="238"/>
+      <c r="A15" s="235"/>
+      <c r="B15" s="236"/>
+      <c r="C15" s="235"/>
       <c r="D15" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="240"/>
+      <c r="E15" s="238"/>
       <c r="F15" s="237"/>
       <c r="G15" s="237"/>
       <c r="H15" s="237"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="235"/>
+      <c r="I15" s="239"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="240"/>
+      <c r="L15" s="239"/>
     </row>
     <row r="16" spans="1:14" ht="28.8">
-      <c r="A16" s="238"/>
-      <c r="B16" s="239"/>
-      <c r="C16" s="238"/>
+      <c r="A16" s="235"/>
+      <c r="B16" s="236"/>
+      <c r="C16" s="235"/>
       <c r="D16" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="240"/>
+      <c r="E16" s="238"/>
       <c r="F16" s="237"/>
       <c r="G16" s="237"/>
       <c r="H16" s="237"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="235"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="240"/>
+      <c r="L16" s="239"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="238"/>
-      <c r="B17" s="239"/>
-      <c r="C17" s="238"/>
+      <c r="A17" s="235"/>
+      <c r="B17" s="236"/>
+      <c r="C17" s="235"/>
       <c r="D17" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="240"/>
+      <c r="E17" s="238"/>
       <c r="F17" s="237"/>
       <c r="G17" s="237"/>
       <c r="H17" s="237"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="235"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="240"/>
+      <c r="L17" s="239"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="238"/>
-      <c r="B18" s="239"/>
-      <c r="C18" s="238"/>
+      <c r="A18" s="235"/>
+      <c r="B18" s="236"/>
+      <c r="C18" s="235"/>
       <c r="D18" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="240"/>
+      <c r="E18" s="238"/>
       <c r="F18" s="237"/>
       <c r="G18" s="237"/>
       <c r="H18" s="237"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="235"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="240"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="125" t="s">
@@ -12555,7 +12566,7 @@
         <v>237</v>
       </c>
       <c r="E26" s="132" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F26" s="124" t="s">
         <v>17</v>
@@ -12931,7 +12942,7 @@
         <v>285</v>
       </c>
       <c r="E36" s="138" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F36" s="124" t="s">
         <v>17</v>
@@ -13117,7 +13128,7 @@
       </c>
       <c r="L40" s="107"/>
     </row>
-    <row r="41" spans="1:14" ht="28.8">
+    <row r="41" spans="1:14" ht="158.4">
       <c r="A41" s="125" t="s">
         <v>306</v>
       </c>
@@ -13131,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="E41" s="74" t="s">
-        <v>309</v>
+        <v>674</v>
       </c>
       <c r="F41" s="127" t="s">
         <v>17</v>
@@ -13152,30 +13163,30 @@
         <v>137</v>
       </c>
       <c r="L41" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M41" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N41" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
       <c r="A42" s="121" t="s">
+        <v>310</v>
+      </c>
+      <c r="B42" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="C42" s="121" t="s">
         <v>312</v>
-      </c>
-      <c r="C42" s="121" t="s">
-        <v>313</v>
       </c>
       <c r="D42" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="132" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F42" s="124" t="s">
         <v>17</v>
@@ -13196,26 +13207,26 @@
         <v>138</v>
       </c>
       <c r="L42" s="141" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M42" s="107"/>
       <c r="N42" s="107"/>
     </row>
     <row r="43" spans="1:14" ht="28.8">
       <c r="A43" s="125" t="s">
+        <v>315</v>
+      </c>
+      <c r="B43" s="74" t="s">
         <v>316</v>
       </c>
-      <c r="B43" s="74" t="s">
+      <c r="C43" s="125" t="s">
         <v>317</v>
-      </c>
-      <c r="C43" s="125" t="s">
-        <v>318</v>
       </c>
       <c r="D43" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="205" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F43" s="127" t="s">
         <v>17</v>
@@ -13236,26 +13247,26 @@
         <v>139</v>
       </c>
       <c r="L43" s="134" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M43" s="129"/>
       <c r="N43" s="129"/>
     </row>
     <row r="44" spans="1:14" ht="57.6">
       <c r="A44" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="B44" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="C44" s="121" t="s">
         <v>322</v>
       </c>
-      <c r="C44" s="121" t="s">
+      <c r="D44" s="143" t="s">
         <v>323</v>
       </c>
-      <c r="D44" s="143" t="s">
+      <c r="E44" s="132" t="s">
         <v>324</v>
-      </c>
-      <c r="E44" s="132" t="s">
-        <v>325</v>
       </c>
       <c r="F44" s="124" t="s">
         <v>17</v>
@@ -13293,7 +13304,7 @@
         <v>16</v>
       </c>
       <c r="E45" s="74" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F45" s="127" t="s">
         <v>17</v>
@@ -13314,36 +13325,36 @@
         <v>125</v>
       </c>
       <c r="L45" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M45" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N45" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="57.6">
       <c r="A46" s="121" t="s">
+        <v>326</v>
+      </c>
+      <c r="B46" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="C46" s="141" t="s">
         <v>328</v>
-      </c>
-      <c r="C46" s="141" t="s">
-        <v>329</v>
       </c>
       <c r="D46" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F46" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="124" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H46" s="124" t="s">
         <v>81</v>
@@ -13363,19 +13374,19 @@
     </row>
     <row r="47" spans="1:14" ht="74.25" customHeight="1">
       <c r="A47" s="125" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B47" s="74" t="s">
         <v>127</v>
       </c>
       <c r="C47" s="125" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="142" t="s">
         <v>333</v>
       </c>
-      <c r="D47" s="142" t="s">
+      <c r="E47" s="74" t="s">
         <v>334</v>
-      </c>
-      <c r="E47" s="74" t="s">
-        <v>335</v>
       </c>
       <c r="F47" s="127" t="s">
         <v>35</v>
@@ -13413,7 +13424,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="132" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F48" s="124" t="s">
         <v>35</v>
@@ -13439,19 +13450,19 @@
     </row>
     <row r="49" spans="1:14" ht="57.6">
       <c r="A49" s="125" t="s">
+        <v>336</v>
+      </c>
+      <c r="B49" s="74" t="s">
         <v>337</v>
       </c>
-      <c r="B49" s="74" t="s">
+      <c r="C49" s="125" t="s">
         <v>338</v>
       </c>
-      <c r="C49" s="125" t="s">
+      <c r="D49" s="217" t="s">
         <v>339</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="E49" s="83" t="s">
         <v>340</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>341</v>
       </c>
       <c r="F49" s="127" t="s">
         <v>17</v>
@@ -13477,19 +13488,19 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="121" t="s">
+        <v>341</v>
+      </c>
+      <c r="B50" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="C50" s="121" t="s">
         <v>343</v>
-      </c>
-      <c r="C50" s="121" t="s">
-        <v>344</v>
       </c>
       <c r="D50" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="132" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F50" s="124" t="s">
         <v>17</v>
@@ -13515,19 +13526,19 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="125" t="s">
+        <v>345</v>
+      </c>
+      <c r="B51" s="74" t="s">
         <v>346</v>
       </c>
-      <c r="B51" s="74" t="s">
+      <c r="C51" s="125" t="s">
         <v>347</v>
-      </c>
-      <c r="C51" s="125" t="s">
-        <v>348</v>
       </c>
       <c r="D51" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F51" s="127" t="s">
         <v>17</v>
@@ -13553,13 +13564,13 @@
     </row>
     <row r="52" spans="1:14" ht="84.75" customHeight="1">
       <c r="A52" s="121" t="s">
+        <v>349</v>
+      </c>
+      <c r="B52" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="C52" s="121" t="s">
         <v>351</v>
-      </c>
-      <c r="C52" s="121" t="s">
-        <v>352</v>
       </c>
       <c r="D52" s="132" t="s">
         <v>16</v>
@@ -13569,7 +13580,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="124" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H52" s="124" t="s">
         <v>19</v>
@@ -13605,17 +13616,17 @@
     <sortCondition ref="A2:A53"/>
   </sortState>
   <mergeCells count="11">
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
     <mergeCell ref="L14:L18"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="G14:G18"/>
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="J14:J18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F14 F19:F53">
     <cfRule type="cellIs" dxfId="171" priority="8" operator="equal">
@@ -13782,42 +13793,42 @@
         <v>10</v>
       </c>
       <c r="L1" s="223" t="s">
+        <v>353</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>354</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="N1" s="108" t="s">
         <v>355</v>
       </c>
-      <c r="N1" s="108" t="s">
+      <c r="O1" s="108" t="s">
         <v>356</v>
       </c>
-      <c r="O1" s="108" t="s">
+      <c r="P1" s="223" t="s">
         <v>357</v>
       </c>
-      <c r="P1" s="223" t="s">
+      <c r="Q1" s="223" t="s">
         <v>358</v>
       </c>
-      <c r="Q1" s="223" t="s">
+      <c r="R1" s="224" t="s">
         <v>359</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="S1" s="224" t="s">
         <v>360</v>
       </c>
-      <c r="S1" s="224" t="s">
+      <c r="T1" s="224" t="s">
         <v>361</v>
       </c>
-      <c r="T1" s="224" t="s">
+      <c r="U1" s="224" t="s">
         <v>362</v>
       </c>
-      <c r="U1" s="224" t="s">
+      <c r="V1" s="233" t="s">
         <v>363</v>
-      </c>
-      <c r="V1" s="233" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="28.8">
       <c r="A2" s="64" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B2" s="157" t="s">
         <v>61</v>
@@ -13826,10 +13837,10 @@
         <v>62</v>
       </c>
       <c r="D2" s="152" t="s">
+        <v>365</v>
+      </c>
+      <c r="E2" s="158" t="s">
         <v>366</v>
-      </c>
-      <c r="E2" s="158" t="s">
-        <v>367</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
@@ -13849,25 +13860,25 @@
     </row>
     <row r="3" spans="1:22" ht="115.2">
       <c r="A3" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="68" t="s">
         <v>369</v>
-      </c>
-      <c r="C3" s="68" t="s">
-        <v>370</v>
       </c>
       <c r="D3" s="162" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -13879,7 +13890,7 @@
         <v>66</v>
       </c>
       <c r="K3" s="136" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -13903,10 +13914,10 @@
         <v>213</v>
       </c>
       <c r="D4" s="71" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="158" t="s">
         <v>373</v>
-      </c>
-      <c r="E4" s="158" t="s">
-        <v>374</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
@@ -13921,28 +13932,28 @@
         <v>28</v>
       </c>
       <c r="J4" s="160" t="s">
+        <v>374</v>
+      </c>
+      <c r="K4" s="136" t="s">
         <v>375</v>
-      </c>
-      <c r="K4" s="136" t="s">
-        <v>376</v>
       </c>
       <c r="L4" s="107"/>
     </row>
     <row r="5" spans="1:22" ht="43.2">
       <c r="A5" s="165" t="s">
+        <v>376</v>
+      </c>
+      <c r="B5" s="75" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="C5" s="165" t="s">
         <v>378</v>
-      </c>
-      <c r="C5" s="165" t="s">
-        <v>379</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F5" s="166" t="s">
         <v>35</v>
@@ -13960,7 +13971,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="136" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -13975,19 +13986,19 @@
     </row>
     <row r="6" spans="1:22" ht="72">
       <c r="A6" s="168" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" s="151" t="s">
         <v>382</v>
       </c>
-      <c r="B6" s="151" t="s">
+      <c r="C6" s="168" t="s">
         <v>383</v>
-      </c>
-      <c r="C6" s="168" t="s">
-        <v>384</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F6" s="133" t="s">
         <v>17</v>
@@ -14009,19 +14020,19 @@
     </row>
     <row r="7" spans="1:22" ht="115.2">
       <c r="A7" s="125" t="s">
+        <v>385</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>386</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>387</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="D7" s="171" t="s">
         <v>388</v>
       </c>
-      <c r="D7" s="171" t="s">
+      <c r="E7" s="81" t="s">
         <v>389</v>
-      </c>
-      <c r="E7" s="81" t="s">
-        <v>390</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
@@ -14052,19 +14063,19 @@
     </row>
     <row r="8" spans="1:22" ht="28.8">
       <c r="A8" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" s="157" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="157" t="s">
+      <c r="C8" s="172" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="172" t="s">
-        <v>339</v>
-      </c>
       <c r="D8" s="143" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E8" s="135" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F8" s="159" t="s">
         <v>17</v>
@@ -14082,13 +14093,13 @@
         <v>29</v>
       </c>
       <c r="K8" s="136" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:22" ht="43.2">
       <c r="A9" s="165" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>77</v>
@@ -14100,7 +14111,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="173" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F9" s="166" t="s">
         <v>35</v>
@@ -14118,7 +14129,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="136" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
@@ -14863,45 +14874,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="225" t="s">
+        <v>395</v>
+      </c>
+      <c r="M1" s="108" t="s">
         <v>396</v>
       </c>
-      <c r="M1" s="108" t="s">
+      <c r="N1" s="223" t="s">
         <v>397</v>
       </c>
-      <c r="N1" s="223" t="s">
+      <c r="O1" s="224" t="s">
         <v>398</v>
       </c>
-      <c r="O1" s="224" t="s">
+      <c r="P1" s="232" t="s">
         <v>399</v>
       </c>
-      <c r="P1" s="232" t="s">
+      <c r="Q1" s="233" t="s">
         <v>400</v>
-      </c>
-      <c r="Q1" s="233" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="64.349999999999994" customHeight="1">
       <c r="A2" s="64" t="s">
+        <v>401</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="172" t="s">
         <v>403</v>
-      </c>
-      <c r="C2" s="172" t="s">
-        <v>404</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>19</v>
@@ -14913,31 +14924,31 @@
         <v>29</v>
       </c>
       <c r="K2" s="156" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L2" s="136"/>
     </row>
     <row r="3" spans="1:17" ht="129.6">
       <c r="A3" s="68" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>407</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="68" t="s">
         <v>408</v>
-      </c>
-      <c r="C3" s="68" t="s">
-        <v>409</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -14949,7 +14960,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L3" s="75"/>
       <c r="M3" s="61"/>
@@ -14959,25 +14970,25 @@
     </row>
     <row r="4" spans="1:17" ht="28.8">
       <c r="A4" s="64" t="s">
+        <v>410</v>
+      </c>
+      <c r="B4" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="C4" s="64" t="s">
         <v>412</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>413</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H4" s="159">
         <v>1</v>
@@ -14989,7 +15000,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="156" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L4" s="136"/>
     </row>
@@ -15812,27 +15823,27 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
+        <v>416</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>417</v>
-      </c>
-      <c r="M1" s="223" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8">
       <c r="A2" s="121" t="s">
+        <v>418</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>419</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>420</v>
-      </c>
-      <c r="C2" s="121" t="s">
-        <v>421</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -15850,30 +15861,30 @@
         <v>37</v>
       </c>
       <c r="K2" s="98" t="s">
+        <v>422</v>
+      </c>
+      <c r="L2" s="141" t="s">
         <v>423</v>
       </c>
-      <c r="L2" s="141" t="s">
-        <v>424</v>
-      </c>
       <c r="M2" s="141" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="72">
       <c r="A3" s="125" t="s">
+        <v>424</v>
+      </c>
+      <c r="B3" s="74" t="s">
         <v>425</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="C3" s="125" t="s">
         <v>426</v>
-      </c>
-      <c r="C3" s="125" t="s">
-        <v>427</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="85" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>35</v>
@@ -15891,7 +15902,7 @@
         <v>37</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -15910,7 +15921,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -15935,25 +15946,25 @@
     </row>
     <row r="5" spans="1:13" ht="43.2">
       <c r="A5" s="125" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" s="74" t="s">
         <v>431</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="C5" s="134" t="s">
         <v>432</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>433</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="126" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H5" s="127">
         <v>1</v>
@@ -15965,32 +15976,32 @@
         <v>29</v>
       </c>
       <c r="K5" s="98" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
     </row>
     <row r="6" spans="1:13" ht="57.6">
       <c r="A6" s="121" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>437</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="121" t="s">
         <v>438</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>439</v>
       </c>
       <c r="D6" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H6" s="124" t="s">
         <v>81</v>
@@ -16002,36 +16013,36 @@
         <v>29</v>
       </c>
       <c r="K6" s="98" t="s">
+        <v>441</v>
+      </c>
+      <c r="L6" s="107" t="s">
         <v>442</v>
       </c>
-      <c r="L6" s="107" t="s">
-        <v>443</v>
-      </c>
       <c r="M6" s="107" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="43.2">
       <c r="A7" s="125" t="s">
+        <v>443</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>444</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="134" t="s">
         <v>445</v>
       </c>
-      <c r="C7" s="134" t="s">
+      <c r="D7" s="185" t="s">
         <v>446</v>
       </c>
-      <c r="D7" s="185" t="s">
+      <c r="E7" s="126" t="s">
         <v>447</v>
-      </c>
-      <c r="E7" s="126" t="s">
-        <v>448</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="156" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H7" s="127" t="s">
         <v>81</v>
@@ -16043,7 +16054,7 @@
         <v>29</v>
       </c>
       <c r="K7" s="98" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
@@ -16062,7 +16073,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>17</v>
@@ -16080,7 +16091,7 @@
         <v>29</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L8" s="107"/>
       <c r="M8" s="107"/>
@@ -16099,7 +16110,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="126" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>17</v>
@@ -16117,26 +16128,26 @@
         <v>29</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
     </row>
     <row r="10" spans="1:13" ht="57.6">
       <c r="A10" s="121" t="s">
+        <v>454</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="141" t="s">
         <v>456</v>
-      </c>
-      <c r="C10" s="141" t="s">
-        <v>457</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>17</v>
@@ -16154,32 +16165,32 @@
         <v>37</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L10" s="107"/>
       <c r="M10" s="107"/>
     </row>
     <row r="11" spans="1:13" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>459</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="125" t="s">
         <v>461</v>
       </c>
-      <c r="C11" s="125" t="s">
+      <c r="D11" s="154" t="s">
         <v>462</v>
       </c>
-      <c r="D11" s="154" t="s">
-        <v>463</v>
-      </c>
       <c r="E11" s="126" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F11" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H11" s="127">
         <v>1</v>
@@ -16191,7 +16202,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L11" s="129"/>
       <c r="M11" s="129"/>
@@ -16210,7 +16221,7 @@
         <v>85</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -16228,14 +16239,14 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L12" s="107"/>
       <c r="M12" s="107"/>
     </row>
     <row r="13" spans="1:13" ht="72">
       <c r="A13" s="125" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B13" s="74" t="s">
         <v>90</v>
@@ -16247,13 +16258,13 @@
         <v>92</v>
       </c>
       <c r="E13" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H13" s="127">
         <v>1</v>
@@ -16265,14 +16276,14 @@
         <v>37</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="L13" s="129"/>
       <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="72">
       <c r="A14" s="121" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>175</v>
@@ -16284,7 +16295,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -16302,32 +16313,32 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
     </row>
     <row r="15" spans="1:13" ht="100.8">
       <c r="A15" s="125" t="s">
+        <v>474</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>475</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>476</v>
       </c>
-      <c r="C15" s="125" t="s">
+      <c r="D15" s="185" t="s">
+        <v>446</v>
+      </c>
+      <c r="E15" s="80" t="s">
         <v>477</v>
-      </c>
-      <c r="D15" s="185" t="s">
-        <v>447</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>478</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="127" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H15" s="127" t="s">
         <v>81</v>
@@ -16339,7 +16350,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
@@ -16374,32 +16385,32 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
     </row>
     <row r="17" spans="1:13" ht="57.6">
       <c r="A17" s="125" t="s">
+        <v>480</v>
+      </c>
+      <c r="B17" s="74" t="s">
         <v>481</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="C17" s="125" t="s">
         <v>482</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="D17" s="185" t="s">
+        <v>446</v>
+      </c>
+      <c r="E17" s="74" t="s">
         <v>483</v>
-      </c>
-      <c r="D17" s="185" t="s">
-        <v>447</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>484</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="127" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H17" s="127" t="s">
         <v>81</v>
@@ -16411,7 +16422,7 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
@@ -16430,7 +16441,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="132" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -16448,12 +16459,12 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L18" s="107"/>
       <c r="M18" s="107"/>
     </row>
-    <row r="19" spans="1:13" ht="28.8">
+    <row r="19" spans="1:13" ht="185.4" customHeight="1">
       <c r="A19" s="125" t="s">
         <v>306</v>
       </c>
@@ -16461,11 +16472,11 @@
         <v>307</v>
       </c>
       <c r="C19" s="125" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D19" s="126"/>
-      <c r="E19" s="80" t="s">
-        <v>309</v>
+      <c r="E19" s="74" t="s">
+        <v>675</v>
       </c>
       <c r="F19" s="127" t="s">
         <v>17</v>
@@ -16484,10 +16495,10 @@
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="129" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M19" s="129" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="129.6">
@@ -16504,7 +16515,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F20" s="190" t="s">
         <v>35</v>
@@ -16522,26 +16533,26 @@
         <v>29</v>
       </c>
       <c r="K20" s="99" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
     </row>
     <row r="21" spans="1:13" ht="43.2">
       <c r="A21" s="125" t="s">
+        <v>320</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>321</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>322</v>
       </c>
-      <c r="C21" s="125" t="s">
-        <v>323</v>
-      </c>
       <c r="D21" s="154" t="s">
+        <v>491</v>
+      </c>
+      <c r="E21" s="81" t="s">
         <v>492</v>
-      </c>
-      <c r="E21" s="81" t="s">
-        <v>493</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -16559,32 +16570,32 @@
         <v>29</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L21" s="129"/>
       <c r="M21" s="129"/>
     </row>
     <row r="22" spans="1:13" ht="57.6">
       <c r="A22" s="121" t="s">
+        <v>326</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="C22" s="121" t="s">
         <v>328</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>329</v>
       </c>
       <c r="D22" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="132" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="124" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H22" s="124" t="s">
         <v>81</v>
@@ -16613,7 +16624,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>17</v>
@@ -16631,7 +16642,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
@@ -17113,7 +17124,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17130,7 +17141,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -17148,7 +17159,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L2" s="129"/>
     </row>
@@ -17184,7 +17195,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
@@ -17204,7 +17215,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -17222,7 +17233,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L4" s="129"/>
     </row>
@@ -17240,7 +17251,7 @@
         <v>196</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
@@ -17261,104 +17272,104 @@
       <c r="L5" s="107"/>
     </row>
     <row r="6" spans="1:12" ht="28.8">
-      <c r="A6" s="245" t="s">
+      <c r="A6" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="246" t="s">
+      <c r="B6" s="244" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="245" t="s">
+      <c r="C6" s="243" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="247" t="s">
+      <c r="E6" s="245" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="244" t="s">
+      <c r="F6" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="244" t="s">
+      <c r="G6" s="242" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="244" t="s">
+      <c r="H6" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="242" t="s">
+      <c r="I6" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="235" t="s">
+      <c r="J6" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="243" t="s">
-        <v>505</v>
-      </c>
-      <c r="L6" s="242"/>
+      <c r="K6" s="247" t="s">
+        <v>504</v>
+      </c>
+      <c r="L6" s="246"/>
     </row>
     <row r="7" spans="1:12" ht="28.8">
-      <c r="A7" s="245"/>
-      <c r="B7" s="246"/>
-      <c r="C7" s="245"/>
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="243"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="247"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="242"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="246"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="245"/>
+      <c r="A8" s="243"/>
+      <c r="B8" s="244"/>
+      <c r="C8" s="243"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="247"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="243"/>
-      <c r="L8" s="242"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="247"/>
+      <c r="L8" s="246"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="245"/>
-      <c r="B9" s="246"/>
-      <c r="C9" s="245"/>
+      <c r="A9" s="243"/>
+      <c r="B9" s="244"/>
+      <c r="C9" s="243"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="247"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="243"/>
-      <c r="L9" s="242"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="246"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="245"/>
-      <c r="B10" s="246"/>
-      <c r="C10" s="245"/>
+      <c r="A10" s="243"/>
+      <c r="B10" s="244"/>
+      <c r="C10" s="243"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="247"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="243"/>
-      <c r="L10" s="242"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="247"/>
+      <c r="L10" s="246"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="121" t="s">
@@ -17374,7 +17385,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -17392,7 +17403,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L11" s="107"/>
     </row>
@@ -17410,7 +17421,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -17428,7 +17439,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
@@ -17448,7 +17459,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
@@ -17466,7 +17477,7 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L13" s="107"/>
     </row>
@@ -17484,7 +17495,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -17502,10 +17513,10 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L14" s="129" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -17522,7 +17533,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -17667,17 +17678,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{FBE7E653-2382-46E4-9C76-9C694EDC9195}"/>
   <mergeCells count="11">
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="J6:J10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
@@ -17821,7 +17832,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="92.4">
@@ -17838,7 +17849,7 @@
         <v>152</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
@@ -17856,7 +17867,7 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L2" s="186"/>
     </row>
@@ -17894,7 +17905,7 @@
     </row>
     <row r="4" spans="1:12" ht="92.25" customHeight="1">
       <c r="A4" s="121" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>175</v>
@@ -17906,7 +17917,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -18044,7 +18055,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -18062,31 +18073,31 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L8" s="107"/>
     </row>
     <row r="9" spans="1:12" ht="43.2">
       <c r="A9" s="125" t="s">
+        <v>520</v>
+      </c>
+      <c r="B9" s="74" t="s">
         <v>521</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="C9" s="125" t="s">
         <v>522</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>523</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H9" s="127">
         <v>1</v>
@@ -18098,31 +18109,31 @@
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
       <c r="A10" s="121" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>526</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="121" t="s">
         <v>527</v>
-      </c>
-      <c r="C10" s="121" t="s">
-        <v>528</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H10" s="133">
         <v>1</v>
@@ -18134,29 +18145,29 @@
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L10" s="107"/>
     </row>
     <row r="11" spans="1:12" ht="43.2">
       <c r="A11" s="125" t="s">
+        <v>459</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="134" t="s">
         <v>461</v>
       </c>
-      <c r="C11" s="134" t="s">
+      <c r="D11" s="154" t="s">
         <v>462</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>463</v>
       </c>
       <c r="E11" s="126"/>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -18172,13 +18183,13 @@
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="121" t="s">
+        <v>530</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>531</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>532</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>533</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -18216,7 +18227,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -18270,19 +18281,19 @@
     </row>
     <row r="15" spans="1:12" ht="57.6">
       <c r="A15" s="125" t="s">
+        <v>534</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>535</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>536</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>537</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -18316,7 +18327,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -18350,7 +18361,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
@@ -18368,7 +18379,7 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L17" s="129"/>
     </row>
@@ -18386,7 +18397,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -18437,7 +18448,7 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="43.2">
@@ -18454,7 +18465,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -18478,19 +18489,19 @@
     </row>
     <row r="21" spans="1:12" ht="57.6">
       <c r="A21" s="125" t="s">
+        <v>544</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>545</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>546</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>547</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -18508,27 +18519,27 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
+        <v>548</v>
+      </c>
+      <c r="L21" s="192" t="s">
         <v>549</v>
-      </c>
-      <c r="L21" s="192" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="43.2">
       <c r="A22" s="121" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B22" s="35" t="s">
         <v>127</v>
       </c>
       <c r="C22" s="121" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" s="143" t="s">
         <v>333</v>
       </c>
-      <c r="D22" s="143" t="s">
-        <v>334</v>
-      </c>
       <c r="E22" s="35" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
@@ -18562,7 +18573,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -18580,7 +18591,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L23" s="195"/>
     </row>
@@ -19063,15 +19074,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -19314,6 +19316,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19327,14 +19338,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19353,6 +19356,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
   <ds:schemaRefs>
